--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -433,318 +433,320 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E2" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
-        <v>10:30:00-14:00:00; 14:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E3" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B4" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C4" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E4" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="H4" t="str">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B5" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C5" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E5" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="H5" t="str">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B6" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C6" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E6" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="F6" t="str">
-        <v>10:30:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="H6" t="str">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B7" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" t="str">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E7" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E8" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E9" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B10" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C10" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E10" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="str">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E11" t="str">
         <v>Available</v>
       </c>
       <c r="F11" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B12" t="str">
         <v>16</v>
       </c>
       <c r="C12" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E12" t="str">
         <v>Available</v>
       </c>
       <c r="F12" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -752,28 +754,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B13" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E13" t="str">
         <v>Available</v>
       </c>
       <c r="F13" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>7.25</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="str">
-        <v>7.25</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -781,28 +783,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>08:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G14" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -810,231 +812,231 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B15" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G15" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B16" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="H16" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="H17" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B18" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G18" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="H18" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="I18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
       </c>
       <c r="F19" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G19" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="H19" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="I19" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B20" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
       </c>
       <c r="F20" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G20" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="H20" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B21" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
       </c>
       <c r="F21" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G21" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>4.75</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B22" t="str">
-        <v>14</v>
+        <v>37.5</v>
       </c>
       <c r="C22" t="str">
-        <v>2.8</v>
+        <v>9.38</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
       </c>
       <c r="F22" t="str">
-        <v>09:15:00-14:45:00</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>5.5</v>
+        <v>9.38</v>
       </c>
       <c r="H22" t="str">
-        <v>5.5</v>
+        <v>9.38</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1042,28 +1044,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B23" t="str">
-        <v>14</v>
+        <v>37.5</v>
       </c>
       <c r="C23" t="str">
-        <v>2.8</v>
+        <v>9.38</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v>09:15:00-11:30:00</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>2.25</v>
+        <v>9.38</v>
       </c>
       <c r="H23" t="str">
-        <v>2.25</v>
+        <v>9.38</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1071,28 +1073,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B24" t="str">
-        <v>14</v>
+        <v>37.5</v>
       </c>
       <c r="C24" t="str">
-        <v>2.8</v>
+        <v>9.38</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>09:15:00-14:45:00</v>
+        <v/>
       </c>
       <c r="G24" t="str">
-        <v>5.5</v>
+        <v>9.38</v>
       </c>
       <c r="H24" t="str">
-        <v>5.5</v>
+        <v>9.38</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1100,28 +1102,28 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B25" t="str">
-        <v>14</v>
+        <v>37.5</v>
       </c>
       <c r="C25" t="str">
-        <v>2.8</v>
+        <v>9.38</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>09:15:00-11:30:00</v>
+        <v/>
       </c>
       <c r="G25" t="str">
-        <v>2.25</v>
+        <v>9.38</v>
       </c>
       <c r="H25" t="str">
-        <v>2.25</v>
+        <v>9.38</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1129,173 +1131,173 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B26" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C26" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>09:15:00-10:15:00</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B27" t="str">
         <v>20</v>
       </c>
       <c r="C27" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H27" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B28" t="str">
         <v>20</v>
       </c>
       <c r="C28" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
       </c>
       <c r="F28" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G28" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="I28" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B29" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C29" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B30" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C30" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H30" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B31" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C31" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G31" t="str">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="str">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1303,28 +1305,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B32" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C32" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G32" t="str">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="str">
-        <v>13.5</v>
+        <v>2.8</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1332,13 +1334,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B33" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="str">
         <v>2025-08-27</v>
@@ -1347,13 +1349,13 @@
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1361,13 +1363,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B34" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D34" t="str">
         <v>2025-08-28</v>
@@ -1376,13 +1378,13 @@
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G34" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1390,13 +1392,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B35" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C35" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="str">
         <v>2025-08-29</v>
@@ -1405,13 +1407,13 @@
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G35" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="H35" t="str">
-        <v>7.25</v>
+        <v>2.8</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1419,86 +1421,86 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B36" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G36" t="str">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B37" t="str">
         <v>20</v>
       </c>
       <c r="C37" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>16:45:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G37" t="str">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="H37" t="str">
-        <v>4.75</v>
+        <v>10</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="B38" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C38" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G38" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H38" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1506,28 +1508,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="B39" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C39" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G39" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H39" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1535,57 +1537,57 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="B40" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C40" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E40" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="F40" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H40" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I40" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="B41" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
       </c>
       <c r="F41" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G41" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H41" t="str">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1593,57 +1595,57 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B42" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C42" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D42" t="str">
         <v>2025-08-27</v>
       </c>
       <c r="E42" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="F42" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G42" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H42" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B43" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C43" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
       </c>
       <c r="F43" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G43" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="str">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1651,57 +1653,57 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B44" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C44" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E44" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H44" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B45" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C45" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
       </c>
       <c r="F45" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H45" t="str">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1709,57 +1711,57 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B46" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C46" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E46" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G46" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H46" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I46" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B47" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C47" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G47" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H47" t="str">
-        <v>4.5</v>
+        <v>6.67</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1767,31 +1769,31 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B48" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C48" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E48" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H48" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I48" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1805,19 +1807,19 @@
         <v>9</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G49" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H49" t="str">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1825,57 +1827,57 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B50" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C50" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E50" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00:00-16:45:00</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="H50" t="str">
         <v>0</v>
       </c>
       <c r="I50" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B51" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C51" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
       </c>
       <c r="F51" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H51" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1883,28 +1885,28 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B52" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C52" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
       </c>
       <c r="F52" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1912,13 +1914,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B53" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C53" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D53" t="str">
         <v>2025-08-30</v>
@@ -1927,13 +1929,13 @@
         <v>Available</v>
       </c>
       <c r="F53" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G53" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H53" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1950,19 +1952,19 @@
         <v>7.5</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
       </c>
       <c r="F54" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G54" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1970,7 +1972,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B55" t="str">
         <v>30</v>
@@ -1979,19 +1981,19 @@
         <v>7.5</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
       </c>
       <c r="F55" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G55" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -1999,7 +2001,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B56" t="str">
         <v>30</v>
@@ -2008,19 +2010,19 @@
         <v>7.5</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G56" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H56" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2028,7 +2030,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B57" t="str">
         <v>30</v>
@@ -2037,19 +2039,19 @@
         <v>7.5</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G57" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H57" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2066,19 +2068,19 @@
         <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G58" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2086,13 +2088,13 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B59" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C59" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D59" t="str">
         <v>2025-08-26</v>
@@ -2101,13 +2103,13 @@
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G59" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2115,28 +2117,28 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B60" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C60" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G60" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2144,28 +2146,28 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B61" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
       </c>
       <c r="F61" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G61" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2182,19 +2184,19 @@
         <v>11.25</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
       </c>
       <c r="F62" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G62" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="H62" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2202,28 +2204,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B63" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C63" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
       </c>
       <c r="F63" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="H63" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2231,28 +2233,28 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B64" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C64" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
       </c>
       <c r="F64" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G64" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="H64" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2260,28 +2262,28 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B65" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C65" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
       </c>
       <c r="F65" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G65" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="H65" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2298,19 +2300,19 @@
         <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G66" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2327,19 +2329,19 @@
         <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G67" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2347,89 +2349,89 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B68" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G68" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B69" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G69" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B70" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G70" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="I70" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2443,19 +2445,19 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G71" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="H71" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="I71" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
@@ -2472,19 +2474,19 @@
         <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G72" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="I72" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
@@ -2492,89 +2494,89 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B73" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G73" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B74" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G74" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B75" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C75" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G75" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="76">
@@ -2588,19 +2590,19 @@
         <v>6</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G76" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2617,19 +2619,19 @@
         <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G77" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2637,28 +2639,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C78" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00:00-17:15:00</v>
+        <v/>
       </c>
       <c r="G78" t="str">
-        <v>9.25</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>9.25</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2666,28 +2668,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B79" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C79" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>08:00:00-13:00:00</v>
+        <v/>
       </c>
       <c r="G79" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H79" t="str">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2695,13 +2697,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B80" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C80" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D80" t="str">
         <v>2025-08-31</v>
@@ -2710,13 +2712,13 @@
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>08:00:00-18:00:00</v>
+        <v/>
       </c>
       <c r="G80" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -2724,28 +2726,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B81" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C81" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="G81" t="str">
-        <v>7</v>
+        <v>5.33</v>
       </c>
       <c r="H81" t="str">
-        <v>7</v>
+        <v>5.33</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2753,28 +2755,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B82" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>08:00:00-15:00:00; 08:00:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G82" t="str">
-        <v>13</v>
+        <v>5.33</v>
       </c>
       <c r="H82" t="str">
-        <v>13</v>
+        <v>5.33</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2782,28 +2784,28 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B83" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C83" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
       </c>
       <c r="F83" t="str">
-        <v>08:00:00-14:00:00; 08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="G83" t="str">
-        <v>13</v>
+        <v>5.33</v>
       </c>
       <c r="H83" t="str">
-        <v>13</v>
+        <v>5.33</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2820,19 +2822,19 @@
         <v>4</v>
       </c>
       <c r="D84" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E84" t="str">
         <v>Available</v>
       </c>
       <c r="F84" t="str">
-        <v>08:00:00-15:00:00; 08:00:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G84" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H84" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2849,19 +2851,19 @@
         <v>4</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E85" t="str">
         <v>Available</v>
       </c>
       <c r="F85" t="str">
-        <v>08:00:00-14:00:00; 08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="G85" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H85" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2869,28 +2871,28 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B86" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C86" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E86" t="str">
         <v>Available</v>
       </c>
       <c r="F86" t="str">
-        <v>09:15:00-10:15:00</v>
+        <v/>
       </c>
       <c r="G86" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H86" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2898,63 +2900,63 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B87" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C87" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E87" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F87" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="G87" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H87" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I87" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B88" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C88" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E88" t="str">
         <v>Available</v>
       </c>
       <c r="F88" t="str">
-        <v>09:15:00-16:15:00</v>
+        <v/>
       </c>
       <c r="G88" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H88" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I88" t="str">
         <v/>
       </c>
     </row>
-    <row r="89" xml:space="preserve">
+    <row r="89">
       <c r="A89" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
@@ -2965,23 +2967,22 @@
         <v>4.8</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E89" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F89" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="G89" t="str">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="H89" t="str">
-        <v>2</v>
-      </c>
-      <c r="I89" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>4.8</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -2995,19 +2996,19 @@
         <v>4.8</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E90" t="str">
         <v>Available</v>
       </c>
       <c r="F90" t="str">
-        <v>09:15:00-16:30:00; 16:15:00-17:15:00</v>
+        <v/>
       </c>
       <c r="G90" t="str">
-        <v>8.25</v>
+        <v>2.8</v>
       </c>
       <c r="H90" t="str">
-        <v>8.25</v>
+        <v>2.8</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3024,25 +3025,25 @@
         <v>4.8</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E91" t="str">
         <v>Available</v>
       </c>
       <c r="F91" t="str">
-        <v>09:15:00-16:15:00</v>
+        <v/>
       </c>
       <c r="G91" t="str">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="H91" t="str">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="I91" t="str">
         <v/>
       </c>
     </row>
-    <row r="92" xml:space="preserve">
+    <row r="92">
       <c r="A92" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
@@ -3053,23 +3054,22 @@
         <v>4.8</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E92" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F92" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="G92" t="str">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="H92" t="str">
-        <v>2</v>
-      </c>
-      <c r="I92" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>4.8</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -3089,13 +3089,13 @@
         <v>Available</v>
       </c>
       <c r="F93" t="str">
-        <v>09:15:00-17:00:00; 17:00:00-18:15:00</v>
+        <v/>
       </c>
       <c r="G93" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H93" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3118,16 +3118,16 @@
         <v>Available</v>
       </c>
       <c r="F94" t="str">
-        <v>09:15:00-14:00:00; 14:00:00-15:00:00; 15:00:00-15:15:00; 16:45:00-17:45:00; 16:45:00-21:30:00</v>
+        <v/>
       </c>
       <c r="G94" t="str">
-        <v>11.75</v>
+        <v>6</v>
       </c>
       <c r="H94" t="str">
-        <v>11.75</v>
+        <v>6</v>
       </c>
       <c r="I94" t="str">
-        <v>Lori has agreed to extend her availability via email on 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -3147,7 +3147,7 @@
         <v>Available</v>
       </c>
       <c r="F95" t="str">
-        <v>09:15:00-14:00:00; 14:00:00-15:00:00; 15:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="G95" t="str">
         <v>6</v>
@@ -3176,13 +3176,13 @@
         <v>Available</v>
       </c>
       <c r="F96" t="str">
-        <v>09:15:00-15:00:00; 14:00:00-16:45:00; 16:45:00-17:45:00</v>
+        <v/>
       </c>
       <c r="G96" t="str">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="H96" t="str">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3205,13 +3205,13 @@
         <v>Available</v>
       </c>
       <c r="F97" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G97" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="H97" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3234,13 +3234,13 @@
         <v>Available</v>
       </c>
       <c r="F98" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="G98" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="H98" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3288,10 +3288,10 @@
         <v>2025-08-25</v>
       </c>
       <c r="B2" t="str">
-        <v>100.25</v>
+        <v>50.17</v>
       </c>
       <c r="C2" t="str">
-        <v>92.75</v>
+        <v>50.17</v>
       </c>
       <c r="D2" t="str">
         <v>0</v>
@@ -3303,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>92.75</v>
+        <v>50.17</v>
       </c>
       <c r="H2" t="str">
         <v>Sufficient</v>
@@ -3314,22 +3314,22 @@
         <v>2025-08-26</v>
       </c>
       <c r="B3" t="str">
-        <v>152.5</v>
+        <v>83.8</v>
       </c>
       <c r="C3" t="str">
-        <v>143.5</v>
+        <v>83.8</v>
       </c>
       <c r="D3" t="str">
         <v>0</v>
       </c>
       <c r="E3" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="str">
         <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>143.5</v>
+        <v>83.8</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -3340,22 +3340,22 @@
         <v>2025-08-27</v>
       </c>
       <c r="B4" t="str">
-        <v>157.5</v>
+        <v>79.47</v>
       </c>
       <c r="C4" t="str">
-        <v>148.5</v>
+        <v>79.47</v>
       </c>
       <c r="D4" t="str">
         <v>0</v>
       </c>
       <c r="E4" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
         <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>148.5</v>
+        <v>79.47</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -3366,22 +3366,22 @@
         <v>2025-08-28</v>
       </c>
       <c r="B5" t="str">
-        <v>151.25</v>
+        <v>80.8</v>
       </c>
       <c r="C5" t="str">
-        <v>142.25</v>
+        <v>80.8</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
         <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>142.25</v>
+        <v>80.8</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3392,22 +3392,22 @@
         <v>2025-08-29</v>
       </c>
       <c r="B6" t="str">
-        <v>129.25</v>
+        <v>72.13</v>
       </c>
       <c r="C6" t="str">
-        <v>120.25</v>
+        <v>72.13</v>
       </c>
       <c r="D6" t="str">
         <v>0</v>
       </c>
       <c r="E6" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
         <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>120.25</v>
+        <v>72.13</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3418,22 +3418,22 @@
         <v>2025-08-30</v>
       </c>
       <c r="B7" t="str">
-        <v>81</v>
+        <v>33.67</v>
       </c>
       <c r="C7" t="str">
-        <v>72</v>
+        <v>33.67</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="F7" t="str">
         <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>72</v>
+        <v>33.67</v>
       </c>
       <c r="H7" t="str">
         <v>Sufficient</v>
@@ -3444,10 +3444,10 @@
         <v>2025-08-31</v>
       </c>
       <c r="B8" t="str">
-        <v>84.75</v>
+        <v>47</v>
       </c>
       <c r="C8" t="str">
-        <v>84.75</v>
+        <v>47</v>
       </c>
       <c r="D8" t="str">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>84.75</v>
+        <v>47</v>
       </c>
       <c r="H8" t="str">
         <v>Sufficient</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B2" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
@@ -3513,16 +3513,16 @@
         <v>Available</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>7.5</v>
       </c>
       <c r="F2" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3539,16 +3539,16 @@
         <v>Available</v>
       </c>
       <c r="D3" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3556,77 +3556,77 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B4" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="C4" t="str">
         <v>Available</v>
       </c>
       <c r="D4" t="str">
-        <v>10:30:00-14:00:00; 14:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F4" t="str">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="G4" t="str">
-        <v>4.75</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B5" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C5" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D5" t="str">
-        <v>09:15:00-14:45:00</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B6" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3634,25 +3634,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -3660,51 +3660,51 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>6.75</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>6.75</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>09:15:00-10:15:00</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G9" t="str">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -3712,48 +3712,48 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B10" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C10" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>08:00:00-16:45:00</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>7.5</v>
+        <v>9.38</v>
       </c>
       <c r="F10" t="str">
-        <v>8.75</v>
+        <v>9.38</v>
       </c>
       <c r="G10" t="str">
-        <v>0</v>
+        <v>9.38</v>
       </c>
       <c r="H10" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B11" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="str">
         <v>6</v>
@@ -3764,80 +3764,80 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B12" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C12" t="str">
         <v>Available</v>
       </c>
       <c r="D12" t="str">
-        <v>08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F12" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="F13" t="str">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B14" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15:00-14:00:00; 14:00:00-15:00:00; 15:00:00-15:15:00; 16:45:00-17:45:00; 16:45:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F14" t="str">
-        <v>11.75</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="str">
-        <v>11.75</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="str">
-        <v>Lori has agreed to extend her availability via email on 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3845,22 +3845,22 @@
         <v>2025-08-26</v>
       </c>
       <c r="B15" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v>7.5</v>
       </c>
       <c r="F15" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -3871,25 +3871,25 @@
         <v>2025-08-26</v>
       </c>
       <c r="B16" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G16" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H16" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3897,22 +3897,22 @@
         <v>2025-08-26</v>
       </c>
       <c r="B17" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E17" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="F17" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="G17" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3923,25 +3923,25 @@
         <v>2025-08-26</v>
       </c>
       <c r="B18" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C18" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E18" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F18" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="G18" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H18" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
@@ -3949,22 +3949,22 @@
         <v>2025-08-26</v>
       </c>
       <c r="B19" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E19" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F19" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="str">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -3972,51 +3972,51 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B20" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C20" t="str">
         <v>Available</v>
       </c>
       <c r="D20" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="str">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="str">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="H20" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B21" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>09:15:00-11:30:00</v>
+        <v/>
       </c>
       <c r="E21" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F21" t="str">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="G21" t="str">
-        <v>2.25</v>
+        <v>7.5</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -4024,51 +4024,51 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B22" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C22" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D22" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="G22" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B23" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C23" t="str">
         <v>Available</v>
       </c>
       <c r="D23" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>9.38</v>
+        <v>9</v>
       </c>
       <c r="F23" t="str">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -4076,25 +4076,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B24" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E24" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F24" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="G24" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -4102,77 +4102,77 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B25" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v>3.2</v>
       </c>
       <c r="F25" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B26" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C26" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="E26" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="F26" t="str">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G26" t="str">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="H26" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B27" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>09:15:00-16:15:00</v>
+        <v/>
       </c>
       <c r="E27" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F27" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" t="str">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -4180,25 +4180,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B28" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E28" t="str">
-        <v>7.5</v>
+        <v>9.38</v>
       </c>
       <c r="F28" t="str">
-        <v>7.25</v>
+        <v>9.38</v>
       </c>
       <c r="G28" t="str">
-        <v>7.25</v>
+        <v>9.38</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -4206,25 +4206,25 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B29" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C29" t="str">
         <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00:00-15:00:00; 08:00:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F29" t="str">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G29" t="str">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -4232,77 +4232,78 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B30" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C30" t="str">
         <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E30" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="F30" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B31" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C31" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D31" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E31" t="str">
-        <v>2.67</v>
+        <v>4.8</v>
       </c>
       <c r="F31" t="str">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="G31" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>0</v>
+      </c>
+      <c r="H31" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B32" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C32" t="str">
         <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v>09:15:00-14:00:00; 14:00:00-15:00:00; 15:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F32" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G32" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -4313,25 +4314,25 @@
         <v>2025-08-27</v>
       </c>
       <c r="B33" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v>4</v>
       </c>
       <c r="F33" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G33" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -4339,22 +4340,22 @@
         <v>2025-08-27</v>
       </c>
       <c r="B34" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E34" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F34" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -4365,25 +4366,25 @@
         <v>2025-08-27</v>
       </c>
       <c r="B35" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C35" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E35" t="str">
-        <v>9</v>
+        <v>11.25</v>
       </c>
       <c r="F35" t="str">
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="G35" t="str">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="H35" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4391,25 +4392,25 @@
         <v>2025-08-27</v>
       </c>
       <c r="B36" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E36" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F36" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="G36" t="str">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="37">
@@ -4417,22 +4418,22 @@
         <v>2025-08-27</v>
       </c>
       <c r="B37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
       </c>
       <c r="D37" t="str">
-        <v>16:45:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E37" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="F37" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="G37" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -4440,51 +4441,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B38" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E38" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
-        <v>10.5</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B39" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>09:15:00-14:45:00</v>
+        <v/>
       </c>
       <c r="E39" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F39" t="str">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="G39" t="str">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4492,51 +4493,51 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B40" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C40" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D40" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E40" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40" t="str">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="G40" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B41" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>08:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E41" t="str">
-        <v>9.38</v>
+        <v>9</v>
       </c>
       <c r="F41" t="str">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G41" t="str">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4544,25 +4545,25 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B42" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
       </c>
       <c r="D42" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E42" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F42" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="G42" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -4570,78 +4571,77 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B43" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C43" t="str">
         <v>Available</v>
       </c>
       <c r="D43" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v>3.2</v>
       </c>
       <c r="F43" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="G43" t="str">
-        <v>6.75</v>
+        <v>3.2</v>
       </c>
       <c r="H43" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="44" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B44" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C44" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="E44" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="F44" t="str">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="G44" t="str">
-        <v>2</v>
-      </c>
-      <c r="H44" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>2.8</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B45" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>09:15:00-16:30:00; 16:15:00-17:15:00</v>
+        <v/>
       </c>
       <c r="E45" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="G45" t="str">
-        <v>8.25</v>
+        <v>6</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4649,25 +4649,25 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B46" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="F46" t="str">
-        <v>7.25</v>
+        <v>9.38</v>
       </c>
       <c r="G46" t="str">
-        <v>7.25</v>
+        <v>9.38</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4675,51 +4675,51 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B47" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C47" t="str">
         <v>Available</v>
       </c>
       <c r="D47" t="str">
-        <v>08:00:00-14:00:00; 08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="E47" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F47" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="G47" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B48" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E48" t="str">
-        <v>11.25</v>
+        <v>4.8</v>
       </c>
       <c r="F48" t="str">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="G48" t="str">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -4727,51 +4727,51 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B49" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E49" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F49" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G49" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B50" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>09:15:00-15:00:00; 14:00:00-16:45:00; 16:45:00-17:45:00</v>
+        <v/>
       </c>
       <c r="E50" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" t="str">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="G50" t="str">
-        <v>9.5</v>
+        <v>4</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -4782,25 +4782,25 @@
         <v>2025-08-28</v>
       </c>
       <c r="B51" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
       </c>
       <c r="D51" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="F51" t="str">
-        <v>4.75</v>
+        <v>11.25</v>
       </c>
       <c r="G51" t="str">
-        <v>4.75</v>
+        <v>11.25</v>
       </c>
       <c r="H51" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -4808,22 +4808,22 @@
         <v>2025-08-28</v>
       </c>
       <c r="B52" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E52" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F52" t="str">
-        <v>13.5</v>
+        <v>5.33</v>
       </c>
       <c r="G52" t="str">
-        <v>13.5</v>
+        <v>5.33</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -4834,25 +4834,25 @@
         <v>2025-08-28</v>
       </c>
       <c r="B53" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C53" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E53" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F53" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="G53" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H53" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -4860,22 +4860,22 @@
         <v>2025-08-28</v>
       </c>
       <c r="B54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G54" t="str">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -4883,103 +4883,103 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B55" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E55" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="F55" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B56" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (GH), Kaitlyn</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>09:15:00-15:15:00; 10:30:00-14:00:00; 20:30:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E56" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F56" t="str">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="G56" t="str">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="H56" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B57" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C57" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D57" t="str">
-        <v>09:15:00-11:30:00</v>
+        <v/>
       </c>
       <c r="E57" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="str">
-        <v>2.25</v>
+        <v>9</v>
       </c>
       <c r="G57" t="str">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B58" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E58" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F58" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="G58" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -4987,77 +4987,77 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B59" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E59" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="F59" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="G59" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E60" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F60" t="str">
-        <v>6.75</v>
+        <v>2.8</v>
       </c>
       <c r="G60" t="str">
-        <v>6.75</v>
+        <v>2.8</v>
       </c>
       <c r="H60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B61" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>09:15:00-16:15:00</v>
+        <v/>
       </c>
       <c r="E61" t="str">
-        <v>4.8</v>
+        <v>9.38</v>
       </c>
       <c r="F61" t="str">
-        <v>7</v>
+        <v>9.38</v>
       </c>
       <c r="G61" t="str">
-        <v>7</v>
+        <v>9.38</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -5065,25 +5065,25 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B62" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C62" t="str">
         <v>Available</v>
       </c>
       <c r="D62" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E62" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="G62" t="str">
-        <v>7.25</v>
+        <v>6</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -5091,77 +5091,78 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B63" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>08:00:00-15:00:00; 08:00:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E63" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="G63" t="str">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="H63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B64" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C64" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D64" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E64" t="str">
-        <v>11.25</v>
+        <v>4.8</v>
       </c>
       <c r="F64" t="str">
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="G64" t="str">
-        <v>13.5</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B65" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>08:00:00-17:15:00</v>
+        <v/>
       </c>
       <c r="E65" t="str">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="F65" t="str">
-        <v>9.25</v>
+        <v>2.8</v>
       </c>
       <c r="G65" t="str">
-        <v>9.25</v>
+        <v>2.8</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -5169,25 +5170,25 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B66" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
       </c>
       <c r="D66" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E66" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F66" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G66" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -5195,25 +5196,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B67" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E67" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G67" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5224,25 +5225,25 @@
         <v>2025-08-29</v>
       </c>
       <c r="B68" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
       </c>
       <c r="D68" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E68" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="F68" t="str">
-        <v>4.75</v>
+        <v>11.25</v>
       </c>
       <c r="G68" t="str">
-        <v>4.75</v>
+        <v>11.25</v>
       </c>
       <c r="H68" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -5250,22 +5251,22 @@
         <v>2025-08-29</v>
       </c>
       <c r="B69" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E69" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F69" t="str">
-        <v>13.5</v>
+        <v>5.33</v>
       </c>
       <c r="G69" t="str">
-        <v>13.5</v>
+        <v>5.33</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -5276,25 +5277,25 @@
         <v>2025-08-29</v>
       </c>
       <c r="B70" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C70" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E70" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F70" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="G70" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H70" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -5302,22 +5303,22 @@
         <v>2025-08-29</v>
       </c>
       <c r="B71" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E71" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F71" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G71" t="str">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -5325,77 +5326,77 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B72" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>10:30:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F72" t="str">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="G72" t="str">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="H72" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B73" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C73" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D73" t="str">
-        <v>09:15:00-10:15:00</v>
+        <v/>
       </c>
       <c r="E73" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="str">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G73" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B74" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E74" t="str">
-        <v>9.38</v>
+        <v>9</v>
       </c>
       <c r="F74" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5403,7 +5404,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B75" t="str">
         <v>Hussain (NL) (GH), Mustansar</v>
@@ -5412,16 +5413,16 @@
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E75" t="str">
         <v>6</v>
       </c>
       <c r="F75" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G75" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5429,104 +5430,103 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B76" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15:00-15:00:00; 14:15:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E76" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F76" t="str">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="G76" t="str">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="H76" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="77" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B77" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C77" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>10:30:00-12:30:00</v>
+        <v/>
       </c>
       <c r="E77" t="str">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="F77" t="str">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="G77" t="str">
-        <v>2</v>
-      </c>
-      <c r="H77" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>2.67</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B78" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>09:15:00-17:00:00; 17:00:00-18:15:00</v>
+        <v/>
       </c>
       <c r="E78" t="str">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="F78" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G78" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B79" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E79" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F79" t="str">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="G79" t="str">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -5534,77 +5534,77 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B80" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00:00-14:00:00; 08:00:00-15:00:00</v>
+        <v/>
       </c>
       <c r="E80" t="str">
         <v>4</v>
       </c>
       <c r="F80" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G80" t="str">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B81" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E81" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="F81" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="G81" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B82" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C82" t="str">
         <v>Available</v>
       </c>
       <c r="D82" t="str">
-        <v>08:00:00-13:00:00</v>
+        <v/>
       </c>
       <c r="E82" t="str">
-        <v>5.33</v>
+        <v>2.8</v>
       </c>
       <c r="F82" t="str">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="G82" t="str">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -5612,25 +5612,25 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B83" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E83" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F83" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="G83" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5638,25 +5638,25 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B84" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C84" t="str">
         <v>Available</v>
       </c>
       <c r="D84" t="str">
-        <v>09:15:00-14:00:00</v>
+        <v/>
       </c>
       <c r="E84" t="str">
         <v>6</v>
       </c>
       <c r="F84" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="G84" t="str">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -5664,103 +5664,103 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B85" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C85" t="str">
         <v>Available</v>
       </c>
       <c r="D85" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E85" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F85" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="G85" t="str">
-        <v>13.5</v>
+        <v>3.2</v>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B86" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C86" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D86" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E86" t="str">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="F86" t="str">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="G86" t="str">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H86" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B87" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C87" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D87" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E87" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F87" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="G87" t="str">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B88" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
       </c>
       <c r="D88" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E88" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F88" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="G88" t="str">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5768,25 +5768,25 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B89" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C89" t="str">
         <v>Available</v>
       </c>
       <c r="D89" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E89" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F89" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="G89" t="str">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5794,7 +5794,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B90" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
@@ -5803,45 +5803,45 @@
         <v>Available</v>
       </c>
       <c r="D90" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E90" t="str">
         <v>2.67</v>
       </c>
       <c r="F90" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="G90" t="str">
-        <v>13.5</v>
+        <v>2.67</v>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B91" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
       </c>
       <c r="D91" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E91" t="str">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F91" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G91" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H91" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -5855,16 +5855,16 @@
         <v>Available</v>
       </c>
       <c r="D92" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E92" t="str">
         <v>7.5</v>
       </c>
       <c r="F92" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="G92" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -5881,16 +5881,16 @@
         <v>Available</v>
       </c>
       <c r="D93" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E93" t="str">
         <v>6.67</v>
       </c>
       <c r="F93" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="G93" t="str">
-        <v>13.5</v>
+        <v>6.67</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5907,16 +5907,16 @@
         <v>Available</v>
       </c>
       <c r="D94" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E94" t="str">
         <v>6</v>
       </c>
       <c r="F94" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="G94" t="str">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5933,16 +5933,16 @@
         <v>Available</v>
       </c>
       <c r="D95" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E95" t="str">
         <v>7.5</v>
       </c>
       <c r="F95" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="G95" t="str">
-        <v>13.5</v>
+        <v>7.5</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -5959,16 +5959,16 @@
         <v>Available</v>
       </c>
       <c r="D96" t="str">
-        <v>08:00:00-15:15:00</v>
+        <v/>
       </c>
       <c r="E96" t="str">
         <v>4</v>
       </c>
       <c r="F96" t="str">
-        <v>7.25</v>
+        <v>4</v>
       </c>
       <c r="G96" t="str">
-        <v>7.25</v>
+        <v>4</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -5985,16 +5985,16 @@
         <v>Available</v>
       </c>
       <c r="D97" t="str">
-        <v>08:00:00-18:00:00</v>
+        <v/>
       </c>
       <c r="E97" t="str">
         <v>5.33</v>
       </c>
       <c r="F97" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="G97" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6011,16 +6011,16 @@
         <v>Available</v>
       </c>
       <c r="D98" t="str">
-        <v>08:00:00-21:30:00</v>
+        <v/>
       </c>
       <c r="E98" t="str">
         <v>10</v>
       </c>
       <c r="F98" t="str">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="G98" t="str">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="H98" t="str">
         <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3300,13 +3300,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G2" t="str">
-        <v>50.17</v>
+        <v>-13.83</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
@@ -3326,13 +3326,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G3" t="str">
-        <v>83.8</v>
+        <v>-14.2</v>
       </c>
       <c r="H3" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="4">
@@ -3352,13 +3352,13 @@
         <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G4" t="str">
-        <v>79.47</v>
+        <v>-25.53</v>
       </c>
       <c r="H4" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="5">
@@ -3378,13 +3378,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G5" t="str">
-        <v>80.8</v>
+        <v>-16.2</v>
       </c>
       <c r="H5" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="6">
@@ -3404,10 +3404,10 @@
         <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="G6" t="str">
-        <v>72.13</v>
+        <v>13.13</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3430,13 +3430,13 @@
         <v>9</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G7" t="str">
-        <v>33.67</v>
+        <v>-10.33</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
@@ -3456,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="H8" t="str">
         <v>Sufficient</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3268,7 +3268,7 @@
         <v>Net Capacity</v>
       </c>
       <c r="D1" t="str">
-        <v>Sickness</v>
+        <v>Unavailability</v>
       </c>
       <c r="E1" t="str">
         <v>Holidays</v>
@@ -3294,7 +3294,7 @@
         <v>50.17</v>
       </c>
       <c r="D2" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>83.8</v>
       </c>
       <c r="D3" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
         <v>9</v>
@@ -3346,7 +3346,7 @@
         <v>79.47</v>
       </c>
       <c r="D4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>9</v>
@@ -3398,7 +3398,7 @@
         <v>72.13</v>
       </c>
       <c r="D6" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
         <v>9</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -34,9 +34,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,89 +432,89 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B2" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C2" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E2" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B3" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E3" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B4" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C4" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E4" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E5" t="str">
         <v>Holiday</v>
@@ -558,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E6" t="str">
         <v>Holiday</v>
@@ -578,236 +577,238 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B7" t="str">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C7" t="str">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B8" t="str">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C8" t="str">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E8" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H8" t="str">
         <v>0</v>
       </c>
-      <c r="I8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+      <c r="I8" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B9" t="str">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C9" t="str">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E9" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+      <c r="I9" t="str">
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B10" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E10" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F10" t="str">
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="H10" t="str">
         <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B11" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C11" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E11" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H11" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B12" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C12" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E12" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H12" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. _x000d_
+_x000d_
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B13" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C13" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E13" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H13" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="I13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. _x000d_
+_x000d_
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B14" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C14" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E14" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="15">
@@ -821,7 +822,7 @@
         <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
@@ -841,16 +842,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
@@ -859,27 +860,27 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
@@ -888,27 +889,27 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B18" t="str">
         <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -917,27 +918,27 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B19" t="str">
         <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -946,13 +947,13 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="20">
@@ -966,7 +967,7 @@
         <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -981,7 +982,7 @@
         <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
@@ -995,7 +996,7 @@
         <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1004,27 +1005,27 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B22" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1033,27 +1034,27 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1062,10 +1063,10 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1073,16 +1074,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B24" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
@@ -1091,10 +1092,10 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1102,16 +1103,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B25" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
@@ -1120,10 +1121,10 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1131,16 +1132,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B26" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C26" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
@@ -1149,27 +1150,27 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H26" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I26" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B27" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
@@ -1178,27 +1179,27 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I27" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B28" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1207,27 +1208,27 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I28" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B29" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
@@ -1236,13 +1237,13 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I29" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1256,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
@@ -1276,16 +1277,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B31" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
@@ -1294,27 +1295,27 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B32" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
@@ -1323,27 +1324,27 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B33" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
@@ -1352,27 +1353,27 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B34" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
@@ -1381,13 +1382,13 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="35">
@@ -1401,7 +1402,7 @@
         <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
@@ -1421,16 +1422,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B36" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C36" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1439,27 +1440,27 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I36" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1468,27 +1469,27 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B38" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C38" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1497,10 +1498,10 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1508,16 +1509,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B39" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1526,10 +1527,10 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1537,16 +1538,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B40" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1555,27 +1556,27 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B41" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1584,27 +1585,27 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B42" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C42" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1613,10 +1614,10 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H42" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1624,16 +1625,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B43" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1642,10 +1643,10 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1653,16 +1654,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B44" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
@@ -1671,10 +1672,10 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1682,16 +1683,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B45" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1700,10 +1701,10 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1711,13 +1712,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B46" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C46" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
         <v>2025-08-27</v>
@@ -1729,10 +1730,10 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1740,13 +1741,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B47" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D47" t="str">
         <v>2025-08-28</v>
@@ -1758,10 +1759,10 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1769,16 +1770,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B48" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1787,10 +1788,10 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1798,16 +1799,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B49" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C49" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
@@ -1816,10 +1817,10 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1827,13 +1828,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B50" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C50" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D50" t="str">
         <v>2025-08-27</v>
@@ -1845,10 +1846,10 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H50" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1856,13 +1857,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B51" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D51" t="str">
         <v>2025-08-28</v>
@@ -1874,10 +1875,10 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H51" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1885,16 +1886,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B52" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1903,10 +1904,10 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H52" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1923,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1943,16 +1944,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B54" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C54" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1972,16 +1973,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B55" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C55" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1990,10 +1991,10 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H55" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2001,16 +2002,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B56" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C56" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
@@ -2019,10 +2020,10 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2030,16 +2031,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B57" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C57" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
@@ -2048,10 +2049,10 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2059,7 +2060,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B58" t="str">
         <v>30</v>
@@ -2077,10 +2078,10 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H58" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2088,7 +2089,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B59" t="str">
         <v>30</v>
@@ -2117,7 +2118,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B60" t="str">
         <v>30</v>
@@ -2146,7 +2147,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
@@ -2175,16 +2176,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B62" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C62" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2193,10 +2194,10 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H62" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2204,16 +2205,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B63" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2222,10 +2223,10 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2233,16 +2234,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B64" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2251,10 +2252,10 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2262,16 +2263,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B65" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2280,10 +2281,10 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2291,16 +2292,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B66" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C66" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
@@ -2309,10 +2310,10 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H66" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2320,16 +2321,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B67" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
@@ -2338,10 +2339,10 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2349,16 +2350,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B68" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
@@ -2367,10 +2368,10 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2378,13 +2379,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B69" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D69" t="str">
         <v>2025-08-29</v>
@@ -2396,10 +2397,10 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2416,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
@@ -2436,16 +2437,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B71" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
@@ -2454,27 +2455,27 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I71" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B72" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
@@ -2483,27 +2484,27 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B73" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
@@ -2512,27 +2513,27 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I73" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B74" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
@@ -2541,13 +2542,13 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -2561,7 +2562,7 @@
         <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
@@ -2581,16 +2582,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B76" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
@@ -2599,27 +2600,27 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B77" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
@@ -2628,27 +2629,27 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B78" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
@@ -2657,27 +2658,27 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B79" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
@@ -2686,13 +2687,13 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="80">
@@ -2706,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
@@ -2726,16 +2727,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B81" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
@@ -2744,10 +2745,10 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2755,16 +2756,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B82" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
@@ -2773,10 +2774,10 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2784,16 +2785,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B83" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
@@ -2802,10 +2803,10 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2813,16 +2814,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B84" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E84" t="str">
         <v>Available</v>
@@ -2831,10 +2832,10 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2842,16 +2843,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B85" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E85" t="str">
         <v>Available</v>
@@ -2860,10 +2861,10 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2871,16 +2872,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B86" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E86" t="str">
         <v>Available</v>
@@ -2889,10 +2890,10 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2900,16 +2901,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B87" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E87" t="str">
         <v>Available</v>
@@ -2918,10 +2919,10 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2929,16 +2930,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B88" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C88" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E88" t="str">
         <v>Available</v>
@@ -2947,27 +2948,27 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B89" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C89" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E89" t="str">
         <v>Available</v>
@@ -2976,10 +2977,10 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H89" t="str">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -2987,16 +2988,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B90" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C90" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E90" t="str">
         <v>Available</v>
@@ -3005,10 +3006,10 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H90" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3016,16 +3017,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B91" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C91" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E91" t="str">
         <v>Available</v>
@@ -3034,10 +3035,10 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H91" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3045,16 +3046,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B92" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C92" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E92" t="str">
         <v>Available</v>
@@ -3063,10 +3064,10 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="H92" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3074,16 +3075,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B93" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C93" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E93" t="str">
         <v>Available</v>
@@ -3092,10 +3093,10 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H93" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3103,16 +3104,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B94" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C94" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D94" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E94" t="str">
         <v>Available</v>
@@ -3121,10 +3122,10 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H94" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3132,16 +3133,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B95" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E95" t="str">
         <v>Available</v>
@@ -3150,10 +3151,10 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3161,16 +3162,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B96" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D96" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E96" t="str">
         <v>Available</v>
@@ -3179,10 +3180,10 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3190,16 +3191,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B97" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D97" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E97" t="str">
         <v>Available</v>
@@ -3208,10 +3209,10 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3219,36 +3220,329 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B98" t="str">
+        <v>24</v>
+      </c>
+      <c r="C98" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2025-08-25</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H98" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B99" t="str">
+        <v>24</v>
+      </c>
+      <c r="C99" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H99" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B100" t="str">
+        <v>24</v>
+      </c>
+      <c r="C100" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H100" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B101" t="str">
+        <v>24</v>
+      </c>
+      <c r="C101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B102" t="str">
+        <v>24</v>
+      </c>
+      <c r="C102" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H102" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B103" t="str">
         <v>30</v>
       </c>
-      <c r="C98" t="str">
-        <v>6</v>
-      </c>
-      <c r="D98" t="str">
+      <c r="C103" t="str">
+        <v>6</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2025-08-25</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>6</v>
+      </c>
+      <c r="H103" t="str">
+        <v>6</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B104" t="str">
+        <v>30</v>
+      </c>
+      <c r="C104" t="str">
+        <v>6</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>6</v>
+      </c>
+      <c r="H104" t="str">
+        <v>6</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B105" t="str">
+        <v>30</v>
+      </c>
+      <c r="C105" t="str">
+        <v>6</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>6</v>
+      </c>
+      <c r="H105" t="str">
+        <v>6</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B106" t="str">
+        <v>30</v>
+      </c>
+      <c r="C106" t="str">
+        <v>6</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>6</v>
+      </c>
+      <c r="H106" t="str">
+        <v>6</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B107" t="str">
+        <v>30</v>
+      </c>
+      <c r="C107" t="str">
+        <v>6</v>
+      </c>
+      <c r="D107" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="E98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F98" t="str">
-        <v/>
-      </c>
-      <c r="G98" t="str">
-        <v>6</v>
-      </c>
-      <c r="H98" t="str">
-        <v>6</v>
-      </c>
-      <c r="I98" t="str">
-        <v/>
+      <c r="E107" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>6</v>
+      </c>
+      <c r="H107" t="str">
+        <v>6</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B108" t="str">
+        <v>16</v>
+      </c>
+      <c r="C108" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Dependant Leave</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v>4.75</v>
+      </c>
+      <c r="H108" t="str">
+        <v>0</v>
+      </c>
+      <c r="I108" t="str" xml:space="preserve">
+        <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
+_x000d_
+Peter_x000d_
+26.8.25, 0827</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3294,16 +3588,16 @@
         <v>50.17</v>
       </c>
       <c r="D2" t="str">
-        <v>7.5</v>
+        <v>10.7</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G2" t="str">
-        <v>-13.83</v>
+        <v>-11.83</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3314,22 +3608,22 @@
         <v>2025-08-26</v>
       </c>
       <c r="B3" t="str">
-        <v>83.8</v>
+        <v>81.8</v>
       </c>
       <c r="C3" t="str">
-        <v>83.8</v>
+        <v>81.8</v>
       </c>
       <c r="D3" t="str">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="E3" t="str">
         <v>9</v>
       </c>
       <c r="F3" t="str">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G3" t="str">
-        <v>-14.2</v>
+        <v>-8.2</v>
       </c>
       <c r="H3" t="str">
         <v>Shortage</v>
@@ -3346,16 +3640,16 @@
         <v>79.47</v>
       </c>
       <c r="D4" t="str">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="E4" t="str">
         <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G4" t="str">
-        <v>-25.53</v>
+        <v>-24.53</v>
       </c>
       <c r="H4" t="str">
         <v>Shortage</v>
@@ -3366,10 +3660,10 @@
         <v>2025-08-28</v>
       </c>
       <c r="B5" t="str">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="C5" t="str">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
@@ -3378,10 +3672,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" t="str">
-        <v>-16.2</v>
+        <v>-12</v>
       </c>
       <c r="H5" t="str">
         <v>Shortage</v>
@@ -3392,10 +3686,10 @@
         <v>2025-08-29</v>
       </c>
       <c r="B6" t="str">
-        <v>72.13</v>
+        <v>75.33</v>
       </c>
       <c r="C6" t="str">
-        <v>72.13</v>
+        <v>75.33</v>
       </c>
       <c r="D6" t="str">
         <v>2</v>
@@ -3404,10 +3698,10 @@
         <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" t="str">
-        <v>13.13</v>
+        <v>17.33</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3430,10 +3724,10 @@
         <v>9</v>
       </c>
       <c r="F7" t="str">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" t="str">
-        <v>-10.33</v>
+        <v>-9.33</v>
       </c>
       <c r="H7" t="str">
         <v>Shortage</v>
@@ -3456,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" t="str">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" t="str">
         <v>Sufficient</v>
@@ -3474,7 +3768,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3504,7 +3798,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B2" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
@@ -3530,7 +3824,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3556,10 +3850,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B4" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C4" t="str">
         <v>Available</v>
@@ -3568,50 +3862,50 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B5" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C5" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B6" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
@@ -3620,13 +3914,13 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3634,10 +3928,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
@@ -3646,13 +3940,13 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -3660,10 +3954,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B8" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
@@ -3672,24 +3966,24 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B9" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
@@ -3698,13 +3992,13 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -3712,36 +4006,36 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B10" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C10" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="F10" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="G10" t="str">
-        <v>9.38</v>
+        <v>0</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B11" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
@@ -3750,13 +4044,13 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F11" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -3764,13 +4058,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B12" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Sick</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -3782,44 +4076,44 @@
         <v>3.2</v>
       </c>
       <c r="G12" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C13" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F13" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="str">
         <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B14" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
@@ -3828,13 +4122,13 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3842,10 +4136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B15" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
@@ -3854,24 +4148,24 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B16" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
@@ -3880,13 +4174,13 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3897,7 +4191,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B17" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
@@ -3906,13 +4200,13 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="G17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3923,7 +4217,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
@@ -3932,16 +4226,16 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F18" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G18" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="19">
@@ -3949,7 +4243,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B19" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
@@ -3958,13 +4252,13 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -3972,36 +4266,36 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C20" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F20" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B21" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
@@ -4010,13 +4304,13 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F21" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -4024,36 +4318,36 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B22" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C22" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D22" t="str">
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F22" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H22" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B23" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C23" t="str">
         <v>Available</v>
@@ -4062,13 +4356,13 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="F23" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -4076,10 +4370,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B24" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
@@ -4088,13 +4382,13 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="F24" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="G24" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -4102,10 +4396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B25" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
@@ -4114,13 +4408,13 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="F25" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="G25" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -4128,10 +4422,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B26" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
@@ -4140,13 +4434,13 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F26" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G26" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -4154,10 +4448,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B27" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
@@ -4166,50 +4460,50 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F27" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B28" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C28" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>9.38</v>
+        <v>4.8</v>
       </c>
       <c r="F28" t="str">
-        <v>9.38</v>
+        <v>2</v>
       </c>
       <c r="G28" t="str">
-        <v>9.38</v>
+        <v>0</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B29" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C29" t="str">
         <v>Available</v>
@@ -4218,13 +4512,13 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F29" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G29" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -4232,10 +4526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B30" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C30" t="str">
         <v>Available</v>
@@ -4244,51 +4538,50 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F30" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G30" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H30" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B31" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C31" t="str">
-        <v>Other Unavailable</v>
+        <v>Sick</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F31" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
       </c>
-      <c r="H31" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+      <c r="H31" t="str">
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B32" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C32" t="str">
         <v>Available</v>
@@ -4297,13 +4590,13 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F32" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G32" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -4311,10 +4604,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
@@ -4337,10 +4630,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B34" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
@@ -4349,13 +4642,13 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="F34" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -4363,33 +4656,33 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B35" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C35" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>11.25</v>
+        <v>2.67</v>
       </c>
       <c r="F35" t="str">
-        <v>11.25</v>
+        <v>2</v>
       </c>
       <c r="G35" t="str">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B36" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
@@ -4404,47 +4697,50 @@
         <v>2.67</v>
       </c>
       <c r="F36" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="G36" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="H36" t="str">
         <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B37" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C37" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F37" t="str">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="G37" t="str">
-        <v>6</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
+_x000d_
+Peter_x000d_
+26.8.25, 0827</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B38" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
@@ -4453,24 +4749,24 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F38" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H38" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B39" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
@@ -4479,53 +4775,53 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F39" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C40" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D40" t="str">
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F40" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G40" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H40" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B41" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C41" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D41" t="str">
         <v/>
@@ -4534,21 +4830,21 @@
         <v>9</v>
       </c>
       <c r="F41" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G41" t="str">
         <v>0</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B42" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4557,13 +4853,13 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="F42" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="G42" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H42" t="str">
         <v/>
@@ -4571,10 +4867,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B43" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C43" t="str">
         <v>Available</v>
@@ -4583,13 +4879,13 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F43" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G43" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -4597,10 +4893,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B44" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
@@ -4609,13 +4905,13 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F44" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G44" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4623,10 +4919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B45" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
@@ -4635,13 +4931,13 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F45" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G45" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4649,10 +4945,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B46" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
@@ -4661,13 +4957,13 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="F46" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="G46" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4675,10 +4971,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B47" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C47" t="str">
         <v>Available</v>
@@ -4687,24 +4983,24 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="F47" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="G47" t="str">
-        <v>3.2</v>
+        <v>9.38</v>
       </c>
       <c r="H47" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B48" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
@@ -4713,13 +5009,13 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F48" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="G48" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -4727,10 +5023,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B49" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
@@ -4739,50 +5035,52 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F49" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G49" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B50" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C50" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F50" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" t="str">
-        <v>4</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H50" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. _x000d_
+_x000d_
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B51" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
@@ -4791,13 +5089,13 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>11.25</v>
+        <v>4.8</v>
       </c>
       <c r="F51" t="str">
-        <v>11.25</v>
+        <v>2.8</v>
       </c>
       <c r="G51" t="str">
-        <v>11.25</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -4805,10 +5103,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B52" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
@@ -4817,13 +5115,13 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="F52" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="G52" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -4831,36 +5129,36 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B53" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C53" t="str">
-        <v>Available</v>
+        <v>Sick</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F53" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="G53" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B54" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
@@ -4869,13 +5167,13 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F54" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G54" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -4883,10 +5181,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B55" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
@@ -4904,15 +5202,15 @@
         <v>4</v>
       </c>
       <c r="H55" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B56" t="str">
-        <v>Barton (GH), Kaitlyn</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
@@ -4921,13 +5219,13 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="F56" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="G56" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -4935,36 +5233,36 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C57" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D57" t="str">
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F57" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="G57" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H57" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B58" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
@@ -4973,13 +5271,13 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F58" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G58" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -4987,10 +5285,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B59" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
@@ -4999,24 +5297,24 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F59" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G59" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H59" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B60" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
@@ -5025,13 +5323,13 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F60" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="G60" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -5039,36 +5337,36 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B61" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C61" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>9.38</v>
+        <v>9</v>
       </c>
       <c r="F61" t="str">
-        <v>9.38</v>
+        <v>9</v>
       </c>
       <c r="G61" t="str">
-        <v>9.38</v>
+        <v>0</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B62" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C62" t="str">
         <v>Available</v>
@@ -5077,13 +5375,13 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F62" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -5091,10 +5389,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B63" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
@@ -5103,51 +5401,50 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F63" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G63" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H63" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B64" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C64" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D64" t="str">
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F64" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G64" t="str">
-        <v>0</v>
-      </c>
-      <c r="H64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B65" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
@@ -5156,7 +5453,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="F65" t="str">
         <v>2.8</v>
@@ -5170,10 +5467,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B66" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -5182,13 +5479,13 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F66" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G66" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -5196,10 +5493,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B67" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
@@ -5208,13 +5505,13 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="F67" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="G67" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5222,10 +5519,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B68" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -5234,24 +5531,24 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="F68" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="G68" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B69" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
@@ -5260,13 +5557,13 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="F69" t="str">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="G69" t="str">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -5274,10 +5571,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B70" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
@@ -5286,13 +5583,13 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F70" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G70" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -5300,10 +5597,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B71" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
@@ -5312,13 +5609,13 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -5326,10 +5623,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B72" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
@@ -5338,13 +5635,13 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F72" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G72" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -5352,36 +5649,36 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B73" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C73" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D73" t="str">
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>9</v>
+        <v>11.25</v>
       </c>
       <c r="F73" t="str">
-        <v>9</v>
+        <v>11.25</v>
       </c>
       <c r="G73" t="str">
-        <v>0</v>
+        <v>11.25</v>
       </c>
       <c r="H73" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B74" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
@@ -5390,13 +5687,13 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="F74" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G74" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5404,10 +5701,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B75" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
@@ -5416,13 +5713,13 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F75" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G75" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5430,10 +5727,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B76" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
@@ -5442,13 +5739,13 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F76" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G76" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -5456,10 +5753,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B77" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
@@ -5468,24 +5765,24 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F77" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G77" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B78" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
@@ -5494,50 +5791,50 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F78" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G78" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H78" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B79" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C79" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D79" t="str">
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F79" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G79" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B80" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
@@ -5546,21 +5843,21 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F80" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G80" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H80" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B81" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -5586,7 +5883,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B82" t="str">
         <v>Gabillard (NL), Donna</v>
@@ -5612,10 +5909,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B83" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
@@ -5624,13 +5921,13 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="F83" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="G83" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5638,7 +5935,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B84" t="str">
         <v>Hussain (NL) (GH), Mustansar</v>
@@ -5664,7 +5961,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B85" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
@@ -5688,15 +5985,15 @@
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B86" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
       <c r="C86" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D86" t="str">
         <v/>
@@ -5705,47 +6002,49 @@
         <v>4.8</v>
       </c>
       <c r="F86" t="str">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="G86" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H86" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. _x000d_
+_x000d_
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B87" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C87" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D87" t="str">
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="F87" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G87" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H87" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B88" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
@@ -5754,13 +6053,13 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F88" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G88" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5768,10 +6067,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B89" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C89" t="str">
         <v>Available</v>
@@ -5780,13 +6079,13 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F89" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G89" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5794,10 +6093,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B90" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C90" t="str">
         <v>Available</v>
@@ -5806,24 +6105,24 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F90" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G90" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H90" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B91" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
@@ -5832,13 +6131,13 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="F91" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="G91" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5846,10 +6145,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B92" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C92" t="str">
         <v>Available</v>
@@ -5858,13 +6157,13 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F92" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G92" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -5872,10 +6171,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B93" t="str">
-        <v>Ferris, Marykate</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C93" t="str">
         <v>Available</v>
@@ -5884,13 +6183,13 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="F93" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="G93" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5898,10 +6197,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B94" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C94" t="str">
         <v>Available</v>
@@ -5924,10 +6223,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B95" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C95" t="str">
         <v>Available</v>
@@ -5950,36 +6249,36 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B96" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C96" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D96" t="str">
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F96" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G96" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B97" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C97" t="str">
         <v>Available</v>
@@ -5988,13 +6287,13 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="F97" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="G97" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6002,33 +6301,293 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v>6</v>
+      </c>
+      <c r="F98" t="str">
+        <v>6</v>
+      </c>
+      <c r="G98" t="str">
+        <v>6</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F99" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G99" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B100" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>10</v>
+      </c>
+      <c r="F101" t="str">
+        <v>10</v>
+      </c>
+      <c r="G101" t="str">
+        <v>10</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>2025-08-31</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B102" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>6</v>
+      </c>
+      <c r="F104" t="str">
+        <v>6</v>
+      </c>
+      <c r="G104" t="str">
+        <v>6</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>4</v>
+      </c>
+      <c r="F106" t="str">
+        <v>4</v>
+      </c>
+      <c r="G106" t="str">
+        <v>4</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B108" t="str">
         <v>Shawcross (NL), Emma</v>
       </c>
-      <c r="C98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D98" t="str">
-        <v/>
-      </c>
-      <c r="E98" t="str">
+      <c r="C108" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
         <v>10</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F108" t="str">
         <v>10</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G108" t="str">
         <v>10</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H108" t="str">
         <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,89 +432,89 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E2" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E3" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B4" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C4" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E4" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E5" t="str">
         <v>Holiday</v>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E6" t="str">
         <v>Holiday</v>
@@ -577,238 +577,238 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B7" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C7" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E7" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E8" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
         <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E9" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
-      <c r="I9" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="B10" t="str">
-        <v>16</v>
-      </c>
-      <c r="C10" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Other Unavailable</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v>2</v>
-      </c>
-      <c r="H10" t="str">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B11" t="str">
-        <v>24</v>
-      </c>
-      <c r="C11" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Other Unavailable</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v>2</v>
-      </c>
-      <c r="H11" t="str">
-        <v>0</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
-      <c r="A12" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B12" t="str">
-        <v>24</v>
-      </c>
-      <c r="C12" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Other Unavailable</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>2</v>
-      </c>
-      <c r="H12" t="str">
-        <v>0</v>
-      </c>
-      <c r="I12" t="str" xml:space="preserve">
+      <c r="I9" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B10" t="str">
         <v>24</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C10" t="str">
         <v>4.8</v>
       </c>
-      <c r="D13" t="str">
+      <c r="D10" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E10" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
         <v>2</v>
       </c>
-      <c r="H13" t="str">
+      <c r="H10" t="str">
         <v>0</v>
       </c>
-      <c r="I13" t="str" xml:space="preserve">
+      <c r="I10" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="B11" t="str">
+        <v>30</v>
+      </c>
+      <c r="C11" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2025-08-25</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Pre-Agreed Appointment</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B12" t="str">
+        <v>16</v>
+      </c>
+      <c r="C12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2025-08-25</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B13" t="str">
+        <v>16</v>
+      </c>
+      <c r="C13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E14" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -822,7 +822,7 @@
         <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
@@ -837,7 +837,7 @@
         <v>3.2</v>
       </c>
       <c r="I15" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -851,7 +851,7 @@
         <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
@@ -866,21 +866,21 @@
         <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
@@ -889,27 +889,27 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B18" t="str">
         <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -918,27 +918,27 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>3.2</v>
+        <v>0.67</v>
       </c>
       <c r="H18" t="str">
-        <v>3.2</v>
+        <v>0.67</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
         <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -947,13 +947,13 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I19" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
@@ -967,7 +967,7 @@
         <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -982,7 +982,7 @@
         <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -996,7 +996,7 @@
         <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1005,13 +1005,13 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1025,7 +1025,7 @@
         <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1040,21 +1040,21 @@
         <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C23" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1063,10 +1063,10 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="H23" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B24" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C24" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
@@ -1092,10 +1092,10 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="H24" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1103,16 +1103,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B25" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C25" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
@@ -1121,10 +1121,10 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="H25" t="str">
-        <v>2.67</v>
+        <v>9.38</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v>9.38</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B27" t="str">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="C27" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
@@ -1179,27 +1179,27 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H27" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B28" t="str">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="C28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1208,27 +1208,27 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B29" t="str">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="C29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
@@ -1237,13 +1237,13 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="30">
@@ -1257,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
@@ -1306,16 +1306,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B32" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C32" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
@@ -1324,27 +1324,27 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I32" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B33" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
@@ -1353,27 +1353,27 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I33" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B34" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
@@ -1382,13 +1382,13 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1402,7 +1402,7 @@
         <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
@@ -1431,7 +1431,7 @@
         <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1451,16 +1451,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B37" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C37" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1469,27 +1469,27 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H37" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B38" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1498,27 +1498,27 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B39" t="str">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C39" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1527,10 +1527,10 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="H39" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B40" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1556,27 +1556,27 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I40" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B41" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1585,13 +1585,13 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I41" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1605,7 +1605,7 @@
         <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1625,13 +1625,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B43" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="str">
         <v>2025-08-27</v>
@@ -1643,10 +1643,10 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1654,13 +1654,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B44" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D44" t="str">
         <v>2025-08-28</v>
@@ -1672,10 +1672,10 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1683,13 +1683,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B45" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="str">
         <v>2025-08-29</v>
@@ -1701,10 +1701,10 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
@@ -1741,16 +1741,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B47" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C47" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1759,10 +1759,10 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="H47" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1770,16 +1770,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B48" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C48" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1788,10 +1788,10 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="H48" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1799,13 +1799,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B49" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C49" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="D49" t="str">
         <v>2025-08-31</v>
@@ -1817,10 +1817,10 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="H49" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B50" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C50" t="str">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1846,10 +1846,10 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H50" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1857,16 +1857,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B51" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C51" t="str">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1875,10 +1875,10 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H51" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1886,16 +1886,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B52" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C52" t="str">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1904,10 +1904,10 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1924,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1953,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1973,16 +1973,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B55" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -2002,16 +2002,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B56" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C56" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
@@ -2020,10 +2020,10 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H56" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2031,13 +2031,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B57" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C57" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D57" t="str">
         <v>2025-08-30</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H57" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2069,7 +2069,7 @@
         <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
@@ -2078,10 +2078,10 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B59" t="str">
         <v>30</v>
@@ -2098,7 +2098,7 @@
         <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B60" t="str">
         <v>30</v>
@@ -2127,7 +2127,7 @@
         <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
@@ -2156,7 +2156,7 @@
         <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2185,7 +2185,7 @@
         <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2205,13 +2205,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B63" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C63" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="D63" t="str">
         <v>2025-08-26</v>
@@ -2223,10 +2223,10 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="H63" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B64" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C64" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2252,10 +2252,10 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="H64" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B65" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C65" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2281,10 +2281,10 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="H65" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>11.25</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B67" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
@@ -2339,10 +2339,10 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B68" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
@@ -2368,10 +2368,10 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B69" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
@@ -2397,10 +2397,10 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
@@ -2446,7 +2446,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B72" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
@@ -2484,27 +2484,27 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B73" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
@@ -2513,27 +2513,27 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B74" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
@@ -2542,13 +2542,13 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="75">
@@ -2562,7 +2562,7 @@
         <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
@@ -2591,7 +2591,7 @@
         <v>3.2</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
@@ -2629,27 +2629,27 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
@@ -2658,27 +2658,27 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B79" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
@@ -2687,13 +2687,13 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I79" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2707,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
@@ -2736,7 +2736,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
@@ -2756,16 +2756,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
@@ -2774,10 +2774,10 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B83" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
@@ -2803,10 +2803,10 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2814,13 +2814,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B84" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C84" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D84" t="str">
         <v>2025-08-31</v>
@@ -2832,10 +2832,10 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H84" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2843,16 +2843,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B85" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C85" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E85" t="str">
         <v>Available</v>
@@ -2861,10 +2861,10 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H85" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2872,16 +2872,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B86" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C86" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E86" t="str">
         <v>Available</v>
@@ -2890,10 +2890,10 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H86" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2901,16 +2901,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B87" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C87" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E87" t="str">
         <v>Available</v>
@@ -2919,10 +2919,10 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H87" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2930,16 +2930,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B88" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C88" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E88" t="str">
         <v>Available</v>
@@ -2948,27 +2948,27 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I88" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B89" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C89" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E89" t="str">
         <v>Available</v>
@@ -2977,10 +2977,10 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H89" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -2988,16 +2988,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B90" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C90" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E90" t="str">
         <v>Available</v>
@@ -3006,10 +3006,10 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H90" t="str">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B91" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C91" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E91" t="str">
         <v>Available</v>
@@ -3035,10 +3035,10 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H91" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3046,16 +3046,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B92" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C92" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E92" t="str">
         <v>Available</v>
@@ -3064,10 +3064,10 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H92" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3075,16 +3075,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B93" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C93" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="D93" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E93" t="str">
         <v>Available</v>
@@ -3093,10 +3093,10 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H93" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B94" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C94" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="D94" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E94" t="str">
         <v>Available</v>
@@ -3122,10 +3122,10 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H94" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3133,16 +3133,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B95" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E95" t="str">
         <v>Available</v>
@@ -3151,10 +3151,10 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B96" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D96" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E96" t="str">
         <v>Available</v>
@@ -3180,10 +3180,10 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3191,16 +3191,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B97" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D97" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E97" t="str">
         <v>Available</v>
@@ -3209,10 +3209,10 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3220,16 +3220,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B98" t="str">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="D98" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E98" t="str">
         <v>Available</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3249,291 +3249,59 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B99" t="str">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C99" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="D99" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>6</v>
+      </c>
+      <c r="H99" t="str">
+        <v>6</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B100" t="str">
+        <v>16</v>
+      </c>
+      <c r="C100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D100" t="str">
         <v>2025-08-26</v>
       </c>
-      <c r="E99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H99" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B100" t="str">
-        <v>24</v>
-      </c>
-      <c r="C100" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2025-08-27</v>
-      </c>
       <c r="E100" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="F100" t="str">
         <v/>
       </c>
       <c r="G100" t="str">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="H100" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B101" t="str">
-        <v>24</v>
-      </c>
-      <c r="C101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="E101" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F101" t="str">
-        <v/>
-      </c>
-      <c r="G101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="H101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="I101" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B102" t="str">
-        <v>24</v>
-      </c>
-      <c r="C102" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="E102" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H102" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B103" t="str">
-        <v>30</v>
-      </c>
-      <c r="C103" t="str">
-        <v>6</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="E103" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F103" t="str">
-        <v/>
-      </c>
-      <c r="G103" t="str">
-        <v>6</v>
-      </c>
-      <c r="H103" t="str">
-        <v>6</v>
-      </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B104" t="str">
-        <v>30</v>
-      </c>
-      <c r="C104" t="str">
-        <v>6</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E104" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
-        <v>6</v>
-      </c>
-      <c r="H104" t="str">
-        <v>6</v>
-      </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B105" t="str">
-        <v>30</v>
-      </c>
-      <c r="C105" t="str">
-        <v>6</v>
-      </c>
-      <c r="D105" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v>6</v>
-      </c>
-      <c r="H105" t="str">
-        <v>6</v>
-      </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B106" t="str">
-        <v>30</v>
-      </c>
-      <c r="C106" t="str">
-        <v>6</v>
-      </c>
-      <c r="D106" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="E106" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
-        <v>6</v>
-      </c>
-      <c r="H106" t="str">
-        <v>6</v>
-      </c>
-      <c r="I106" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B107" t="str">
-        <v>30</v>
-      </c>
-      <c r="C107" t="str">
-        <v>6</v>
-      </c>
-      <c r="D107" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="E107" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
-        <v>6</v>
-      </c>
-      <c r="H107" t="str">
-        <v>6</v>
-      </c>
-      <c r="I107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="B108" t="str">
-        <v>16</v>
-      </c>
-      <c r="C108" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="D108" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E108" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="H108" t="str">
         <v>0</v>
       </c>
-      <c r="I108" t="str" xml:space="preserve">
+      <c r="I100" t="str" xml:space="preserve">
         <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
 _x000d_
 Peter_x000d_
@@ -3542,7 +3310,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I100"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3588,7 +3356,7 @@
         <v>50.17</v>
       </c>
       <c r="D2" t="str">
-        <v>10.7</v>
+        <v>7.5</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
@@ -3614,7 +3382,7 @@
         <v>81.8</v>
       </c>
       <c r="D3" t="str">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
         <v>9</v>
@@ -3640,7 +3408,7 @@
         <v>79.47</v>
       </c>
       <c r="D4" t="str">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>9</v>
@@ -3660,10 +3428,10 @@
         <v>2025-08-28</v>
       </c>
       <c r="B5" t="str">
-        <v>84</v>
+        <v>80.8</v>
       </c>
       <c r="C5" t="str">
-        <v>84</v>
+        <v>80.8</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
@@ -3675,7 +3443,7 @@
         <v>96</v>
       </c>
       <c r="G5" t="str">
-        <v>-12</v>
+        <v>-15.2</v>
       </c>
       <c r="H5" t="str">
         <v>Shortage</v>
@@ -3686,10 +3454,10 @@
         <v>2025-08-29</v>
       </c>
       <c r="B6" t="str">
-        <v>75.33</v>
+        <v>72.13</v>
       </c>
       <c r="C6" t="str">
-        <v>75.33</v>
+        <v>72.13</v>
       </c>
       <c r="D6" t="str">
         <v>2</v>
@@ -3701,7 +3469,7 @@
         <v>58</v>
       </c>
       <c r="G6" t="str">
-        <v>17.33</v>
+        <v>14.13</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3768,7 +3536,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3798,7 +3566,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B2" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
@@ -3824,7 +3592,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3850,10 +3618,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B4" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C4" t="str">
         <v>Available</v>
@@ -3862,50 +3630,50 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F4" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G4" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B5" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C5" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B6" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
@@ -3914,13 +3682,13 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3928,10 +3696,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
@@ -3940,13 +3708,13 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -3954,10 +3722,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
@@ -3966,24 +3734,24 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
@@ -3992,13 +3760,13 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="G9" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -4006,36 +3774,36 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B10" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C10" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>7.5</v>
+        <v>9.38</v>
       </c>
       <c r="F10" t="str">
-        <v>7.5</v>
+        <v>9.38</v>
       </c>
       <c r="G10" t="str">
-        <v>0</v>
+        <v>9.38</v>
       </c>
       <c r="H10" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B11" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
@@ -4044,13 +3812,13 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -4058,13 +3826,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B12" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C12" t="str">
-        <v>Sick</v>
+        <v>Available</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -4076,44 +3844,44 @@
         <v>3.2</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B13" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="F13" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
         <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B14" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
@@ -4122,13 +3890,13 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F14" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -4136,10 +3904,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
@@ -4148,24 +3916,24 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="B16" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
@@ -4174,13 +3942,13 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F16" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -4191,7 +3959,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B17" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
@@ -4200,13 +3968,13 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="F17" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="G17" t="str">
-        <v>7.5</v>
+        <v>11.25</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -4217,25 +3985,25 @@
         <v>2025-08-26</v>
       </c>
       <c r="B18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C18" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F18" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
       </c>
     </row>
     <row r="19">
@@ -4243,7 +4011,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B19" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
@@ -4252,495 +4020,497 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F19" t="str">
-        <v>7.5</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="str">
-        <v>7.5</v>
+        <v>0.67</v>
       </c>
       <c r="H19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v>2025-08-26</v>
       </c>
       <c r="B20" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C20" t="str">
-        <v>Holiday</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F20" t="str">
-        <v>9</v>
+        <v>4.75</v>
       </c>
       <c r="G20" t="str">
         <v>0</v>
       </c>
-      <c r="H20" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v>9</v>
-      </c>
-      <c r="F21" t="str">
-        <v>0</v>
-      </c>
-      <c r="G21" t="str">
-        <v>0</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F22" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G22" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F23" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G23" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
-        <v>6</v>
-      </c>
-      <c r="F24" t="str">
-        <v>6</v>
-      </c>
-      <c r="G24" t="str">
-        <v>6</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="F25" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="G25" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
-        <v>6</v>
-      </c>
-      <c r="F26" t="str">
-        <v>6</v>
-      </c>
-      <c r="G26" t="str">
-        <v>6</v>
-      </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Other Unavailable</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F28" t="str">
-        <v>2</v>
-      </c>
-      <c r="G28" t="str">
-        <v>0</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F29" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G29" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F30" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G30" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B31" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Sick</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F31" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G31" t="str">
-        <v>0</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B32" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F32" t="str">
-        <v>0</v>
-      </c>
-      <c r="G32" t="str">
-        <v>0</v>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v>4</v>
-      </c>
-      <c r="F33" t="str">
-        <v>4</v>
-      </c>
-      <c r="G33" t="str">
-        <v>4</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="F34" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="G34" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B35" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Other Unavailable</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F35" t="str">
-        <v>2</v>
-      </c>
-      <c r="G35" t="str">
-        <v>0</v>
-      </c>
-      <c r="H35" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B36" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F36" t="str">
-        <v>0.67</v>
-      </c>
-      <c r="G36" t="str">
-        <v>0.67</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="B37" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F37" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="G37" t="str">
-        <v>0</v>
-      </c>
-      <c r="H37" t="str" xml:space="preserve">
+      <c r="H20" t="str" xml:space="preserve">
         <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
 _x000d_
 Peter_x000d_
 26.8.25, 0827</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>6</v>
+      </c>
+      <c r="F21" t="str">
+        <v>6</v>
+      </c>
+      <c r="G21" t="str">
+        <v>6</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>4</v>
+      </c>
+      <c r="F22" t="str">
+        <v>4</v>
+      </c>
+      <c r="G22" t="str">
+        <v>4</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>9</v>
+      </c>
+      <c r="F24" t="str">
+        <v>9</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>9</v>
+      </c>
+      <c r="F25" t="str">
+        <v>0</v>
+      </c>
+      <c r="G25" t="str">
+        <v>0</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F26" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G26" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>6</v>
+      </c>
+      <c r="F29" t="str">
+        <v>6</v>
+      </c>
+      <c r="G29" t="str">
+        <v>6</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="F30" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="G30" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>6</v>
+      </c>
+      <c r="F31" t="str">
+        <v>6</v>
+      </c>
+      <c r="G31" t="str">
+        <v>6</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F32" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G32" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2</v>
+      </c>
+      <c r="G33" t="str">
+        <v>0</v>
+      </c>
+      <c r="H33" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. _x000d_
+_x000d_
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>4</v>
+      </c>
+      <c r="F35" t="str">
+        <v>4</v>
+      </c>
+      <c r="G35" t="str">
+        <v>4</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>4</v>
+      </c>
+      <c r="F36" t="str">
+        <v>4</v>
+      </c>
+      <c r="G36" t="str">
+        <v>4</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Nafees (NL) (GH), Hamza</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="F37" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="G37" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B38" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
@@ -4749,16 +4519,16 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F38" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G38" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="39">
@@ -4766,7 +4536,7 @@
         <v>2025-08-27</v>
       </c>
       <c r="B39" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
@@ -4775,24 +4545,24 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G39" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B40" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C40" t="str">
         <v>Available</v>
@@ -4801,53 +4571,53 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F40" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G40" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C41" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F41" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G41" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H41" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B42" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C42" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -4856,21 +4626,21 @@
         <v>9</v>
       </c>
       <c r="F42" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G42" t="str">
         <v>0</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B43" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C43" t="str">
         <v>Available</v>
@@ -4879,13 +4649,13 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>6.67</v>
+        <v>9</v>
       </c>
       <c r="F43" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="G43" t="str">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -4893,10 +4663,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B44" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
@@ -4905,13 +4675,13 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F44" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G44" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4919,10 +4689,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B45" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
@@ -4931,13 +4701,13 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F45" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G45" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4945,10 +4715,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B46" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
@@ -4957,13 +4727,13 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F46" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G46" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4971,10 +4741,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B47" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C47" t="str">
         <v>Available</v>
@@ -4983,13 +4753,13 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="F47" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="G47" t="str">
-        <v>9.38</v>
+        <v>6</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -4997,10 +4767,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B48" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
@@ -5009,13 +4779,13 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="F48" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="G48" t="str">
-        <v>6</v>
+        <v>9.38</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -5023,7 +4793,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B49" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
@@ -5047,15 +4817,15 @@
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
+    <row r="50">
       <c r="A50" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B50" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
       <c r="C50" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -5064,439 +4834,439 @@
         <v>4.8</v>
       </c>
       <c r="F50" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="G50" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v>4</v>
+      </c>
+      <c r="F51" t="str">
+        <v>4</v>
+      </c>
+      <c r="G51" t="str">
+        <v>4</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v>4</v>
+      </c>
+      <c r="F52" t="str">
+        <v>4</v>
+      </c>
+      <c r="G52" t="str">
+        <v>4</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Nafees (NL) (GH), Hamza</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="F53" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="G53" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F54" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G54" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B55" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F55" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G55" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v>6</v>
+      </c>
+      <c r="F56" t="str">
+        <v>6</v>
+      </c>
+      <c r="G56" t="str">
+        <v>6</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v>4</v>
+      </c>
+      <c r="F57" t="str">
+        <v>4</v>
+      </c>
+      <c r="G57" t="str">
+        <v>4</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v>9</v>
+      </c>
+      <c r="F59" t="str">
+        <v>9</v>
+      </c>
+      <c r="G59" t="str">
+        <v>0</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v>9</v>
+      </c>
+      <c r="F60" t="str">
+        <v>0</v>
+      </c>
+      <c r="G60" t="str">
+        <v>0</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F62" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G62" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="F63" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="G63" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v>6</v>
+      </c>
+      <c r="F64" t="str">
+        <v>6</v>
+      </c>
+      <c r="G64" t="str">
+        <v>6</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F66" t="str">
         <v>2</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G66" t="str">
         <v>0</v>
       </c>
-      <c r="H50" t="str" xml:space="preserve">
+      <c r="H66" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F51" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G51" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C52" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v>4</v>
-      </c>
-      <c r="F52" t="str">
-        <v>4</v>
-      </c>
-      <c r="G52" t="str">
-        <v>4</v>
-      </c>
-      <c r="H52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B53" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Sick</v>
-      </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F53" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G53" t="str">
-        <v>0</v>
-      </c>
-      <c r="H53" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B54" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F54" t="str">
-        <v>0</v>
-      </c>
-      <c r="G54" t="str">
-        <v>0</v>
-      </c>
-      <c r="H54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
-        <v>4</v>
-      </c>
-      <c r="F55" t="str">
-        <v>4</v>
-      </c>
-      <c r="G55" t="str">
-        <v>4</v>
-      </c>
-      <c r="H55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D56" t="str">
-        <v/>
-      </c>
-      <c r="E56" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="F56" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="G56" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="H56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B57" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F57" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G57" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H57" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B58" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v>6</v>
-      </c>
-      <c r="F58" t="str">
-        <v>6</v>
-      </c>
-      <c r="G58" t="str">
-        <v>6</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B59" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v>4</v>
-      </c>
-      <c r="F59" t="str">
-        <v>4</v>
-      </c>
-      <c r="G59" t="str">
-        <v>4</v>
-      </c>
-      <c r="H59" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B60" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F60" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G60" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B61" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Holiday</v>
-      </c>
-      <c r="D61" t="str">
-        <v/>
-      </c>
-      <c r="E61" t="str">
-        <v>9</v>
-      </c>
-      <c r="F61" t="str">
-        <v>9</v>
-      </c>
-      <c r="G61" t="str">
-        <v>0</v>
-      </c>
-      <c r="H61" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D62" t="str">
-        <v/>
-      </c>
-      <c r="E62" t="str">
-        <v>9</v>
-      </c>
-      <c r="F62" t="str">
-        <v>0</v>
-      </c>
-      <c r="G62" t="str">
-        <v>0</v>
-      </c>
-      <c r="H62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B63" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D63" t="str">
-        <v/>
-      </c>
-      <c r="E63" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F63" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G63" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D64" t="str">
-        <v/>
-      </c>
-      <c r="E64" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F64" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G64" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B65" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D65" t="str">
-        <v/>
-      </c>
-      <c r="E65" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F65" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G65" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B66" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-      <c r="E66" t="str">
-        <v>6</v>
-      </c>
-      <c r="F66" t="str">
-        <v>6</v>
-      </c>
-      <c r="G66" t="str">
-        <v>6</v>
-      </c>
-      <c r="H66" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B67" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
@@ -5505,13 +5275,13 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>9.38</v>
+        <v>4.8</v>
       </c>
       <c r="F67" t="str">
-        <v>9.38</v>
+        <v>2.8</v>
       </c>
       <c r="G67" t="str">
-        <v>9.38</v>
+        <v>2.8</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5519,10 +5289,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B68" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -5531,24 +5301,24 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G68" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H68" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B69" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
@@ -5557,13 +5327,13 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="G69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -5571,10 +5341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B70" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
@@ -5583,13 +5353,13 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="F70" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="G70" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -5597,10 +5367,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
@@ -5609,13 +5379,13 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="F71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="G71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -5623,10 +5393,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B72" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
@@ -5635,13 +5405,13 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F72" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G72" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -5649,10 +5419,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B73" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
@@ -5661,13 +5431,13 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="F73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="G73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -5675,10 +5445,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B74" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
@@ -5687,13 +5457,13 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5701,36 +5471,36 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B75" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C75" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D75" t="str">
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2.67</v>
+        <v>9</v>
       </c>
       <c r="F75" t="str">
-        <v>2.67</v>
+        <v>9</v>
       </c>
       <c r="G75" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B76" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
@@ -5739,13 +5509,13 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F76" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -5753,10 +5523,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B77" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
@@ -5765,24 +5535,24 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B78" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
@@ -5805,36 +5575,36 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B79" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C79" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D79" t="str">
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F79" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="G79" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H79" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B80" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
@@ -5843,24 +5613,24 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F80" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G80" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B81" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
@@ -5869,24 +5639,24 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H81" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B82" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C82" t="str">
         <v>Available</v>
@@ -5895,24 +5665,24 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="F82" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G82" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B83" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
@@ -5921,24 +5691,24 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="F83" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="G83" t="str">
-        <v>9.38</v>
+        <v>3.2</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B84" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C84" t="str">
         <v>Available</v>
@@ -5947,13 +5717,13 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F84" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G84" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H84" t="str">
         <v/>
@@ -5961,10 +5731,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B85" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C85" t="str">
         <v>Available</v>
@@ -5973,52 +5743,50 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F85" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G85" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H85" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B86" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C86" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D86" t="str">
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="F86" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G86" t="str">
-        <v>0</v>
-      </c>
-      <c r="H86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. _x000d_
-_x000d_
-Eilidh 29/05/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B87" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C87" t="str">
         <v>Available</v>
@@ -6027,24 +5795,24 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F87" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G87" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B88" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
@@ -6053,13 +5821,13 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F88" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="G88" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -6067,36 +5835,36 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B89" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C89" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D89" t="str">
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F89" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G89" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B90" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C90" t="str">
         <v>Available</v>
@@ -6105,13 +5873,13 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F90" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G90" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -6119,10 +5887,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B91" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
@@ -6131,13 +5899,13 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>11.25</v>
+        <v>4</v>
       </c>
       <c r="F91" t="str">
-        <v>11.25</v>
+        <v>4</v>
       </c>
       <c r="G91" t="str">
-        <v>11.25</v>
+        <v>4</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -6145,10 +5913,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B92" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C92" t="str">
         <v>Available</v>
@@ -6157,24 +5925,24 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>5.33</v>
+        <v>2.67</v>
       </c>
       <c r="F92" t="str">
-        <v>5.33</v>
+        <v>2.67</v>
       </c>
       <c r="G92" t="str">
-        <v>5.33</v>
+        <v>2.67</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B93" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C93" t="str">
         <v>Available</v>
@@ -6183,13 +5951,13 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F93" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G93" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -6197,10 +5965,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B94" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C94" t="str">
         <v>Available</v>
@@ -6209,13 +5977,13 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -6223,10 +5991,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B95" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C95" t="str">
         <v>Available</v>
@@ -6235,13 +6003,13 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="F95" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="G95" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -6249,36 +6017,36 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B96" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C96" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D96" t="str">
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F96" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G96" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H96" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B97" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C97" t="str">
         <v>Available</v>
@@ -6287,13 +6055,13 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F97" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G97" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6301,10 +6069,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B98" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C98" t="str">
         <v>Available</v>
@@ -6313,13 +6081,13 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F98" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G98" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -6327,10 +6095,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B99" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C99" t="str">
         <v>Available</v>
@@ -6339,13 +6107,13 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F99" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G99" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -6353,10 +6121,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="B100" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C100" t="str">
         <v>Available</v>
@@ -6365,229 +6133,21 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F100" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="G100" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="H100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Shawcross (NL), Emma</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
-      <c r="E101" t="str">
-        <v>10</v>
-      </c>
-      <c r="F101" t="str">
-        <v>10</v>
-      </c>
-      <c r="G101" t="str">
-        <v>10</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D104" t="str">
-        <v/>
-      </c>
-      <c r="E104" t="str">
-        <v>6</v>
-      </c>
-      <c r="F104" t="str">
-        <v>6</v>
-      </c>
-      <c r="G104" t="str">
-        <v>6</v>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
-        <v>4</v>
-      </c>
-      <c r="F106" t="str">
-        <v>4</v>
-      </c>
-      <c r="G106" t="str">
-        <v>4</v>
-      </c>
-      <c r="H106" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Shawcross (NL), Emma</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v>10</v>
-      </c>
-      <c r="F108" t="str">
-        <v>10</v>
-      </c>
-      <c r="G108" t="str">
-        <v>10</v>
-      </c>
-      <c r="H108" t="str">
         <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,89 +432,89 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B2" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C2" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E2" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B3" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E3" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B4" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C4" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E4" t="str">
-        <v>Holiday</v>
+        <v>Sick</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E5" t="str">
         <v>Holiday</v>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E6" t="str">
         <v>Holiday</v>
@@ -577,238 +577,238 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B7" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C7" t="str">
-        <v>2.67</v>
+        <v>9</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B8" t="str">
+        <v>45</v>
+      </c>
+      <c r="C8" t="str">
+        <v>9</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>9</v>
+      </c>
+      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B9" t="str">
+        <v>45</v>
+      </c>
+      <c r="C9" t="str">
+        <v>9</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>9</v>
+      </c>
+      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B10" t="str">
+        <v>16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>2</v>
+      </c>
+      <c r="H10" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B11" t="str">
         <v>24</v>
       </c>
-      <c r="C8" t="str">
+      <c r="C11" t="str">
         <v>4.8</v>
       </c>
-      <c r="D8" t="str">
+      <c r="D11" t="str">
         <v>2025-08-26</v>
       </c>
-      <c r="E8" t="str">
+      <c r="E11" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
         <v>2</v>
       </c>
-      <c r="H8" t="str">
-        <v>0</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
         <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
-      <c r="A9" t="str">
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B12" t="str">
         <v>24</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C12" t="str">
         <v>4.8</v>
       </c>
-      <c r="D9" t="str">
+      <c r="D12" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="E9" t="str">
+      <c r="E12" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>2</v>
       </c>
-      <c r="H9" t="str">
-        <v>0</v>
-      </c>
-      <c r="I9" t="str" xml:space="preserve">
+      <c r="H12" t="str">
+        <v>0</v>
+      </c>
+      <c r="I12" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B13" t="str">
         <v>24</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C13" t="str">
         <v>4.8</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D13" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E13" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>2</v>
       </c>
-      <c r="H10" t="str">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str" xml:space="preserve">
+      <c r="H13" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="B11" t="str">
-        <v>30</v>
-      </c>
-      <c r="C11" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Pre-Agreed Appointment</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H11" t="str">
-        <v>0</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="B12" t="str">
-        <v>16</v>
-      </c>
-      <c r="C12" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H12" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="B13" t="str">
-        <v>16</v>
-      </c>
-      <c r="C13" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H13" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B14" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C14" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E14" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="15">
@@ -822,7 +822,7 @@
         <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
@@ -837,7 +837,7 @@
         <v>3.2</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="16">
@@ -851,7 +851,7 @@
         <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
@@ -866,21 +866,21 @@
         <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
@@ -889,27 +889,27 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B18" t="str">
         <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -918,27 +918,27 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>0.67</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="str">
-        <v>0.67</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B19" t="str">
         <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -947,13 +947,13 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="20">
@@ -967,7 +967,7 @@
         <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -982,7 +982,7 @@
         <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
@@ -996,7 +996,7 @@
         <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1005,13 +1005,13 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="H21" t="str">
-        <v>2.67</v>
+        <v>0.67</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="22">
@@ -1025,7 +1025,7 @@
         <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1040,21 +1040,21 @@
         <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1063,10 +1063,10 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1074,16 +1074,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B24" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
@@ -1092,10 +1092,10 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H24" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1103,16 +1103,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B25" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
@@ -1121,10 +1121,10 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H25" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v>9.38</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
@@ -1161,16 +1161,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B27" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
@@ -1179,27 +1179,27 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H27" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I27" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B28" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1208,27 +1208,27 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H28" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I28" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B29" t="str">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="C29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
@@ -1237,13 +1237,13 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="H29" t="str">
-        <v>4</v>
+        <v>9.38</v>
       </c>
       <c r="I29" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1257,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
@@ -1306,16 +1306,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B32" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
@@ -1324,27 +1324,27 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B33" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
@@ -1353,27 +1353,27 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B34" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
@@ -1382,13 +1382,13 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="35">
@@ -1402,7 +1402,7 @@
         <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
@@ -1431,7 +1431,7 @@
         <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1451,16 +1451,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1469,27 +1469,27 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B38" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1498,27 +1498,27 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B39" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1527,10 +1527,10 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1538,16 +1538,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B40" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1556,27 +1556,27 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B41" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1585,13 +1585,13 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="42">
@@ -1605,7 +1605,7 @@
         <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1625,13 +1625,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B43" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D43" t="str">
         <v>2025-08-27</v>
@@ -1643,10 +1643,10 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1654,13 +1654,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B44" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D44" t="str">
         <v>2025-08-28</v>
@@ -1672,10 +1672,10 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1683,13 +1683,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B45" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D45" t="str">
         <v>2025-08-29</v>
@@ -1701,10 +1701,10 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1721,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
@@ -1741,16 +1741,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B47" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1759,10 +1759,10 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H47" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1770,16 +1770,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B48" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1788,10 +1788,10 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1799,13 +1799,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B49" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C49" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D49" t="str">
         <v>2025-08-31</v>
@@ -1817,10 +1817,10 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B50" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C50" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1846,10 +1846,10 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H50" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1857,16 +1857,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B51" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1875,10 +1875,10 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H51" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1886,16 +1886,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B52" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1904,10 +1904,10 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H52" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1924,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1953,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1973,16 +1973,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B55" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C55" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -2002,16 +2002,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B56" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C56" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
@@ -2020,10 +2020,10 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2031,13 +2031,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B57" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C57" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D57" t="str">
         <v>2025-08-30</v>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2069,7 +2069,7 @@
         <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
@@ -2078,10 +2078,10 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H58" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B59" t="str">
         <v>30</v>
@@ -2098,7 +2098,7 @@
         <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B60" t="str">
         <v>30</v>
@@ -2127,7 +2127,7 @@
         <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
@@ -2147,7 +2147,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
@@ -2156,7 +2156,7 @@
         <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2185,7 +2185,7 @@
         <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2205,13 +2205,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B63" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D63" t="str">
         <v>2025-08-26</v>
@@ -2223,10 +2223,10 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H63" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2234,16 +2234,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B64" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2252,10 +2252,10 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H64" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B65" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2281,10 +2281,10 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H65" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>11.25</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B67" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
@@ -2339,10 +2339,10 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H67" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B68" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
@@ -2368,10 +2368,10 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H68" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="B69" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
@@ -2397,10 +2397,10 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H69" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
@@ -2446,7 +2446,7 @@
         <v>6</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-08-30</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B72" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
@@ -2484,27 +2484,27 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B73" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
@@ -2513,27 +2513,27 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I73" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B74" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-30</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
@@ -2542,13 +2542,13 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -2562,7 +2562,7 @@
         <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
@@ -2591,7 +2591,7 @@
         <v>3.2</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B77" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
@@ -2629,27 +2629,27 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B78" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
@@ -2658,27 +2658,27 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B79" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
@@ -2687,13 +2687,13 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H79" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="80">
@@ -2707,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
@@ -2736,7 +2736,7 @@
         <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
@@ -2756,16 +2756,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B82" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
@@ -2774,10 +2774,10 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B83" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
@@ -2803,10 +2803,10 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2814,13 +2814,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B84" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C84" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D84" t="str">
         <v>2025-08-31</v>
@@ -2832,10 +2832,10 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H84" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -2843,16 +2843,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B85" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E85" t="str">
         <v>Available</v>
@@ -2861,10 +2861,10 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H85" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2872,16 +2872,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B86" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E86" t="str">
         <v>Available</v>
@@ -2890,10 +2890,10 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H86" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2901,16 +2901,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B87" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-31</v>
       </c>
       <c r="E87" t="str">
         <v>Available</v>
@@ -2919,10 +2919,10 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H87" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2930,16 +2930,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B88" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C88" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E88" t="str">
         <v>Available</v>
@@ -2948,27 +2948,27 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B89" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C89" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E89" t="str">
         <v>Available</v>
@@ -2977,10 +2977,10 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H89" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -2988,16 +2988,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B90" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C90" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E90" t="str">
         <v>Available</v>
@@ -3006,10 +3006,10 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H90" t="str">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B91" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C91" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E91" t="str">
         <v>Available</v>
@@ -3035,10 +3035,10 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H91" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3046,16 +3046,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B92" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C92" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E92" t="str">
         <v>Available</v>
@@ -3064,10 +3064,10 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H92" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3075,16 +3075,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B93" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C93" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D93" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E93" t="str">
         <v>Available</v>
@@ -3093,10 +3093,10 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H93" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B94" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C94" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="D94" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-26</v>
       </c>
       <c r="E94" t="str">
         <v>Available</v>
@@ -3122,10 +3122,10 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H94" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3133,16 +3133,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B95" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-27</v>
       </c>
       <c r="E95" t="str">
         <v>Available</v>
@@ -3151,10 +3151,10 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H95" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B96" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D96" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-28</v>
       </c>
       <c r="E96" t="str">
         <v>Available</v>
@@ -3180,10 +3180,10 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H96" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3191,16 +3191,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B97" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D97" t="str">
-        <v>2025-08-27</v>
+        <v>2025-08-29</v>
       </c>
       <c r="E97" t="str">
         <v>Available</v>
@@ -3209,10 +3209,10 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H97" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3220,16 +3220,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B98" t="str">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C98" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="D98" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-25</v>
       </c>
       <c r="E98" t="str">
         <v>Available</v>
@@ -3238,10 +3238,10 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H98" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3249,59 +3249,291 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B99" t="str">
+        <v>24</v>
+      </c>
+      <c r="C99" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H99" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B100" t="str">
+        <v>24</v>
+      </c>
+      <c r="C100" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H100" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B101" t="str">
+        <v>24</v>
+      </c>
+      <c r="C101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H101" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B102" t="str">
+        <v>24</v>
+      </c>
+      <c r="C102" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H102" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="B99" t="str">
+      <c r="B103" t="str">
         <v>30</v>
       </c>
-      <c r="C99" t="str">
-        <v>6</v>
-      </c>
-      <c r="D99" t="str">
+      <c r="C103" t="str">
+        <v>6</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2025-08-25</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>6</v>
+      </c>
+      <c r="H103" t="str">
+        <v>6</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B104" t="str">
+        <v>30</v>
+      </c>
+      <c r="C104" t="str">
+        <v>6</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>6</v>
+      </c>
+      <c r="H104" t="str">
+        <v>6</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B105" t="str">
+        <v>30</v>
+      </c>
+      <c r="C105" t="str">
+        <v>6</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2025-08-27</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>6</v>
+      </c>
+      <c r="H105" t="str">
+        <v>6</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B106" t="str">
+        <v>30</v>
+      </c>
+      <c r="C106" t="str">
+        <v>6</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>6</v>
+      </c>
+      <c r="H106" t="str">
+        <v>6</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B107" t="str">
+        <v>30</v>
+      </c>
+      <c r="C107" t="str">
+        <v>6</v>
+      </c>
+      <c r="D107" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="E99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99" t="str">
-        <v>6</v>
-      </c>
-      <c r="H99" t="str">
-        <v>6</v>
-      </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100" t="str">
+      <c r="E107" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>6</v>
+      </c>
+      <c r="H107" t="str">
+        <v>6</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B108" t="str">
         <v>16</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C108" t="str">
         <v>2.67</v>
       </c>
-      <c r="D100" t="str">
+      <c r="D108" t="str">
         <v>2025-08-26</v>
       </c>
-      <c r="E100" t="str">
+      <c r="E108" t="str">
         <v>Dependant Leave</v>
       </c>
-      <c r="F100" t="str">
-        <v/>
-      </c>
-      <c r="G100" t="str">
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
         <v>4.75</v>
       </c>
-      <c r="H100" t="str">
-        <v>0</v>
-      </c>
-      <c r="I100" t="str" xml:space="preserve">
+      <c r="H108" t="str">
+        <v>0</v>
+      </c>
+      <c r="I108" t="str" xml:space="preserve">
         <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
 _x000d_
 Peter_x000d_
@@ -3310,7 +3542,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3356,7 +3588,7 @@
         <v>50.17</v>
       </c>
       <c r="D2" t="str">
-        <v>7.5</v>
+        <v>10.7</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
@@ -3382,7 +3614,7 @@
         <v>81.8</v>
       </c>
       <c r="D3" t="str">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="E3" t="str">
         <v>9</v>
@@ -3408,7 +3640,7 @@
         <v>79.47</v>
       </c>
       <c r="D4" t="str">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="E4" t="str">
         <v>9</v>
@@ -3428,10 +3660,10 @@
         <v>2025-08-28</v>
       </c>
       <c r="B5" t="str">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="C5" t="str">
-        <v>80.8</v>
+        <v>84</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
@@ -3443,7 +3675,7 @@
         <v>96</v>
       </c>
       <c r="G5" t="str">
-        <v>-15.2</v>
+        <v>-12</v>
       </c>
       <c r="H5" t="str">
         <v>Shortage</v>
@@ -3454,10 +3686,10 @@
         <v>2025-08-29</v>
       </c>
       <c r="B6" t="str">
-        <v>72.13</v>
+        <v>75.33</v>
       </c>
       <c r="C6" t="str">
-        <v>72.13</v>
+        <v>75.33</v>
       </c>
       <c r="D6" t="str">
         <v>2</v>
@@ -3469,7 +3701,7 @@
         <v>58</v>
       </c>
       <c r="G6" t="str">
-        <v>14.13</v>
+        <v>17.33</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3536,7 +3768,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H108"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3566,7 +3798,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B2" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
@@ -3592,7 +3824,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3618,10 +3850,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B4" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C4" t="str">
         <v>Available</v>
@@ -3630,50 +3862,50 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B5" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C5" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B6" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
@@ -3682,13 +3914,13 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3696,10 +3928,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
@@ -3708,13 +3940,13 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -3722,10 +3954,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B8" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
@@ -3734,24 +3966,24 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B9" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
@@ -3760,13 +3992,13 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="G9" t="str">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -3774,36 +4006,36 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B10" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C10" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="F10" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="G10" t="str">
-        <v>9.38</v>
+        <v>0</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B11" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
@@ -3812,13 +4044,13 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F11" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -3826,13 +4058,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B12" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Sick</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -3844,44 +4076,44 @@
         <v>3.2</v>
       </c>
       <c r="G12" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C13" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F13" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="str">
         <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B14" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
@@ -3890,13 +4122,13 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F14" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G14" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3904,10 +4136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B15" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
@@ -3916,24 +4148,24 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G15" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-08-26</v>
+        <v>2025-08-25</v>
       </c>
       <c r="B16" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
@@ -3942,13 +4174,13 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3959,7 +4191,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B17" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
@@ -3968,13 +4200,13 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="G17" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3985,25 +4217,25 @@
         <v>2025-08-26</v>
       </c>
       <c r="B18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C18" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F18" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="19">
@@ -4011,7 +4243,7 @@
         <v>2025-08-26</v>
       </c>
       <c r="B19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
@@ -4020,835 +4252,835 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="str">
-        <v>0.67</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="str">
-        <v>0.67</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="str">
         <v>2025-08-26</v>
       </c>
       <c r="B20" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>9</v>
+      </c>
+      <c r="F20" t="str">
+        <v>9</v>
+      </c>
+      <c r="G20" t="str">
+        <v>0</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>9</v>
+      </c>
+      <c r="F21" t="str">
+        <v>0</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>6</v>
+      </c>
+      <c r="F24" t="str">
+        <v>6</v>
+      </c>
+      <c r="G24" t="str">
+        <v>6</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="F25" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="G25" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>6</v>
+      </c>
+      <c r="F26" t="str">
+        <v>6</v>
+      </c>
+      <c r="G26" t="str">
+        <v>6</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G27" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2</v>
+      </c>
+      <c r="G28" t="str">
+        <v>0</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F30" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G30" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B31" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F31" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B32" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F32" t="str">
+        <v>0</v>
+      </c>
+      <c r="G32" t="str">
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>4</v>
+      </c>
+      <c r="F33" t="str">
+        <v>4</v>
+      </c>
+      <c r="G33" t="str">
+        <v>4</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Nafees (NL) (GH), Hamza</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="F34" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="G34" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B35" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C35" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2</v>
+      </c>
+      <c r="G35" t="str">
+        <v>0</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B36" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F36" t="str">
+        <v>0.67</v>
+      </c>
+      <c r="G36" t="str">
+        <v>0.67</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>2025-08-26</v>
+      </c>
+      <c r="B37" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C37" t="str">
         <v>Dependant Leave</v>
       </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
         <v>2.67</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F37" t="str">
         <v>4.75</v>
       </c>
-      <c r="G20" t="str">
-        <v>0</v>
-      </c>
-      <c r="H20" t="str" xml:space="preserve">
+      <c r="G37" t="str">
+        <v>0</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
         <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
 _x000d_
 Peter_x000d_
 26.8.25, 0827</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
+    <row r="38">
+      <c r="A38" t="str">
         <v>2025-08-26</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B38" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="C21" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D21" t="str">
-        <v/>
-      </c>
-      <c r="E21" t="str">
-        <v>6</v>
-      </c>
-      <c r="F21" t="str">
-        <v>6</v>
-      </c>
-      <c r="G21" t="str">
-        <v>6</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
+      <c r="C38" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>6</v>
+      </c>
+      <c r="F38" t="str">
+        <v>6</v>
+      </c>
+      <c r="G38" t="str">
+        <v>6</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B39" t="str">
         <v>Asokhia (NL), Deborah</v>
       </c>
-      <c r="C22" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v>4</v>
-      </c>
-      <c r="F22" t="str">
-        <v>4</v>
-      </c>
-      <c r="G22" t="str">
-        <v>4</v>
-      </c>
-      <c r="H22" t="str">
+      <c r="C39" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v>4</v>
+      </c>
+      <c r="F39" t="str">
+        <v>4</v>
+      </c>
+      <c r="G39" t="str">
+        <v>4</v>
+      </c>
+      <c r="H39" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
+    <row r="40">
+      <c r="A40" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B40" t="str">
         <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
-      <c r="C23" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-      <c r="E23" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F23" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G23" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
+      <c r="C40" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B41" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C41" t="str">
         <v>Holiday</v>
       </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-      <c r="E24" t="str">
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
         <v>9</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F41" t="str">
         <v>9</v>
       </c>
-      <c r="G24" t="str">
-        <v>0</v>
-      </c>
-      <c r="H24" t="str">
+      <c r="G41" t="str">
+        <v>0</v>
+      </c>
+      <c r="H41" t="str">
         <v>Created by new vacation process.</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="str">
+    <row r="42">
+      <c r="A42" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B42" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
-      <c r="C25" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
-      </c>
-      <c r="E25" t="str">
+      <c r="C42" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
         <v>9</v>
       </c>
-      <c r="F25" t="str">
-        <v>0</v>
-      </c>
-      <c r="G25" t="str">
-        <v>0</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
+      <c r="F42" t="str">
+        <v>0</v>
+      </c>
+      <c r="G42" t="str">
+        <v>0</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B43" t="str">
         <v>Ferris, Marykate</v>
       </c>
-      <c r="C26" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
-      </c>
-      <c r="E26" t="str">
+      <c r="C43" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
         <v>6.67</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F43" t="str">
         <v>6.67</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G43" t="str">
         <v>6.67</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B44" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
       </c>
-      <c r="C27" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D27" t="str">
-        <v/>
-      </c>
-      <c r="E27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G27" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
+      <c r="C44" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F44" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G44" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B45" t="str">
         <v>Gabillard (NL), Donna</v>
       </c>
-      <c r="C28" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
+      <c r="C45" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
         <v>2.8</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F45" t="str">
         <v>2.8</v>
       </c>
-      <c r="G28" t="str">
+      <c r="G45" t="str">
         <v>2.8</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B46" t="str">
         <v>Griffiths (NL), Wayne (GH)</v>
       </c>
-      <c r="C29" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v>6</v>
-      </c>
-      <c r="F29" t="str">
-        <v>6</v>
-      </c>
-      <c r="G29" t="str">
-        <v>6</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
+      <c r="C46" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v>6</v>
+      </c>
+      <c r="F46" t="str">
+        <v>6</v>
+      </c>
+      <c r="G46" t="str">
+        <v>6</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B47" t="str">
         <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
-      <c r="C30" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
+      <c r="C47" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
         <v>9.38</v>
       </c>
-      <c r="F30" t="str">
+      <c r="F47" t="str">
         <v>9.38</v>
       </c>
-      <c r="G30" t="str">
+      <c r="G47" t="str">
         <v>9.38</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B48" t="str">
         <v>Hussain (NL) (GH), Mustansar</v>
       </c>
-      <c r="C31" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v>6</v>
-      </c>
-      <c r="F31" t="str">
-        <v>6</v>
-      </c>
-      <c r="G31" t="str">
-        <v>6</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
+      <c r="C48" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v>6</v>
+      </c>
+      <c r="F48" t="str">
+        <v>6</v>
+      </c>
+      <c r="G48" t="str">
+        <v>6</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B49" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
-      <c r="C32" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F32" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G32" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H32" t="str">
+      <c r="C49" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F49" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G49" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H49" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str">
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
         <v>2025-08-27</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B50" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C50" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
         <v>4.8</v>
       </c>
-      <c r="F33" t="str">
+      <c r="F50" t="str">
         <v>2</v>
       </c>
-      <c r="G33" t="str">
-        <v>0</v>
-      </c>
-      <c r="H33" t="str" xml:space="preserve">
+      <c r="G50" t="str">
+        <v>0</v>
+      </c>
+      <c r="H50" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F34" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G34" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v>4</v>
-      </c>
-      <c r="F35" t="str">
-        <v>4</v>
-      </c>
-      <c r="G35" t="str">
-        <v>4</v>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D36" t="str">
-        <v/>
-      </c>
-      <c r="E36" t="str">
-        <v>4</v>
-      </c>
-      <c r="F36" t="str">
-        <v>4</v>
-      </c>
-      <c r="G36" t="str">
-        <v>4</v>
-      </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D37" t="str">
-        <v/>
-      </c>
-      <c r="E37" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="F37" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="G37" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="H37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B38" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F38" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G38" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H38" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v>6</v>
-      </c>
-      <c r="F39" t="str">
-        <v>6</v>
-      </c>
-      <c r="G39" t="str">
-        <v>6</v>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B40" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
-      </c>
-      <c r="E40" t="str">
-        <v>4</v>
-      </c>
-      <c r="F40" t="str">
-        <v>4</v>
-      </c>
-      <c r="G40" t="str">
-        <v>4</v>
-      </c>
-      <c r="H40" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B41" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F41" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G41" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Holiday</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v>9</v>
-      </c>
-      <c r="F42" t="str">
-        <v>9</v>
-      </c>
-      <c r="G42" t="str">
-        <v>0</v>
-      </c>
-      <c r="H42" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v>9</v>
-      </c>
-      <c r="F43" t="str">
-        <v>0</v>
-      </c>
-      <c r="G43" t="str">
-        <v>0</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F44" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G44" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F45" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G45" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F46" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G46" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C47" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D47" t="str">
-        <v/>
-      </c>
-      <c r="E47" t="str">
-        <v>6</v>
-      </c>
-      <c r="F47" t="str">
-        <v>6</v>
-      </c>
-      <c r="G47" t="str">
-        <v>6</v>
-      </c>
-      <c r="H47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
-      </c>
-      <c r="C48" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="F48" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="G48" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="H48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D49" t="str">
-        <v/>
-      </c>
-      <c r="E49" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F49" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G49" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D50" t="str">
-        <v/>
-      </c>
-      <c r="E50" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F50" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="G50" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="H50" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B51" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
@@ -4857,13 +5089,13 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="F51" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G51" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="str">
         <v/>
@@ -4871,10 +5103,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B52" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
@@ -4897,36 +5129,36 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B53" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C53" t="str">
-        <v>Available</v>
+        <v>Sick</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="F53" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="G53" t="str">
-        <v>11.25</v>
+        <v>0</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B54" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
@@ -4935,13 +5167,13 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="F54" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="G54" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -4949,10 +5181,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B55" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
@@ -4961,13 +5193,13 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F55" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G55" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4975,10 +5207,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-08-28</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B56" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
@@ -4987,13 +5219,13 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="F56" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="G56" t="str">
-        <v>6</v>
+        <v>11.25</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -5001,10 +5233,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B57" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -5013,24 +5245,24 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F57" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G57" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H57" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-27</v>
       </c>
       <c r="B58" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
@@ -5039,13 +5271,13 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F58" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -5053,36 +5285,36 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B59" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C59" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D59" t="str">
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F59" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G59" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B60" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
@@ -5091,13 +5323,13 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F60" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G60" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -5105,36 +5337,36 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B61" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C61" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F61" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="G61" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H61" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B62" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C62" t="str">
         <v>Available</v>
@@ -5143,13 +5375,13 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F62" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="G62" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -5157,10 +5389,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B63" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
@@ -5169,13 +5401,13 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>9.38</v>
+        <v>6.67</v>
       </c>
       <c r="F63" t="str">
-        <v>9.38</v>
+        <v>6.67</v>
       </c>
       <c r="G63" t="str">
-        <v>9.38</v>
+        <v>6.67</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -5183,10 +5415,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2025-08-29</v>
+        <v>2025-08-28</v>
       </c>
       <c r="B64" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C64" t="str">
         <v>Available</v>
@@ -5195,13 +5427,13 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -5209,584 +5441,584 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F65" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G65" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>6</v>
+      </c>
+      <c r="F66" t="str">
+        <v>6</v>
+      </c>
+      <c r="G66" t="str">
+        <v>6</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="F67" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="G67" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F68" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G68" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="F69" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="G69" t="str">
+        <v>4.8</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v>4</v>
+      </c>
+      <c r="F70" t="str">
+        <v>4</v>
+      </c>
+      <c r="G70" t="str">
+        <v>4</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B71" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v>4</v>
+      </c>
+      <c r="F72" t="str">
+        <v>4</v>
+      </c>
+      <c r="G72" t="str">
+        <v>4</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Nafees (NL) (GH), Hamza</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="F73" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="G73" t="str">
+        <v>11.25</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F74" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G74" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B75" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F75" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G75" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2025-08-28</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v>6</v>
+      </c>
+      <c r="F76" t="str">
+        <v>6</v>
+      </c>
+      <c r="G76" t="str">
+        <v>6</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="B65" t="str">
+      <c r="B77" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v>4</v>
+      </c>
+      <c r="F77" t="str">
+        <v>4</v>
+      </c>
+      <c r="G77" t="str">
+        <v>4</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F78" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G78" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v>9</v>
+      </c>
+      <c r="F79" t="str">
+        <v>9</v>
+      </c>
+      <c r="G79" t="str">
+        <v>0</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v>9</v>
+      </c>
+      <c r="F80" t="str">
+        <v>0</v>
+      </c>
+      <c r="G80" t="str">
+        <v>0</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F81" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G81" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F82" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G82" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="F83" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="G83" t="str">
+        <v>9.38</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v>6</v>
+      </c>
+      <c r="F84" t="str">
+        <v>6</v>
+      </c>
+      <c r="G84" t="str">
+        <v>6</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2025-08-29</v>
+      </c>
+      <c r="B85" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
-      <c r="C65" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D65" t="str">
-        <v/>
-      </c>
-      <c r="E65" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F65" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G65" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H65" t="str">
+      <c r="C85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H85" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66" t="str">
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
         <v>2025-08-29</v>
       </c>
-      <c r="B66" t="str">
+      <c r="B86" t="str">
         <v>Jack (NL), Sharon</v>
       </c>
-      <c r="C66" t="str">
+      <c r="C86" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-      <c r="E66" t="str">
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
         <v>4.8</v>
       </c>
-      <c r="F66" t="str">
+      <c r="F86" t="str">
         <v>2</v>
       </c>
-      <c r="G66" t="str">
-        <v>0</v>
-      </c>
-      <c r="H66" t="str" xml:space="preserve">
+      <c r="G86" t="str">
+        <v>0</v>
+      </c>
+      <c r="H86" t="str" xml:space="preserve">
         <v xml:space="preserve">Wants this as a break. _x000d_
 _x000d_
 Eilidh 29/05/2025</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B67" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D67" t="str">
-        <v/>
-      </c>
-      <c r="E67" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="F67" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G67" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B68" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C68" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D68" t="str">
-        <v/>
-      </c>
-      <c r="E68" t="str">
-        <v>4</v>
-      </c>
-      <c r="F68" t="str">
-        <v>4</v>
-      </c>
-      <c r="G68" t="str">
-        <v>4</v>
-      </c>
-      <c r="H68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B69" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
-      </c>
-      <c r="C69" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D69" t="str">
-        <v/>
-      </c>
-      <c r="E69" t="str">
-        <v>4</v>
-      </c>
-      <c r="F69" t="str">
-        <v>4</v>
-      </c>
-      <c r="G69" t="str">
-        <v>4</v>
-      </c>
-      <c r="H69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
-      </c>
-      <c r="C70" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D70" t="str">
-        <v/>
-      </c>
-      <c r="E70" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="F70" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="G70" t="str">
-        <v>11.25</v>
-      </c>
-      <c r="H70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C71" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D71" t="str">
-        <v/>
-      </c>
-      <c r="E71" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F71" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G71" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B72" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C72" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D72" t="str">
-        <v/>
-      </c>
-      <c r="E72" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F72" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G72" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C73" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D73" t="str">
-        <v/>
-      </c>
-      <c r="E73" t="str">
-        <v>6</v>
-      </c>
-      <c r="F73" t="str">
-        <v>6</v>
-      </c>
-      <c r="G73" t="str">
-        <v>6</v>
-      </c>
-      <c r="H73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C74" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F74" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G74" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B75" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C75" t="str">
-        <v>Holiday</v>
-      </c>
-      <c r="D75" t="str">
-        <v/>
-      </c>
-      <c r="E75" t="str">
-        <v>9</v>
-      </c>
-      <c r="F75" t="str">
-        <v>9</v>
-      </c>
-      <c r="G75" t="str">
-        <v>0</v>
-      </c>
-      <c r="H75" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B76" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C76" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D76" t="str">
-        <v/>
-      </c>
-      <c r="E76" t="str">
-        <v>9</v>
-      </c>
-      <c r="F76" t="str">
-        <v>0</v>
-      </c>
-      <c r="G76" t="str">
-        <v>0</v>
-      </c>
-      <c r="H76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B77" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D77" t="str">
-        <v/>
-      </c>
-      <c r="E77" t="str">
-        <v>6</v>
-      </c>
-      <c r="F77" t="str">
-        <v>6</v>
-      </c>
-      <c r="G77" t="str">
-        <v>6</v>
-      </c>
-      <c r="H77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B78" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C78" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D78" t="str">
-        <v/>
-      </c>
-      <c r="E78" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F78" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G78" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B79" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C79" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D79" t="str">
-        <v/>
-      </c>
-      <c r="E79" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F79" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G79" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B80" t="str">
-        <v>Shawcross (NL), Emma</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D80" t="str">
-        <v/>
-      </c>
-      <c r="E80" t="str">
-        <v>10</v>
-      </c>
-      <c r="F80" t="str">
-        <v>10</v>
-      </c>
-      <c r="G80" t="str">
-        <v>10</v>
-      </c>
-      <c r="H80" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B81" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D81" t="str">
-        <v/>
-      </c>
-      <c r="E81" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F81" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G81" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B82" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="C82" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D82" t="str">
-        <v/>
-      </c>
-      <c r="E82" t="str">
-        <v>4</v>
-      </c>
-      <c r="F82" t="str">
-        <v>4</v>
-      </c>
-      <c r="G82" t="str">
-        <v>4</v>
-      </c>
-      <c r="H82" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B83" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C83" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D83" t="str">
-        <v/>
-      </c>
-      <c r="E83" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F83" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G83" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H83" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D84" t="str">
-        <v/>
-      </c>
-      <c r="E84" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F84" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G84" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D85" t="str">
-        <v/>
-      </c>
-      <c r="E85" t="str">
-        <v>6</v>
-      </c>
-      <c r="F85" t="str">
-        <v>6</v>
-      </c>
-      <c r="G85" t="str">
-        <v>6</v>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D86" t="str">
-        <v/>
-      </c>
-      <c r="E86" t="str">
-        <v>6</v>
-      </c>
-      <c r="F86" t="str">
-        <v>6</v>
-      </c>
-      <c r="G86" t="str">
-        <v>6</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B87" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C87" t="str">
         <v>Available</v>
@@ -5795,24 +6027,24 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="F87" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G87" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H87" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B88" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
@@ -5821,13 +6053,13 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F88" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="G88" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5835,36 +6067,36 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B89" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C89" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D89" t="str">
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F89" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G89" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H89" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B90" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C90" t="str">
         <v>Available</v>
@@ -5873,13 +6105,13 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F90" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G90" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -5887,10 +6119,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B91" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nafees (NL) (GH), Hamza</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
@@ -5899,13 +6131,13 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="F91" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="G91" t="str">
-        <v>4</v>
+        <v>11.25</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5913,10 +6145,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B92" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C92" t="str">
         <v>Available</v>
@@ -5925,24 +6157,24 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="F92" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="G92" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="H92" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2025-08-25</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B93" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C93" t="str">
         <v>Available</v>
@@ -5951,13 +6183,13 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F93" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G93" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -5965,10 +6197,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-29</v>
       </c>
       <c r="B94" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C94" t="str">
         <v>Available</v>
@@ -5977,13 +6209,13 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F94" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G94" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5991,10 +6223,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B95" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C95" t="str">
         <v>Available</v>
@@ -6003,13 +6235,13 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="F95" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="G95" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -6017,36 +6249,36 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B96" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C96" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D96" t="str">
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F96" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G96" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B97" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C97" t="str">
         <v>Available</v>
@@ -6055,13 +6287,13 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F97" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G97" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6069,10 +6301,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B98" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C98" t="str">
         <v>Available</v>
@@ -6081,13 +6313,13 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F98" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G98" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H98" t="str">
         <v/>
@@ -6095,10 +6327,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2025-08-31</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B99" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C99" t="str">
         <v>Available</v>
@@ -6107,13 +6339,13 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F99" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G99" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H99" t="str">
         <v/>
@@ -6121,33 +6353,241 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B100" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2025-08-30</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>10</v>
+      </c>
+      <c r="F101" t="str">
+        <v>10</v>
+      </c>
+      <c r="G101" t="str">
+        <v>10</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>2025-08-31</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B102" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G102" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G103" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>6</v>
+      </c>
+      <c r="F104" t="str">
+        <v>6</v>
+      </c>
+      <c r="G104" t="str">
+        <v>6</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G105" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>4</v>
+      </c>
+      <c r="F106" t="str">
+        <v>4</v>
+      </c>
+      <c r="G106" t="str">
+        <v>4</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G107" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>2025-08-31</v>
+      </c>
+      <c r="B108" t="str">
         <v>Shawcross (NL), Emma</v>
       </c>
-      <c r="C100" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D100" t="str">
-        <v/>
-      </c>
-      <c r="E100" t="str">
+      <c r="C108" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
         <v>10</v>
       </c>
-      <c r="F100" t="str">
+      <c r="F108" t="str">
         <v>10</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G108" t="str">
         <v>10</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H108" t="str">
         <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:I98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -432,103 +432,103 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E2" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E3" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B4" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C4" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E4" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B5" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C5" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E5" t="str">
         <v>Holiday</v>
@@ -537,7 +537,7 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
@@ -548,16 +548,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B6" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C6" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E6" t="str">
         <v>Holiday</v>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
@@ -575,105 +575,107 @@
         <v>Created by new vacation process.</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B7" t="str">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="C7" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E7" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
       </c>
-      <c r="I7" t="str">
-        <v>Created by new vacation process.</v>
+      <c r="I7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E8" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
         <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E9" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
-      <c r="I9" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B10" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C10" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E10" t="str">
         <v>Other Unavailable</v>
@@ -687,128 +689,125 @@
       <c r="H10" t="str">
         <v>0</v>
       </c>
-      <c r="I10" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+      <c r="I10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B11" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E11" t="str">
-        <v>Other Unavailable</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
+        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B12" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C12" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E12" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F12" t="str">
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v>0</v>
-      </c>
-      <c r="I12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. _x000d_
-_x000d_
-Eilidh 29/05/2025</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v>3.2</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B13" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E13" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F13" t="str">
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="str">
-        <v>0</v>
-      </c>
-      <c r="I13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. _x000d_
-_x000d_
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E14" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F14" t="str">
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -822,7 +821,7 @@
         <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
@@ -837,7 +836,7 @@
         <v>3.2</v>
       </c>
       <c r="I15" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -851,7 +850,7 @@
         <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
@@ -866,21 +865,21 @@
         <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
@@ -889,27 +888,27 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>0.17</v>
       </c>
       <c r="H17" t="str">
-        <v>3.2</v>
+        <v>0.17</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B18" t="str">
         <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -918,27 +917,27 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H18" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
         <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -947,13 +946,13 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H19" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I19" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
@@ -967,7 +966,7 @@
         <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -982,7 +981,7 @@
         <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -996,7 +995,7 @@
         <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1005,13 +1004,13 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>0.67</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1025,7 +1024,7 @@
         <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1040,21 +1039,21 @@
         <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C23" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1063,10 +1062,10 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H23" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1074,16 +1073,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B24" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C24" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
@@ -1092,10 +1091,10 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>2.67</v>
+        <v>0.5</v>
       </c>
       <c r="H24" t="str">
-        <v>2.67</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1103,16 +1102,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B25" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C25" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
@@ -1121,10 +1120,10 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H25" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1138,10 +1137,10 @@
         <v>37.5</v>
       </c>
       <c r="C26" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
@@ -1150,16 +1149,16 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
@@ -1167,10 +1166,10 @@
         <v>37.5</v>
       </c>
       <c r="C27" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
@@ -1179,27 +1178,28 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="str">
-        <v>9.38</v>
-      </c>
-      <c r="I27" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="I27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B28" t="str">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="C28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1208,27 +1208,27 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H28" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B29" t="str">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="C29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
@@ -1237,13 +1237,13 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H29" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="30">
@@ -1257,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
@@ -1286,7 +1286,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
@@ -1315,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
@@ -1335,16 +1335,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B33" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
@@ -1353,27 +1353,27 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I33" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B34" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
@@ -1382,13 +1382,13 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H34" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1402,7 +1402,7 @@
         <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
@@ -1431,7 +1431,7 @@
         <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1460,7 +1460,7 @@
         <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1480,16 +1480,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B38" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1498,27 +1498,27 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H38" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B39" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C39" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1527,27 +1527,27 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H39" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B40" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1556,27 +1556,27 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H40" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I40" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B41" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1585,13 +1585,13 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H41" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="I41" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1605,7 +1605,7 @@
         <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1634,7 +1634,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1654,16 +1654,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B44" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C44" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
@@ -1672,10 +1672,10 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H44" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B45" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C45" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1701,10 +1701,10 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H45" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1712,16 +1712,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B46" t="str">
         <v>16</v>
       </c>
       <c r="C46" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
@@ -1730,10 +1730,10 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H46" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1750,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1779,7 +1779,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1808,7 +1808,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
@@ -1828,16 +1828,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B50" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C50" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1846,10 +1846,10 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H50" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1863,10 +1863,10 @@
         <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1875,10 +1875,10 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="H51" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1892,10 +1892,10 @@
         <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1904,10 +1904,10 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="H52" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1924,7 +1924,7 @@
         <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1933,10 +1933,10 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H53" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1953,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1962,10 +1962,10 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1982,7 +1982,7 @@
         <v>9</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1991,10 +1991,10 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H55" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2011,7 +2011,7 @@
         <v>9</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
@@ -2040,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
@@ -2069,7 +2069,7 @@
         <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
@@ -2078,10 +2078,10 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
         <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
@@ -2127,7 +2127,7 @@
         <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
@@ -2156,7 +2156,7 @@
         <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2185,7 +2185,7 @@
         <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2214,7 +2214,7 @@
         <v>7.5</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2243,7 +2243,7 @@
         <v>7.5</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2272,7 +2272,7 @@
         <v>7.5</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B66" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C66" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
@@ -2310,10 +2310,10 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B67" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
@@ -2339,10 +2339,10 @@
         <v/>
       </c>
       <c r="G67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2350,16 +2350,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B68" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
@@ -2368,10 +2368,10 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2379,16 +2379,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B69" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
@@ -2397,10 +2397,10 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2417,7 +2417,7 @@
         <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
@@ -2437,16 +2437,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B71" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
@@ -2455,27 +2455,27 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B72" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
@@ -2484,27 +2484,27 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B73" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
@@ -2513,27 +2513,27 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B74" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
@@ -2542,13 +2542,13 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="75">
@@ -2562,7 +2562,7 @@
         <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C76" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
@@ -2600,27 +2600,27 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I76" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
@@ -2629,27 +2629,27 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
@@ -2658,27 +2658,27 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B79" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
@@ -2687,13 +2687,13 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H79" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I79" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -2707,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
@@ -2727,16 +2727,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B81" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
@@ -2745,10 +2745,10 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2756,16 +2756,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
@@ -2774,10 +2774,10 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B83" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
@@ -2803,10 +2803,10 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H83" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B84" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C84" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D84" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E84" t="str">
         <v>Available</v>
@@ -2832,27 +2832,27 @@
         <v/>
       </c>
       <c r="G84" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H84" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B85" t="str">
         <v>16</v>
       </c>
       <c r="C85" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="D85" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E85" t="str">
         <v>Available</v>
@@ -2861,10 +2861,10 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H85" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -2872,16 +2872,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B86" t="str">
         <v>16</v>
       </c>
       <c r="C86" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="D86" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E86" t="str">
         <v>Available</v>
@@ -2890,10 +2890,10 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H86" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -2901,16 +2901,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B87" t="str">
         <v>16</v>
       </c>
       <c r="C87" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="D87" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E87" t="str">
         <v>Available</v>
@@ -2919,10 +2919,10 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H87" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2939,7 +2939,7 @@
         <v>3.2</v>
       </c>
       <c r="D88" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E88" t="str">
         <v>Available</v>
@@ -2948,27 +2948,27 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H88" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I88" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B89" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C89" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D89" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E89" t="str">
         <v>Available</v>
@@ -2977,10 +2977,10 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="H89" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -2988,16 +2988,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B90" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C90" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D90" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E90" t="str">
         <v>Available</v>
@@ -3006,10 +3006,10 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="H90" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B91" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C91" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D91" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E91" t="str">
         <v>Available</v>
@@ -3035,10 +3035,10 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>3.2</v>
+        <v>1.43</v>
       </c>
       <c r="H91" t="str">
-        <v>3.2</v>
+        <v>1.43</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3046,16 +3046,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B92" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C92" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D92" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E92" t="str">
         <v>Available</v>
@@ -3064,10 +3064,10 @@
         <v/>
       </c>
       <c r="G92" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="H92" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3075,16 +3075,16 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B93" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C93" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="D93" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E93" t="str">
         <v>Available</v>
@@ -3093,10 +3093,10 @@
         <v/>
       </c>
       <c r="G93" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3104,16 +3104,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B94" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C94" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D94" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E94" t="str">
         <v>Available</v>
@@ -3122,10 +3122,10 @@
         <v/>
       </c>
       <c r="G94" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H94" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3133,16 +3133,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B95" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D95" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E95" t="str">
         <v>Available</v>
@@ -3151,10 +3151,10 @@
         <v/>
       </c>
       <c r="G95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H95" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3162,16 +3162,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B96" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D96" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E96" t="str">
         <v>Available</v>
@@ -3180,10 +3180,10 @@
         <v/>
       </c>
       <c r="G96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3191,16 +3191,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B97" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D97" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E97" t="str">
         <v>Available</v>
@@ -3209,10 +3209,10 @@
         <v/>
       </c>
       <c r="G97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H97" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3220,16 +3220,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B98" t="str">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="D98" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E98" t="str">
         <v>Available</v>
@@ -3238,311 +3238,18 @@
         <v/>
       </c>
       <c r="G98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="H98" t="str">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I98" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B99" t="str">
-        <v>24</v>
-      </c>
-      <c r="C99" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H99" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B100" t="str">
-        <v>24</v>
-      </c>
-      <c r="C100" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D100" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="E100" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F100" t="str">
-        <v/>
-      </c>
-      <c r="G100" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H100" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B101" t="str">
-        <v>24</v>
-      </c>
-      <c r="C101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="E101" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F101" t="str">
-        <v/>
-      </c>
-      <c r="G101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="H101" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="I101" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B102" t="str">
-        <v>24</v>
-      </c>
-      <c r="C102" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="E102" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H102" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B103" t="str">
-        <v>30</v>
-      </c>
-      <c r="C103" t="str">
-        <v>6</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2025-08-25</v>
-      </c>
-      <c r="E103" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F103" t="str">
-        <v/>
-      </c>
-      <c r="G103" t="str">
-        <v>6</v>
-      </c>
-      <c r="H103" t="str">
-        <v>6</v>
-      </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B104" t="str">
-        <v>30</v>
-      </c>
-      <c r="C104" t="str">
-        <v>6</v>
-      </c>
-      <c r="D104" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E104" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
-        <v>6</v>
-      </c>
-      <c r="H104" t="str">
-        <v>6</v>
-      </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B105" t="str">
-        <v>30</v>
-      </c>
-      <c r="C105" t="str">
-        <v>6</v>
-      </c>
-      <c r="D105" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="E105" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v>6</v>
-      </c>
-      <c r="H105" t="str">
-        <v>6</v>
-      </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B106" t="str">
-        <v>30</v>
-      </c>
-      <c r="C106" t="str">
-        <v>6</v>
-      </c>
-      <c r="D106" t="str">
-        <v>2025-08-28</v>
-      </c>
-      <c r="E106" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
-        <v>6</v>
-      </c>
-      <c r="H106" t="str">
-        <v>6</v>
-      </c>
-      <c r="I106" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B107" t="str">
-        <v>30</v>
-      </c>
-      <c r="C107" t="str">
-        <v>6</v>
-      </c>
-      <c r="D107" t="str">
-        <v>2025-08-29</v>
-      </c>
-      <c r="E107" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
-        <v>6</v>
-      </c>
-      <c r="H107" t="str">
-        <v>6</v>
-      </c>
-      <c r="I107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="B108" t="str">
-        <v>16</v>
-      </c>
-      <c r="C108" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="D108" t="str">
-        <v>2025-08-26</v>
-      </c>
-      <c r="E108" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="F108" t="str">
-        <v/>
-      </c>
-      <c r="G108" t="str">
-        <v>4.75</v>
-      </c>
-      <c r="H108" t="str">
-        <v>0</v>
-      </c>
-      <c r="I108" t="str" xml:space="preserve">
-        <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
-_x000d_
-Peter_x000d_
-26.8.25, 0827</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3579,129 +3286,129 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B2" t="str">
-        <v>50.17</v>
+        <v>57</v>
       </c>
       <c r="C2" t="str">
-        <v>50.17</v>
+        <v>57</v>
       </c>
       <c r="D2" t="str">
-        <v>10.7</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>-11.83</v>
+        <v>57</v>
       </c>
       <c r="H2" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>81.8</v>
+        <v>70.5</v>
       </c>
       <c r="C3" t="str">
-        <v>81.8</v>
+        <v>70.5</v>
       </c>
       <c r="D3" t="str">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="E3" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>-8.2</v>
+        <v>70.5</v>
       </c>
       <c r="H3" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B4" t="str">
-        <v>79.47</v>
+        <v>74</v>
       </c>
       <c r="C4" t="str">
-        <v>79.47</v>
+        <v>74</v>
       </c>
       <c r="D4" t="str">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>-24.53</v>
+        <v>74</v>
       </c>
       <c r="H4" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B5" t="str">
-        <v>84</v>
+        <v>86.66</v>
       </c>
       <c r="C5" t="str">
-        <v>84</v>
+        <v>86.66</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
       </c>
       <c r="E5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>-12</v>
+        <v>86.66</v>
       </c>
       <c r="H5" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>75.33</v>
+        <v>71.56</v>
       </c>
       <c r="C6" t="str">
-        <v>75.33</v>
+        <v>71.56</v>
       </c>
       <c r="D6" t="str">
         <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>17.33</v>
+        <v>71.56</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3709,51 +3416,51 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B7" t="str">
-        <v>33.67</v>
+        <v>30.17</v>
       </c>
       <c r="C7" t="str">
-        <v>33.67</v>
+        <v>30.17</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>9</v>
+        <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>-9.33</v>
+        <v>30.17</v>
       </c>
       <c r="H7" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-31</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B8" t="str">
-        <v>47</v>
+        <v>40.83</v>
       </c>
       <c r="C8" t="str">
-        <v>47</v>
+        <v>40.83</v>
       </c>
       <c r="D8" t="str">
         <v>0</v>
       </c>
       <c r="E8" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F8" t="str">
         <v>0</v>
       </c>
-      <c r="F8" t="str">
-        <v>39</v>
-      </c>
       <c r="G8" t="str">
-        <v>8</v>
+        <v>40.83</v>
       </c>
       <c r="H8" t="str">
         <v>Sufficient</v>
@@ -3768,7 +3475,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3798,7 +3505,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B2" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
@@ -3824,7 +3531,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3850,10 +3557,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B4" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C4" t="str">
         <v>Available</v>
@@ -3862,50 +3569,50 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="F4" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="G4" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H4" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B5" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C5" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D5" t="str">
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
@@ -3914,13 +3621,13 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3928,10 +3635,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
@@ -3940,13 +3647,13 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -3954,10 +3661,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
@@ -3975,15 +3682,15 @@
         <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
@@ -3992,27 +3699,27 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="F9" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="str">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B10" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C10" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D10" t="str">
         <v/>
@@ -4024,18 +3731,19 @@
         <v>7.5</v>
       </c>
       <c r="G10" t="str">
-        <v>0</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Sophie has a hospital appointment on this date - sent via email on 5th August - MT</v>
+        <v>7.5</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B11" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
@@ -4044,13 +3752,13 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G11" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -4058,13 +3766,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B12" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C12" t="str">
-        <v>Sick</v>
+        <v>Available</v>
       </c>
       <c r="D12" t="str">
         <v/>
@@ -4076,70 +3784,71 @@
         <v>3.2</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B13" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D13" t="str">
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="F13" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="G13" t="str">
         <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B14" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D14" t="str">
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F14" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="str">
-        <v>4</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
@@ -4148,24 +3857,24 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F15" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H15" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-08-25</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B16" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
@@ -4174,13 +3883,13 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -4188,10 +3897,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B17" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
@@ -4200,13 +3909,13 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F17" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -4214,10 +3923,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
@@ -4226,24 +3935,24 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="F18" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B19" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
@@ -4252,13 +3961,13 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F19" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -4266,39 +3975,39 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C20" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D20" t="str">
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F20" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H20" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B21" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C21" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -4307,21 +4016,21 @@
         <v>9</v>
       </c>
       <c r="F21" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G21" t="str">
         <v>0</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B22" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C22" t="str">
         <v>Available</v>
@@ -4330,13 +4039,13 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F22" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -4344,10 +4053,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B23" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C23" t="str">
         <v>Available</v>
@@ -4356,13 +4065,13 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F23" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G23" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -4370,36 +4079,36 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B24" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C24" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D24" t="str">
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F24" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="G24" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
@@ -4408,13 +4117,13 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
-        <v>9.38</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -4422,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B26" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
@@ -4434,13 +4143,13 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F26" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G26" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -4448,10 +4157,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B27" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
@@ -4460,50 +4169,50 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="F27" t="str">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="G27" t="str">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="H27" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B28" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C28" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D28" t="str">
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="F28" t="str">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="G28" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C29" t="str">
         <v>Available</v>
@@ -4512,13 +4221,13 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="F29" t="str">
-        <v>2.8</v>
+        <v>5.33</v>
       </c>
       <c r="G29" t="str">
-        <v>2.8</v>
+        <v>5.33</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -4526,10 +4235,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B30" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C30" t="str">
         <v>Available</v>
@@ -4538,13 +4247,13 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F30" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -4552,36 +4261,36 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B31" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C31" t="str">
-        <v>Sick</v>
+        <v>Holiday</v>
       </c>
       <c r="D31" t="str">
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="F31" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
       </c>
       <c r="H31" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B32" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C32" t="str">
         <v>Available</v>
@@ -4590,13 +4299,13 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -4604,10 +4313,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B33" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
@@ -4616,13 +4325,13 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="F33" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="G33" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -4630,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B34" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
@@ -4642,13 +4351,13 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>11.25</v>
+        <v>2.67</v>
       </c>
       <c r="F34" t="str">
-        <v>11.25</v>
+        <v>2.67</v>
       </c>
       <c r="G34" t="str">
-        <v>11.25</v>
+        <v>2.67</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -4656,36 +4365,36 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B35" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C35" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D35" t="str">
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F35" t="str">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G35" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H35" t="str">
-        <v>Brooke called on call and advised that her son had a doctors appointment and would not be able to make her first client. SM</v>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B36" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
@@ -4694,53 +4403,50 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F36" t="str">
-        <v>0.67</v>
+        <v>7.5</v>
       </c>
       <c r="G36" t="str">
-        <v>0.67</v>
+        <v>7.5</v>
       </c>
       <c r="H36" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B37" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C37" t="str">
-        <v>Dependant Leave</v>
+        <v>Available</v>
       </c>
       <c r="D37" t="str">
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F37" t="str">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="G37" t="str">
-        <v>0</v>
-      </c>
-      <c r="H37" t="str" xml:space="preserve">
-        <v xml:space="preserve">Brooke asked for first visit to be covered as she needs to take son to doctors due to morning fever._x000d_
-_x000d_
-Peter_x000d_
-26.8.25, 0827</v>
+        <v>4</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-08-26</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B38" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
@@ -4749,13 +4455,13 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F38" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G38" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -4763,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B39" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
@@ -4775,24 +4481,24 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F39" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G39" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H39" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B40" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C40" t="str">
         <v>Available</v>
@@ -4801,13 +4507,13 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F40" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G40" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -4815,36 +4521,36 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C41" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D41" t="str">
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4853,50 +4559,51 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" t="str">
+        <v>6</v>
+      </c>
+      <c r="G42" t="str">
+        <v>6</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F43" t="str">
+        <v>7</v>
+      </c>
+      <c r="G43" t="str">
         <v>0</v>
       </c>
-      <c r="G42" t="str">
-        <v>0</v>
-      </c>
-      <c r="H42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>2025-08-27</v>
-      </c>
-      <c r="B43" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C43" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-      <c r="E43" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F43" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G43" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H43" t="str">
-        <v/>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B44" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
@@ -4905,13 +4612,13 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="str">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4919,10 +4626,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B45" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
@@ -4931,13 +4638,13 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G45" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4945,10 +4652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B46" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
@@ -4957,50 +4664,50 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F46" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G46" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B47" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C47" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D47" t="str">
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>9.38</v>
+        <v>3.43</v>
       </c>
       <c r="F47" t="str">
-        <v>9.38</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
-        <v>9.38</v>
+        <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B48" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
@@ -5009,13 +4716,13 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F48" t="str">
-        <v>6</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="str">
-        <v>6</v>
+        <v>1.43</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -5023,10 +4730,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B49" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
@@ -5035,52 +4742,50 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F49" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G49" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B50" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C50" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D50" t="str">
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G50" t="str">
-        <v>0</v>
-      </c>
-      <c r="H50" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. _x000d_
-_x000d_
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B51" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
@@ -5089,24 +4794,24 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="F51" t="str">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="G51" t="str">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B52" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
@@ -5115,13 +4820,13 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G52" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -5129,36 +4834,36 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B53" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C53" t="str">
-        <v>Sick</v>
+        <v>Available</v>
       </c>
       <c r="D53" t="str">
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F53" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G53" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H53" t="str">
-        <v>Cheryl called to advise that she was in the hospital. Megan and Shannon aware of reason. SM</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B54" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
@@ -5167,24 +4872,24 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F54" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B55" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
@@ -5193,13 +4898,13 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F55" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G55" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -5207,10 +4912,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B56" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
@@ -5219,13 +4924,13 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="F56" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="G56" t="str">
-        <v>11.25</v>
+        <v>3.2</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -5233,10 +4938,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B57" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -5245,24 +4950,24 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="F57" t="str">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="G57" t="str">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="H57" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-08-27</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B58" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
@@ -5285,10 +4990,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B59" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
@@ -5297,24 +5002,24 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F59" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G59" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B60" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
@@ -5323,13 +5028,13 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F60" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G60" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -5337,62 +5042,63 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C61" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D61" t="str">
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F61" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G61" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H61" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B62" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C62" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D62" t="str">
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="F62" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" t="str">
         <v>0</v>
       </c>
-      <c r="H62" t="str">
-        <v/>
+      <c r="H62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B63" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
@@ -5401,13 +5107,13 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="F63" t="str">
-        <v>6.67</v>
+        <v>1.43</v>
       </c>
       <c r="G63" t="str">
-        <v>6.67</v>
+        <v>1.43</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -5415,10 +5121,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B64" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C64" t="str">
         <v>Available</v>
@@ -5427,13 +5133,13 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F64" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G64" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -5441,10 +5147,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
@@ -5453,13 +5159,13 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="F65" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -5467,10 +5173,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B66" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -5479,13 +5185,13 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F66" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G66" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -5493,10 +5199,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B67" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
@@ -5505,24 +5211,24 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="F67" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="G67" t="str">
-        <v>9.38</v>
+        <v>2.67</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B68" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -5531,24 +5237,24 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F68" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G68" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B69" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
@@ -5557,24 +5263,24 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="G69" t="str">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B70" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
@@ -5583,13 +5289,13 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F70" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G70" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -5597,10 +5303,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
@@ -5618,15 +5324,15 @@
         <v>3.2</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
@@ -5635,13 +5341,13 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="F72" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G72" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -5649,10 +5355,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
@@ -5661,13 +5367,13 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="F73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="G73" t="str">
-        <v>11.25</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -5675,10 +5381,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B74" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
@@ -5687,13 +5393,13 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G74" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5701,10 +5407,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B75" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
@@ -5713,13 +5419,13 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F75" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G75" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5727,10 +5433,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-08-28</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B76" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
@@ -5739,24 +5445,24 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B77" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
@@ -5765,24 +5471,24 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F77" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="H77" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B78" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
@@ -5791,13 +5497,13 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F78" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G78" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -5805,62 +5511,62 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B79" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C79" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D79" t="str">
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F79" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G79" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H79" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B80" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C80" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D80" t="str">
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F80" t="str">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G80" t="str">
         <v>0</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B81" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
@@ -5869,24 +5575,24 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F81" t="str">
-        <v>3.2</v>
+        <v>0.17</v>
       </c>
       <c r="G81" t="str">
-        <v>3.2</v>
+        <v>0.17</v>
       </c>
       <c r="H81" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B82" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C82" t="str">
         <v>Available</v>
@@ -5895,13 +5601,13 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F82" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G82" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -5909,10 +5615,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B83" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
@@ -5921,13 +5627,13 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="F83" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="G83" t="str">
-        <v>9.38</v>
+        <v>7.5</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -5935,10 +5641,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B84" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C84" t="str">
         <v>Available</v>
@@ -5947,24 +5653,24 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F84" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G84" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B85" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C85" t="str">
         <v>Available</v>
@@ -5973,52 +5679,50 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="F85" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="G85" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H85" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
       <c r="A86" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B86" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C86" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D86" t="str">
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="F86" t="str">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G86" t="str">
-        <v>0</v>
-      </c>
-      <c r="H86" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. _x000d_
-_x000d_
-Eilidh 29/05/2025</v>
+        <v>9</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B87" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C87" t="str">
         <v>Available</v>
@@ -6027,13 +5731,13 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="F87" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="G87" t="str">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -6041,10 +5745,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B88" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
@@ -6053,13 +5757,13 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F88" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G88" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -6067,10 +5771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B89" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C89" t="str">
         <v>Available</v>
@@ -6079,13 +5783,13 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F89" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G89" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -6093,10 +5797,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B90" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C90" t="str">
         <v>Available</v>
@@ -6105,13 +5809,13 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F90" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G90" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -6119,10 +5823,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B91" t="str">
-        <v>Nafees (NL) (GH), Hamza</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
@@ -6131,13 +5835,13 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="F91" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="G91" t="str">
-        <v>11.25</v>
+        <v>7.5</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -6145,10 +5849,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B92" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C92" t="str">
         <v>Available</v>
@@ -6157,24 +5861,24 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="F92" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="G92" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B93" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C93" t="str">
         <v>Available</v>
@@ -6183,13 +5887,13 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F93" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="G93" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H93" t="str">
         <v/>
@@ -6197,10 +5901,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2025-08-29</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B94" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C94" t="str">
         <v>Available</v>
@@ -6209,13 +5913,13 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G94" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -6223,10 +5927,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B95" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C95" t="str">
         <v>Available</v>
@@ -6235,13 +5939,13 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F95" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G95" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -6249,36 +5953,36 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B96" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C96" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D96" t="str">
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="F96" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="G96" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H96" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B97" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C97" t="str">
         <v>Available</v>
@@ -6287,13 +5991,13 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F97" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="G97" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6301,10 +6005,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2025-08-30</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B98" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C98" t="str">
         <v>Available</v>
@@ -6323,271 +6027,11 @@
       </c>
       <c r="H98" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D99" t="str">
-        <v/>
-      </c>
-      <c r="E99" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F99" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G99" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H99" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B100" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D100" t="str">
-        <v/>
-      </c>
-      <c r="E100" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F100" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G100" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>2025-08-30</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Shawcross (NL), Emma</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
-      <c r="E101" t="str">
-        <v>10</v>
-      </c>
-      <c r="F101" t="str">
-        <v>10</v>
-      </c>
-      <c r="G101" t="str">
-        <v>10</v>
-      </c>
-      <c r="H101" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G102" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G103" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D104" t="str">
-        <v/>
-      </c>
-      <c r="E104" t="str">
-        <v>6</v>
-      </c>
-      <c r="F104" t="str">
-        <v>6</v>
-      </c>
-      <c r="G104" t="str">
-        <v>6</v>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B105" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G105" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
-        <v>4</v>
-      </c>
-      <c r="F106" t="str">
-        <v>4</v>
-      </c>
-      <c r="G106" t="str">
-        <v>4</v>
-      </c>
-      <c r="H106" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B107" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G107" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>2025-08-31</v>
-      </c>
-      <c r="B108" t="str">
-        <v>Shawcross (NL), Emma</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v>10</v>
-      </c>
-      <c r="F108" t="str">
-        <v>10</v>
-      </c>
-      <c r="G108" t="str">
-        <v>10</v>
-      </c>
-      <c r="H108" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3301,13 +3301,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G2" t="str">
-        <v>57</v>
+        <v>-12</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
@@ -3327,10 +3327,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G3" t="str">
-        <v>70.5</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -3353,13 +3353,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="G4" t="str">
-        <v>74</v>
+        <v>-8</v>
       </c>
       <c r="H4" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="5">
@@ -3379,10 +3379,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="G5" t="str">
-        <v>86.66</v>
+        <v>15.66</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3405,10 +3405,10 @@
         <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G6" t="str">
-        <v>71.56</v>
+        <v>16.56</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3431,13 +3431,13 @@
         <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G7" t="str">
-        <v>30.17</v>
+        <v>-12.83</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
@@ -3457,13 +3457,13 @@
         <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G8" t="str">
-        <v>40.83</v>
+        <v>-0.17</v>
       </c>
       <c r="H8" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
   </sheetData>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -447,7 +447,7 @@
         <v>Holiday</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G2" t="str">
         <v>9</v>
@@ -476,7 +476,7 @@
         <v>Holiday</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G3" t="str">
         <v>9</v>
@@ -505,7 +505,7 @@
         <v>Holiday</v>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="G4" t="str">
         <v>3.43</v>
@@ -534,7 +534,7 @@
         <v>Holiday</v>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="G5" t="str">
         <v>3.43</v>
@@ -563,7 +563,7 @@
         <v>Holiday</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="G6" t="str">
         <v>3.43</v>
@@ -592,7 +592,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>08:00-15:00</v>
       </c>
       <c r="G7" t="str">
         <v>7</v>
@@ -622,7 +622,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="G8" t="str">
         <v>2</v>
@@ -651,7 +651,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="G9" t="str">
         <v>2</v>
@@ -681,7 +681,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="G10" t="str">
         <v>2</v>
@@ -711,7 +711,7 @@
         <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>10:20-12:50</v>
       </c>
       <c r="G11" t="str">
         <v>2.5</v>
@@ -740,7 +740,7 @@
         <v>Available</v>
       </c>
       <c r="F12" t="str">
-        <v/>
+        <v>10:30-14:00</v>
       </c>
       <c r="G12" t="str">
         <v>3.2</v>
@@ -769,7 +769,7 @@
         <v>Available</v>
       </c>
       <c r="F13" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="G13" t="str">
         <v>3.2</v>
@@ -798,7 +798,7 @@
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="G14" t="str">
         <v>3.2</v>
@@ -827,7 +827,7 @@
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="G15" t="str">
         <v>3.2</v>
@@ -856,7 +856,7 @@
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v/>
+        <v>10:30-14:00</v>
       </c>
       <c r="G16" t="str">
         <v>3.2</v>
@@ -885,7 +885,7 @@
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G17" t="str">
         <v>0.17</v>
@@ -914,7 +914,7 @@
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
         <v>2.67</v>
@@ -943,7 +943,7 @@
         <v>Available</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
         <v>2.67</v>
@@ -972,7 +972,7 @@
         <v>Available</v>
       </c>
       <c r="F20" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
         <v>2.67</v>
@@ -1001,7 +1001,7 @@
         <v>Available</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G21" t="str">
         <v>2.67</v>
@@ -1030,7 +1030,7 @@
         <v>Available</v>
       </c>
       <c r="F22" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
         <v>2.67</v>
@@ -1059,7 +1059,7 @@
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G23" t="str">
         <v>7.5</v>
@@ -1088,7 +1088,7 @@
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G24" t="str">
         <v>0.5</v>
@@ -1117,7 +1117,7 @@
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v/>
+        <v>08:30-21:30</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1146,7 +1146,7 @@
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G26" t="str">
         <v>7.5</v>
@@ -1175,7 +1175,7 @@
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>08:30-14:30</v>
       </c>
       <c r="G27" t="str">
         <v>7.5</v>
@@ -1205,7 +1205,7 @@
         <v>Available</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G28" t="str">
         <v>4</v>
@@ -1234,7 +1234,7 @@
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G29" t="str">
         <v>4</v>
@@ -1263,7 +1263,7 @@
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G30" t="str">
         <v>4</v>
@@ -1292,7 +1292,7 @@
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G31" t="str">
         <v>4</v>
@@ -1321,7 +1321,7 @@
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G32" t="str">
         <v>4</v>
@@ -1350,7 +1350,7 @@
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>09:15-14:45</v>
       </c>
       <c r="G33" t="str">
         <v>2.8</v>
@@ -1379,7 +1379,7 @@
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>09:15-11:30</v>
       </c>
       <c r="G34" t="str">
         <v>2.8</v>
@@ -1408,7 +1408,7 @@
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>09:15-14:45</v>
       </c>
       <c r="G35" t="str">
         <v>2.8</v>
@@ -1437,7 +1437,7 @@
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v/>
+        <v>09:15-11:30</v>
       </c>
       <c r="G36" t="str">
         <v>2.8</v>
@@ -1466,7 +1466,7 @@
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v/>
+        <v>09:15-10:15</v>
       </c>
       <c r="G37" t="str">
         <v>2.8</v>
@@ -1495,7 +1495,7 @@
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G38" t="str">
         <v>10</v>
@@ -1524,7 +1524,7 @@
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G39" t="str">
         <v>10</v>
@@ -1553,7 +1553,7 @@
         <v>Available</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
         <v>7.5</v>
@@ -1582,7 +1582,7 @@
         <v>Available</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
         <v>7.5</v>
@@ -1611,7 +1611,7 @@
         <v>Available</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
         <v>7.5</v>
@@ -1640,7 +1640,7 @@
         <v>Available</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G43" t="str">
         <v>7.5</v>
@@ -1669,7 +1669,7 @@
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G44" t="str">
         <v>5.33</v>
@@ -1698,7 +1698,7 @@
         <v>Available</v>
       </c>
       <c r="F45" t="str">
-        <v/>
+        <v>08:00-17:45</v>
       </c>
       <c r="G45" t="str">
         <v>5.33</v>
@@ -1727,7 +1727,7 @@
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v/>
+        <v>08:00-17:45</v>
       </c>
       <c r="G46" t="str">
         <v>5.33</v>
@@ -1756,7 +1756,7 @@
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G47" t="str">
         <v>4</v>
@@ -1785,7 +1785,7 @@
         <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G48" t="str">
         <v>4</v>
@@ -1814,7 +1814,7 @@
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G49" t="str">
         <v>4</v>
@@ -1843,7 +1843,7 @@
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="G50" t="str">
         <v>4</v>
@@ -1872,7 +1872,7 @@
         <v>Available</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
         <v>10</v>
@@ -1901,7 +1901,7 @@
         <v>Available</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
         <v>10</v>
@@ -1930,7 +1930,7 @@
         <v>Available</v>
       </c>
       <c r="F53" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
         <v>9</v>
@@ -1959,7 +1959,7 @@
         <v>Available</v>
       </c>
       <c r="F54" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
         <v>9</v>
@@ -1988,7 +1988,7 @@
         <v>Available</v>
       </c>
       <c r="F55" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
         <v>9</v>
@@ -2017,7 +2017,7 @@
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G56" t="str">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G57" t="str">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="G58" t="str">
         <v>7.5</v>
@@ -2104,7 +2104,7 @@
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G59" t="str">
         <v>7.5</v>
@@ -2133,7 +2133,7 @@
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G60" t="str">
         <v>7.5</v>
@@ -2162,7 +2162,7 @@
         <v>Available</v>
       </c>
       <c r="F61" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
         <v>7.5</v>
@@ -2191,7 +2191,7 @@
         <v>Available</v>
       </c>
       <c r="F62" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G62" t="str">
         <v>7.5</v>
@@ -2220,7 +2220,7 @@
         <v>Available</v>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G63" t="str">
         <v>7.5</v>
@@ -2249,7 +2249,7 @@
         <v>Available</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G64" t="str">
         <v>7.5</v>
@@ -2278,7 +2278,7 @@
         <v>Available</v>
       </c>
       <c r="F65" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G65" t="str">
         <v>7.5</v>
@@ -2307,7 +2307,7 @@
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G66" t="str">
         <v>6</v>
@@ -2336,7 +2336,7 @@
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G67" t="str">
         <v>6</v>
@@ -2365,7 +2365,7 @@
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G68" t="str">
         <v>6</v>
@@ -2394,7 +2394,7 @@
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G69" t="str">
         <v>6</v>
@@ -2423,7 +2423,7 @@
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G70" t="str">
         <v>6</v>
@@ -2452,7 +2452,7 @@
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2481,7 +2481,7 @@
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G72" t="str">
         <v>3.2</v>
@@ -2510,7 +2510,7 @@
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G73" t="str">
         <v>3.2</v>
@@ -2539,7 +2539,7 @@
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G74" t="str">
         <v>3.2</v>
@@ -2568,7 +2568,7 @@
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G75" t="str">
         <v>3.2</v>
@@ -2597,7 +2597,7 @@
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G76" t="str">
         <v>6</v>
@@ -2626,7 +2626,7 @@
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G77" t="str">
         <v>6</v>
@@ -2655,7 +2655,7 @@
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G78" t="str">
         <v>6</v>
@@ -2684,7 +2684,7 @@
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G79" t="str">
         <v>6</v>
@@ -2713,7 +2713,7 @@
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="G80" t="str">
         <v>6</v>
@@ -2742,7 +2742,7 @@
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v/>
+        <v>08:00-17:15</v>
       </c>
       <c r="G81" t="str">
         <v>5.33</v>
@@ -2771,7 +2771,7 @@
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v/>
+        <v>08:00-13:00</v>
       </c>
       <c r="G82" t="str">
         <v>5.33</v>
@@ -2800,7 +2800,7 @@
         <v>Available</v>
       </c>
       <c r="F83" t="str">
-        <v/>
+        <v>08:00-18:00</v>
       </c>
       <c r="G83" t="str">
         <v>5.33</v>
@@ -2829,7 +2829,7 @@
         <v>Available</v>
       </c>
       <c r="F84" t="str">
-        <v/>
+        <v>09:15-21:30</v>
       </c>
       <c r="G84" t="str">
         <v>3.2</v>
@@ -2858,7 +2858,7 @@
         <v>Available</v>
       </c>
       <c r="F85" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="G85" t="str">
         <v>3.2</v>
@@ -2887,7 +2887,7 @@
         <v>Available</v>
       </c>
       <c r="F86" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="G86" t="str">
         <v>3.2</v>
@@ -2916,7 +2916,7 @@
         <v>Available</v>
       </c>
       <c r="F87" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="G87" t="str">
         <v>3.2</v>
@@ -2945,7 +2945,7 @@
         <v>Available</v>
       </c>
       <c r="F88" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="G88" t="str">
         <v>3.2</v>
@@ -2974,7 +2974,7 @@
         <v>Available</v>
       </c>
       <c r="F89" t="str">
-        <v/>
+        <v>09:15-10:15</v>
       </c>
       <c r="G89" t="str">
         <v>3.43</v>
@@ -3003,7 +3003,7 @@
         <v>Available</v>
       </c>
       <c r="F90" t="str">
-        <v/>
+        <v>09:15-16:15</v>
       </c>
       <c r="G90" t="str">
         <v>1.43</v>
@@ -3032,7 +3032,7 @@
         <v>Available</v>
       </c>
       <c r="F91" t="str">
-        <v/>
+        <v>09:15-16:30</v>
       </c>
       <c r="G91" t="str">
         <v>1.43</v>
@@ -3061,7 +3061,7 @@
         <v>Available</v>
       </c>
       <c r="F92" t="str">
-        <v/>
+        <v>09:15-16:15</v>
       </c>
       <c r="G92" t="str">
         <v>3.43</v>
@@ -3090,7 +3090,7 @@
         <v>Available</v>
       </c>
       <c r="F93" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="G93" t="str">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>Available</v>
       </c>
       <c r="F94" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G94" t="str">
         <v>6</v>
@@ -3148,7 +3148,7 @@
         <v>Available</v>
       </c>
       <c r="F95" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G95" t="str">
         <v>6</v>
@@ -3177,7 +3177,7 @@
         <v>Available</v>
       </c>
       <c r="F96" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="G96" t="str">
         <v>6</v>
@@ -3206,7 +3206,7 @@
         <v>Available</v>
       </c>
       <c r="F97" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G97" t="str">
         <v>6</v>
@@ -3235,7 +3235,7 @@
         <v>Available</v>
       </c>
       <c r="F98" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="G98" t="str">
         <v>6</v>
@@ -3514,7 +3514,7 @@
         <v>Available</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E2" t="str">
         <v>7.5</v>
@@ -3540,7 +3540,7 @@
         <v>Available</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E3" t="str">
         <v>4</v>
@@ -3566,7 +3566,7 @@
         <v>Available</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>08:00-17:45</v>
       </c>
       <c r="E4" t="str">
         <v>5.33</v>
@@ -3592,7 +3592,7 @@
         <v>Holiday</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E5" t="str">
         <v>9</v>
@@ -3618,7 +3618,7 @@
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E6" t="str">
         <v>9</v>
@@ -3644,7 +3644,7 @@
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E7" t="str">
         <v>10</v>
@@ -3670,7 +3670,7 @@
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>10:30-14:00</v>
       </c>
       <c r="E8" t="str">
         <v>3.2</v>
@@ -3696,7 +3696,7 @@
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>09:15-10:15</v>
       </c>
       <c r="E9" t="str">
         <v>2.8</v>
@@ -3722,7 +3722,7 @@
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>08:30-14:30</v>
       </c>
       <c r="E10" t="str">
         <v>7.5</v>
@@ -3749,7 +3749,7 @@
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E11" t="str">
         <v>6</v>
@@ -3775,7 +3775,7 @@
         <v>Available</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E12" t="str">
         <v>3.2</v>
@@ -3801,7 +3801,7 @@
         <v>Holiday</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="E13" t="str">
         <v>3.43</v>
@@ -3827,7 +3827,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="E14" t="str">
         <v>3.43</v>
@@ -3854,7 +3854,7 @@
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="E15" t="str">
         <v>3.43</v>
@@ -3880,7 +3880,7 @@
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E16" t="str">
         <v>7.5</v>
@@ -3906,7 +3906,7 @@
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="E17" t="str">
         <v>3.2</v>
@@ -3932,7 +3932,7 @@
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>08:00-13:00</v>
       </c>
       <c r="E18" t="str">
         <v>5.33</v>
@@ -3958,7 +3958,7 @@
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E19" t="str">
         <v>6</v>
@@ -3984,7 +3984,7 @@
         <v>Available</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
         <v>7.5</v>
@@ -4010,7 +4010,7 @@
         <v>Holiday</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E21" t="str">
         <v>9</v>
@@ -4036,7 +4036,7 @@
         <v>Available</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E22" t="str">
         <v>9</v>
@@ -4062,7 +4062,7 @@
         <v>Available</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E23" t="str">
         <v>6</v>
@@ -4088,7 +4088,7 @@
         <v>Holiday</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="E24" t="str">
         <v>3.43</v>
@@ -4114,7 +4114,7 @@
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E25" t="str">
         <v>4</v>
@@ -4140,7 +4140,7 @@
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E26" t="str">
         <v>2.67</v>
@@ -4166,7 +4166,7 @@
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E27" t="str">
         <v>10</v>
@@ -4192,7 +4192,7 @@
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E28" t="str">
         <v>7.5</v>
@@ -4218,7 +4218,7 @@
         <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>08:00-17:45</v>
       </c>
       <c r="E29" t="str">
         <v>5.33</v>
@@ -4244,7 +4244,7 @@
         <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E30" t="str">
         <v>6</v>
@@ -4270,7 +4270,7 @@
         <v>Holiday</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>09:15-17:00</v>
       </c>
       <c r="E31" t="str">
         <v>3.43</v>
@@ -4296,7 +4296,7 @@
         <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E32" t="str">
         <v>4</v>
@@ -4322,7 +4322,7 @@
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>08:00-18:00</v>
       </c>
       <c r="E33" t="str">
         <v>5.33</v>
@@ -4348,7 +4348,7 @@
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E34" t="str">
         <v>2.67</v>
@@ -4374,7 +4374,7 @@
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E35" t="str">
         <v>10</v>
@@ -4400,7 +4400,7 @@
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E36" t="str">
         <v>7.5</v>
@@ -4426,7 +4426,7 @@
         <v>Available</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E37" t="str">
         <v>4</v>
@@ -4452,7 +4452,7 @@
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E38" t="str">
         <v>7.5</v>
@@ -4478,7 +4478,7 @@
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E39" t="str">
         <v>9</v>
@@ -4504,7 +4504,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4530,7 +4530,7 @@
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>09:15-11:30</v>
       </c>
       <c r="E41" t="str">
         <v>2.8</v>
@@ -4556,7 +4556,7 @@
         <v>Available</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E42" t="str">
         <v>6</v>
@@ -4582,7 +4582,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>08:00-15:00</v>
       </c>
       <c r="E43" t="str">
         <v>7.5</v>
@@ -4609,7 +4609,7 @@
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E44" t="str">
         <v>7.5</v>
@@ -4635,7 +4635,7 @@
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E45" t="str">
         <v>6</v>
@@ -4661,7 +4661,7 @@
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E46" t="str">
         <v>3.2</v>
@@ -4687,7 +4687,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="E47" t="str">
         <v>3.43</v>
@@ -4713,7 +4713,7 @@
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>09:15-16:15</v>
       </c>
       <c r="E48" t="str">
         <v>3.43</v>
@@ -4739,7 +4739,7 @@
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="E49" t="str">
         <v>7.5</v>
@@ -4765,7 +4765,7 @@
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="E50" t="str">
         <v>3.2</v>
@@ -4791,7 +4791,7 @@
         <v>Available</v>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
         <v>2.67</v>
@@ -4817,7 +4817,7 @@
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E52" t="str">
         <v>6</v>
@@ -4843,7 +4843,7 @@
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E53" t="str">
         <v>7.5</v>
@@ -4869,7 +4869,7 @@
         <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E54" t="str">
         <v>4</v>
@@ -4895,7 +4895,7 @@
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E55" t="str">
         <v>9</v>
@@ -4921,7 +4921,7 @@
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="E56" t="str">
         <v>3.2</v>
@@ -4947,7 +4947,7 @@
         <v>Available</v>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>09:15-14:45</v>
       </c>
       <c r="E57" t="str">
         <v>2.8</v>
@@ -4973,7 +4973,7 @@
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E58" t="str">
         <v>6</v>
@@ -4999,7 +4999,7 @@
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v/>
+        <v>08:30-21:30</v>
       </c>
       <c r="E59" t="str">
         <v>7.5</v>
@@ -5025,7 +5025,7 @@
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E60" t="str">
         <v>6</v>
@@ -5051,7 +5051,7 @@
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E61" t="str">
         <v>3.2</v>
@@ -5077,7 +5077,7 @@
         <v>Other Unavailable</v>
       </c>
       <c r="D62" t="str">
-        <v/>
+        <v>10:30-12:30</v>
       </c>
       <c r="E62" t="str">
         <v>3.43</v>
@@ -5104,7 +5104,7 @@
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v/>
+        <v>09:15-16:30</v>
       </c>
       <c r="E63" t="str">
         <v>3.43</v>
@@ -5130,7 +5130,7 @@
         <v>Available</v>
       </c>
       <c r="D64" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E64" t="str">
         <v>7.5</v>
@@ -5156,7 +5156,7 @@
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E65" t="str">
         <v>4</v>
@@ -5182,7 +5182,7 @@
         <v>Available</v>
       </c>
       <c r="D66" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="E66" t="str">
         <v>3.2</v>
@@ -5208,7 +5208,7 @@
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E67" t="str">
         <v>2.67</v>
@@ -5234,7 +5234,7 @@
         <v>Available</v>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E68" t="str">
         <v>6</v>
@@ -5260,7 +5260,7 @@
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E69" t="str">
         <v>4</v>
@@ -5286,7 +5286,7 @@
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E70" t="str">
         <v>7.5</v>
@@ -5312,7 +5312,7 @@
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v/>
+        <v>10:30-14:00</v>
       </c>
       <c r="E71" t="str">
         <v>3.2</v>
@@ -5338,7 +5338,7 @@
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v/>
+        <v>09:15-14:45</v>
       </c>
       <c r="E72" t="str">
         <v>2.8</v>
@@ -5364,7 +5364,7 @@
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E73" t="str">
         <v>6</v>
@@ -5390,7 +5390,7 @@
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E74" t="str">
         <v>7.5</v>
@@ -5416,7 +5416,7 @@
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E75" t="str">
         <v>6</v>
@@ -5442,7 +5442,7 @@
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E76" t="str">
         <v>3.2</v>
@@ -5468,7 +5468,7 @@
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v/>
+        <v>09:15-10:15</v>
       </c>
       <c r="E77" t="str">
         <v>3.43</v>
@@ -5494,7 +5494,7 @@
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v/>
+        <v>08:00-15:15</v>
       </c>
       <c r="E78" t="str">
         <v>4</v>
@@ -5520,7 +5520,7 @@
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>09:15-21:30</v>
       </c>
       <c r="E79" t="str">
         <v>3.2</v>
@@ -5546,7 +5546,7 @@
         <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D80" t="str">
-        <v/>
+        <v>10:20-12:50</v>
       </c>
       <c r="E80" t="str">
         <v>2.67</v>
@@ -5572,7 +5572,7 @@
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E81" t="str">
         <v>2.67</v>
@@ -5598,7 +5598,7 @@
         <v>Available</v>
       </c>
       <c r="D82" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E82" t="str">
         <v>6</v>
@@ -5624,7 +5624,7 @@
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E83" t="str">
         <v>7.5</v>
@@ -5650,7 +5650,7 @@
         <v>Available</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E84" t="str">
         <v>4</v>
@@ -5676,7 +5676,7 @@
         <v>Available</v>
       </c>
       <c r="D85" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E85" t="str">
         <v>5.33</v>
@@ -5702,7 +5702,7 @@
         <v>Available</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E86" t="str">
         <v>9</v>
@@ -5728,7 +5728,7 @@
         <v>Available</v>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E87" t="str">
         <v>10</v>
@@ -5754,7 +5754,7 @@
         <v>Available</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>09:15-15:15</v>
       </c>
       <c r="E88" t="str">
         <v>3.2</v>
@@ -5780,7 +5780,7 @@
         <v>Available</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>09:15-11:30</v>
       </c>
       <c r="E89" t="str">
         <v>2.8</v>
@@ -5806,7 +5806,7 @@
         <v>Available</v>
       </c>
       <c r="D90" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E90" t="str">
         <v>6</v>
@@ -5832,7 +5832,7 @@
         <v>Available</v>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E91" t="str">
         <v>7.5</v>
@@ -5858,7 +5858,7 @@
         <v>Available</v>
       </c>
       <c r="D92" t="str">
-        <v/>
+        <v>09:15-15:00</v>
       </c>
       <c r="E92" t="str">
         <v>3.2</v>
@@ -5884,7 +5884,7 @@
         <v>Available</v>
       </c>
       <c r="D93" t="str">
-        <v/>
+        <v>09:15-16:15</v>
       </c>
       <c r="E93" t="str">
         <v>3.43</v>
@@ -5910,7 +5910,7 @@
         <v>Available</v>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>08:00-21:30</v>
       </c>
       <c r="E94" t="str">
         <v>7.5</v>
@@ -5936,7 +5936,7 @@
         <v>Available</v>
       </c>
       <c r="D95" t="str">
-        <v/>
+        <v>16:45-21:30</v>
       </c>
       <c r="E95" t="str">
         <v>3.2</v>
@@ -5962,7 +5962,7 @@
         <v>Available</v>
       </c>
       <c r="D96" t="str">
-        <v/>
+        <v>08:00-17:15</v>
       </c>
       <c r="E96" t="str">
         <v>5.33</v>
@@ -5988,7 +5988,7 @@
         <v>Available</v>
       </c>
       <c r="D97" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E97" t="str">
         <v>2.67</v>
@@ -6014,7 +6014,7 @@
         <v>Available</v>
       </c>
       <c r="D98" t="str">
-        <v/>
+        <v>09:15-14:00</v>
       </c>
       <c r="E98" t="str">
         <v>6</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3289,10 +3289,10 @@
         <v>2025-09-01</v>
       </c>
       <c r="B2" t="str">
-        <v>57</v>
+        <v>56.83</v>
       </c>
       <c r="C2" t="str">
-        <v>57</v>
+        <v>56.83</v>
       </c>
       <c r="D2" t="str">
         <v>2.5</v>
@@ -3304,7 +3304,7 @@
         <v>69</v>
       </c>
       <c r="G2" t="str">
-        <v>-12</v>
+        <v>-12.17</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3315,10 +3315,10 @@
         <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>70.5</v>
+        <v>68.57</v>
       </c>
       <c r="C3" t="str">
-        <v>70.5</v>
+        <v>68.57</v>
       </c>
       <c r="D3" t="str">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>68</v>
       </c>
       <c r="G3" t="str">
-        <v>2.5</v>
+        <v>0.57</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -3341,10 +3341,10 @@
         <v>2025-09-03</v>
       </c>
       <c r="B4" t="str">
-        <v>74</v>
+        <v>72.57</v>
       </c>
       <c r="C4" t="str">
-        <v>74</v>
+        <v>72.57</v>
       </c>
       <c r="D4" t="str">
         <v>2</v>
@@ -3356,7 +3356,7 @@
         <v>82</v>
       </c>
       <c r="G4" t="str">
-        <v>-8</v>
+        <v>-9.43</v>
       </c>
       <c r="H4" t="str">
         <v>Shortage</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,16 +430,2833 @@
         <v>Notes</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B2" t="str">
+        <v>45</v>
+      </c>
+      <c r="C2" t="str">
+        <v>9</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F2" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G2" t="str">
+        <v>9</v>
+      </c>
+      <c r="H2" t="str">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B3" t="str">
+        <v>45</v>
+      </c>
+      <c r="C3" t="str">
+        <v>9</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F3" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G3" t="str">
+        <v>9</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B4" t="str">
+        <v>24</v>
+      </c>
+      <c r="C4" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F4" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G4" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H4" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B5" t="str">
+        <v>24</v>
+      </c>
+      <c r="C5" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F5" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G5" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H5" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B6" t="str">
+        <v>24</v>
+      </c>
+      <c r="C6" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="F6" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G6" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H6" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B7" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C7" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="F7" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="G7" t="str">
+        <v>7</v>
+      </c>
+      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B8" t="str">
+        <v>24</v>
+      </c>
+      <c r="C8" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="F8" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2</v>
+      </c>
+      <c r="H8" t="str">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B9" t="str">
+        <v>24</v>
+      </c>
+      <c r="C9" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="F9" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2</v>
+      </c>
+      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B10" t="str">
+        <v>24</v>
+      </c>
+      <c r="C10" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="F10" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2</v>
+      </c>
+      <c r="H10" t="str">
+        <v>0</v>
+      </c>
+      <c r="I10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B11" t="str">
+        <v>16</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Pre-Agreed Appointment</v>
+      </c>
+      <c r="F11" t="str">
+        <v>10:20-12:50</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B12" t="str">
+        <v>16</v>
+      </c>
+      <c r="C12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10:30-14:00</v>
+      </c>
+      <c r="G12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B13" t="str">
+        <v>16</v>
+      </c>
+      <c r="C13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F13" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="G13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H13" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B14" t="str">
+        <v>16</v>
+      </c>
+      <c r="C14" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F14" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="G14" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H14" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B15" t="str">
+        <v>16</v>
+      </c>
+      <c r="C15" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F15" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="G15" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H15" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="B16" t="str">
+        <v>16</v>
+      </c>
+      <c r="C16" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10:30-14:00</v>
+      </c>
+      <c r="G16" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H16" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B17" t="str">
+        <v>16</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F17" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G17" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="H17" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B18" t="str">
+        <v>16</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F18" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B19" t="str">
+        <v>16</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F19" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B20" t="str">
+        <v>16</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F20" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B21" t="str">
+        <v>16</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F21" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B22" t="str">
+        <v>16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F22" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B23" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F23" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H23" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B24" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C24" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F24" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="H24" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B25" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C25" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F25" t="str">
+        <v>08:30-21:30</v>
+      </c>
+      <c r="G25" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H25" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B26" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F26" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G26" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H26" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B27" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F27" t="str">
+        <v>08:30-14:30</v>
+      </c>
+      <c r="G27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I27" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="B28" t="str">
+        <v>20</v>
+      </c>
+      <c r="C28" t="str">
+        <v>4</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F28" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G28" t="str">
+        <v>4</v>
+      </c>
+      <c r="H28" t="str">
+        <v>4</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="B29" t="str">
+        <v>20</v>
+      </c>
+      <c r="C29" t="str">
+        <v>4</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F29" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G29" t="str">
+        <v>4</v>
+      </c>
+      <c r="H29" t="str">
+        <v>4</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="B30" t="str">
+        <v>20</v>
+      </c>
+      <c r="C30" t="str">
+        <v>4</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F30" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G30" t="str">
+        <v>4</v>
+      </c>
+      <c r="H30" t="str">
+        <v>4</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="B31" t="str">
+        <v>20</v>
+      </c>
+      <c r="C31" t="str">
+        <v>4</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F31" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G31" t="str">
+        <v>4</v>
+      </c>
+      <c r="H31" t="str">
+        <v>4</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="B32" t="str">
+        <v>20</v>
+      </c>
+      <c r="C32" t="str">
+        <v>4</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F32" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G32" t="str">
+        <v>4</v>
+      </c>
+      <c r="H32" t="str">
+        <v>4</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="B33" t="str">
+        <v>14</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F33" t="str">
+        <v>09:15-14:45</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H33" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="B34" t="str">
+        <v>14</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F34" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H34" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="B35" t="str">
+        <v>14</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F35" t="str">
+        <v>09:15-14:45</v>
+      </c>
+      <c r="G35" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H35" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="B36" t="str">
+        <v>14</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F36" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="G36" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H36" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="B37" t="str">
+        <v>14</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F37" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="G37" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H37" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="B38" t="str">
+        <v>20</v>
+      </c>
+      <c r="C38" t="str">
+        <v>10</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F38" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G38" t="str">
+        <v>10</v>
+      </c>
+      <c r="H38" t="str">
+        <v>10</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="B39" t="str">
+        <v>20</v>
+      </c>
+      <c r="C39" t="str">
+        <v>10</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F39" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G39" t="str">
+        <v>10</v>
+      </c>
+      <c r="H39" t="str">
+        <v>10</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="B40" t="str">
+        <v>30</v>
+      </c>
+      <c r="C40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F40" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H40" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="B41" t="str">
+        <v>30</v>
+      </c>
+      <c r="C41" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F41" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G41" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H41" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="B42" t="str">
+        <v>30</v>
+      </c>
+      <c r="C42" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F42" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G42" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H42" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="B43" t="str">
+        <v>30</v>
+      </c>
+      <c r="C43" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F43" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G43" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H43" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="B44" t="str">
+        <v>16</v>
+      </c>
+      <c r="C44" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F44" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G44" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H44" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="B45" t="str">
+        <v>16</v>
+      </c>
+      <c r="C45" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F45" t="str">
+        <v>08:00-17:45</v>
+      </c>
+      <c r="G45" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H45" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="B46" t="str">
+        <v>16</v>
+      </c>
+      <c r="C46" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F46" t="str">
+        <v>08:00-17:45</v>
+      </c>
+      <c r="G46" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H46" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="B47" t="str">
+        <v>16</v>
+      </c>
+      <c r="C47" t="str">
+        <v>4</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F47" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G47" t="str">
+        <v>4</v>
+      </c>
+      <c r="H47" t="str">
+        <v>4</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="B48" t="str">
+        <v>16</v>
+      </c>
+      <c r="C48" t="str">
+        <v>4</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F48" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G48" t="str">
+        <v>4</v>
+      </c>
+      <c r="H48" t="str">
+        <v>4</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="B49" t="str">
+        <v>16</v>
+      </c>
+      <c r="C49" t="str">
+        <v>4</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F49" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G49" t="str">
+        <v>4</v>
+      </c>
+      <c r="H49" t="str">
+        <v>4</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="B50" t="str">
+        <v>16</v>
+      </c>
+      <c r="C50" t="str">
+        <v>4</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F50" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="G50" t="str">
+        <v>4</v>
+      </c>
+      <c r="H50" t="str">
+        <v>4</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="B51" t="str">
+        <v>20</v>
+      </c>
+      <c r="C51" t="str">
+        <v>10</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F51" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G51" t="str">
+        <v>10</v>
+      </c>
+      <c r="H51" t="str">
+        <v>10</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="B52" t="str">
+        <v>20</v>
+      </c>
+      <c r="C52" t="str">
+        <v>10</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F52" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G52" t="str">
+        <v>10</v>
+      </c>
+      <c r="H52" t="str">
+        <v>10</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B53" t="str">
+        <v>45</v>
+      </c>
+      <c r="C53" t="str">
+        <v>9</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F53" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G53" t="str">
+        <v>9</v>
+      </c>
+      <c r="H53" t="str">
+        <v>9</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B54" t="str">
+        <v>45</v>
+      </c>
+      <c r="C54" t="str">
+        <v>9</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F54" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G54" t="str">
+        <v>9</v>
+      </c>
+      <c r="H54" t="str">
+        <v>9</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B55" t="str">
+        <v>45</v>
+      </c>
+      <c r="C55" t="str">
+        <v>9</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F55" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G55" t="str">
+        <v>9</v>
+      </c>
+      <c r="H55" t="str">
+        <v>9</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B56" t="str">
+        <v>45</v>
+      </c>
+      <c r="C56" t="str">
+        <v>9</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F56" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G56" t="str">
+        <v>0</v>
+      </c>
+      <c r="H56" t="str">
+        <v>0</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="B57" t="str">
+        <v>45</v>
+      </c>
+      <c r="C57" t="str">
+        <v>9</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F57" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G57" t="str">
+        <v>0</v>
+      </c>
+      <c r="H57" t="str">
+        <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="B58" t="str">
+        <v>30</v>
+      </c>
+      <c r="C58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F58" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H58" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="B59" t="str">
+        <v>30</v>
+      </c>
+      <c r="C59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F59" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="B60" t="str">
+        <v>30</v>
+      </c>
+      <c r="C60" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F60" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G60" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H60" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="B61" t="str">
+        <v>30</v>
+      </c>
+      <c r="C61" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F61" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G61" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H61" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="B62" t="str">
+        <v>30</v>
+      </c>
+      <c r="C62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F62" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="B63" t="str">
+        <v>30</v>
+      </c>
+      <c r="C63" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F63" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G63" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H63" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="B64" t="str">
+        <v>30</v>
+      </c>
+      <c r="C64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F64" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="B65" t="str">
+        <v>30</v>
+      </c>
+      <c r="C65" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F65" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G65" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H65" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="B66" t="str">
+        <v>30</v>
+      </c>
+      <c r="C66" t="str">
+        <v>6</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F66" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G66" t="str">
+        <v>6</v>
+      </c>
+      <c r="H66" t="str">
+        <v>6</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="B67" t="str">
+        <v>30</v>
+      </c>
+      <c r="C67" t="str">
+        <v>6</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F67" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G67" t="str">
+        <v>6</v>
+      </c>
+      <c r="H67" t="str">
+        <v>6</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="B68" t="str">
+        <v>30</v>
+      </c>
+      <c r="C68" t="str">
+        <v>6</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F68" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G68" t="str">
+        <v>6</v>
+      </c>
+      <c r="H68" t="str">
+        <v>6</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="B69" t="str">
+        <v>30</v>
+      </c>
+      <c r="C69" t="str">
+        <v>6</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F69" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G69" t="str">
+        <v>6</v>
+      </c>
+      <c r="H69" t="str">
+        <v>6</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="B70" t="str">
+        <v>30</v>
+      </c>
+      <c r="C70" t="str">
+        <v>6</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F70" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G70" t="str">
+        <v>6</v>
+      </c>
+      <c r="H70" t="str">
+        <v>6</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="B71" t="str">
+        <v>16</v>
+      </c>
+      <c r="C71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F71" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="B72" t="str">
+        <v>16</v>
+      </c>
+      <c r="C72" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F72" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G72" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H72" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="B73" t="str">
+        <v>16</v>
+      </c>
+      <c r="C73" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F73" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G73" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H73" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="B74" t="str">
+        <v>16</v>
+      </c>
+      <c r="C74" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F74" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G74" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H74" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="B75" t="str">
+        <v>16</v>
+      </c>
+      <c r="C75" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F75" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G75" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H75" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="B76" t="str">
+        <v>30</v>
+      </c>
+      <c r="C76" t="str">
+        <v>6</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F76" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G76" t="str">
+        <v>6</v>
+      </c>
+      <c r="H76" t="str">
+        <v>6</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="B77" t="str">
+        <v>30</v>
+      </c>
+      <c r="C77" t="str">
+        <v>6</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F77" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G77" t="str">
+        <v>6</v>
+      </c>
+      <c r="H77" t="str">
+        <v>6</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="B78" t="str">
+        <v>30</v>
+      </c>
+      <c r="C78" t="str">
+        <v>6</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F78" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G78" t="str">
+        <v>6</v>
+      </c>
+      <c r="H78" t="str">
+        <v>6</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="B79" t="str">
+        <v>30</v>
+      </c>
+      <c r="C79" t="str">
+        <v>6</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F79" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G79" t="str">
+        <v>6</v>
+      </c>
+      <c r="H79" t="str">
+        <v>6</v>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="B80" t="str">
+        <v>30</v>
+      </c>
+      <c r="C80" t="str">
+        <v>6</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F80" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G80" t="str">
+        <v>6</v>
+      </c>
+      <c r="H80" t="str">
+        <v>6</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="B81" t="str">
+        <v>16</v>
+      </c>
+      <c r="C81" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F81" t="str">
+        <v>08:00-17:15</v>
+      </c>
+      <c r="G81" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H81" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="B82" t="str">
+        <v>16</v>
+      </c>
+      <c r="C82" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F82" t="str">
+        <v>08:00-13:00</v>
+      </c>
+      <c r="G82" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H82" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="B83" t="str">
+        <v>16</v>
+      </c>
+      <c r="C83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F83" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="G83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B84" t="str">
+        <v>16</v>
+      </c>
+      <c r="C84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F84" t="str">
+        <v>09:15-21:30</v>
+      </c>
+      <c r="G84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B85" t="str">
+        <v>16</v>
+      </c>
+      <c r="C85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F85" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B86" t="str">
+        <v>16</v>
+      </c>
+      <c r="C86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F86" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B87" t="str">
+        <v>16</v>
+      </c>
+      <c r="C87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F87" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B88" t="str">
+        <v>16</v>
+      </c>
+      <c r="C88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F88" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B89" t="str">
+        <v>24</v>
+      </c>
+      <c r="C89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F89" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B90" t="str">
+        <v>24</v>
+      </c>
+      <c r="C90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F90" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B91" t="str">
+        <v>24</v>
+      </c>
+      <c r="C91" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F91" t="str">
+        <v>09:15-16:30</v>
+      </c>
+      <c r="G91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B92" t="str">
+        <v>24</v>
+      </c>
+      <c r="C92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F92" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B93" t="str">
+        <v>24</v>
+      </c>
+      <c r="C93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F93" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0</v>
+      </c>
+      <c r="H93" t="str">
+        <v>0</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B94" t="str">
+        <v>30</v>
+      </c>
+      <c r="C94" t="str">
+        <v>6</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F94" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G94" t="str">
+        <v>6</v>
+      </c>
+      <c r="H94" t="str">
+        <v>6</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B95" t="str">
+        <v>30</v>
+      </c>
+      <c r="C95" t="str">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F95" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G95" t="str">
+        <v>6</v>
+      </c>
+      <c r="H95" t="str">
+        <v>6</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B96" t="str">
+        <v>30</v>
+      </c>
+      <c r="C96" t="str">
+        <v>6</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F96" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G96" t="str">
+        <v>6</v>
+      </c>
+      <c r="H96" t="str">
+        <v>6</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B97" t="str">
+        <v>30</v>
+      </c>
+      <c r="C97" t="str">
+        <v>6</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F97" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G97" t="str">
+        <v>6</v>
+      </c>
+      <c r="H97" t="str">
+        <v>6</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B98" t="str">
+        <v>30</v>
+      </c>
+      <c r="C98" t="str">
+        <v>6</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G98" t="str">
+        <v>6</v>
+      </c>
+      <c r="H98" t="str">
+        <v>6</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -467,16 +3284,198 @@
         <v>Status</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>56.83</v>
+      </c>
+      <c r="C2" t="str">
+        <v>56.83</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E2" t="str">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v>69</v>
+      </c>
+      <c r="G2" t="str">
+        <v>-12.17</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Shortage</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>68.57</v>
+      </c>
+      <c r="C3" t="str">
+        <v>68.57</v>
+      </c>
+      <c r="D3" t="str">
+        <v>9</v>
+      </c>
+      <c r="E3" t="str">
+        <v>0</v>
+      </c>
+      <c r="F3" t="str">
+        <v>68</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0.57</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Sufficient</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>72.57</v>
+      </c>
+      <c r="C4" t="str">
+        <v>72.57</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <v>82</v>
+      </c>
+      <c r="G4" t="str">
+        <v>-9.43</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Shortage</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>86.66</v>
+      </c>
+      <c r="C5" t="str">
+        <v>86.66</v>
+      </c>
+      <c r="D5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <v>71</v>
+      </c>
+      <c r="G5" t="str">
+        <v>15.66</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Sufficient</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>71.56</v>
+      </c>
+      <c r="C6" t="str">
+        <v>71.56</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>12.43</v>
+      </c>
+      <c r="F6" t="str">
+        <v>55</v>
+      </c>
+      <c r="G6" t="str">
+        <v>16.56</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Sufficient</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>30.17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>30.17</v>
+      </c>
+      <c r="D7" t="str">
+        <v>0</v>
+      </c>
+      <c r="E7" t="str">
+        <v>12.43</v>
+      </c>
+      <c r="F7" t="str">
+        <v>43</v>
+      </c>
+      <c r="G7" t="str">
+        <v>-12.83</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Shortage</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>40.83</v>
+      </c>
+      <c r="C8" t="str">
+        <v>40.83</v>
+      </c>
+      <c r="D8" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F8" t="str">
+        <v>41</v>
+      </c>
+      <c r="G8" t="str">
+        <v>-0.17</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Shortage</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H98"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -504,9 +3503,2535 @@
         <v>Notes</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D2" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D3" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E3" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3" t="str">
+        <v>4</v>
+      </c>
+      <c r="G3" t="str">
+        <v>4</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D4" t="str">
+        <v>08:00-17:45</v>
+      </c>
+      <c r="E4" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F4" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G4" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D5" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E5" t="str">
+        <v>9</v>
+      </c>
+      <c r="F5" t="str">
+        <v>9</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D6" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E6" t="str">
+        <v>9</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D7" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>10</v>
+      </c>
+      <c r="F7" t="str">
+        <v>10</v>
+      </c>
+      <c r="G7" t="str">
+        <v>10</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D8" t="str">
+        <v>10:30-14:00</v>
+      </c>
+      <c r="E8" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G8" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D9" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D10" t="str">
+        <v>08:30-14:30</v>
+      </c>
+      <c r="E10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D11" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E11" t="str">
+        <v>6</v>
+      </c>
+      <c r="F11" t="str">
+        <v>6</v>
+      </c>
+      <c r="G11" t="str">
+        <v>6</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D12" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G12" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D13" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="E13" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F13" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D14" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="E14" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D15" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="E15" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D16" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E16" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F16" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B17" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D17" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E17" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F17" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G17" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D18" t="str">
+        <v>08:00-13:00</v>
+      </c>
+      <c r="E18" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G18" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D19" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E19" t="str">
+        <v>6</v>
+      </c>
+      <c r="F19" t="str">
+        <v>6</v>
+      </c>
+      <c r="G19" t="str">
+        <v>6</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D20" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E20" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F20" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G20" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D21" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E21" t="str">
+        <v>9</v>
+      </c>
+      <c r="F21" t="str">
+        <v>9</v>
+      </c>
+      <c r="G21" t="str">
+        <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D22" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E22" t="str">
+        <v>9</v>
+      </c>
+      <c r="F22" t="str">
+        <v>0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D23" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E23" t="str">
+        <v>6</v>
+      </c>
+      <c r="F23" t="str">
+        <v>6</v>
+      </c>
+      <c r="G23" t="str">
+        <v>6</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D24" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="E24" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D25" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E25" t="str">
+        <v>4</v>
+      </c>
+      <c r="F25" t="str">
+        <v>4</v>
+      </c>
+      <c r="G25" t="str">
+        <v>4</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B26" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D26" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2025-09-06</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D27" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E27" t="str">
+        <v>10</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+      <c r="G27" t="str">
+        <v>10</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D28" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D29" t="str">
+        <v>08:00-17:45</v>
+      </c>
+      <c r="E29" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G29" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D30" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E30" t="str">
+        <v>6</v>
+      </c>
+      <c r="F30" t="str">
+        <v>6</v>
+      </c>
+      <c r="G30" t="str">
+        <v>6</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Holiday</v>
+      </c>
+      <c r="D31" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="E31" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F31" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D32" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E32" t="str">
+        <v>4</v>
+      </c>
+      <c r="F32" t="str">
+        <v>4</v>
+      </c>
+      <c r="G32" t="str">
+        <v>4</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D33" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="E33" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G33" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B34" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D34" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Shawcross (NL), Emma</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D35" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E35" t="str">
+        <v>10</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+      <c r="G35" t="str">
+        <v>10</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D36" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E36" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F36" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G36" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D37" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E37" t="str">
+        <v>4</v>
+      </c>
+      <c r="F37" t="str">
+        <v>4</v>
+      </c>
+      <c r="G37" t="str">
+        <v>4</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D38" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E38" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F38" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G38" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D39" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E39" t="str">
+        <v>9</v>
+      </c>
+      <c r="F39" t="str">
+        <v>9</v>
+      </c>
+      <c r="G39" t="str">
+        <v>9</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D40" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E40" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F40" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G40" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D41" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F41" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G41" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D42" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E42" t="str">
+        <v>6</v>
+      </c>
+      <c r="F42" t="str">
+        <v>6</v>
+      </c>
+      <c r="G42" t="str">
+        <v>6</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D43" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="E43" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F43" t="str">
+        <v>7</v>
+      </c>
+      <c r="G43" t="str">
+        <v>0</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D44" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E44" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F44" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="G44" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D45" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E45" t="str">
+        <v>6</v>
+      </c>
+      <c r="F45" t="str">
+        <v>6</v>
+      </c>
+      <c r="G45" t="str">
+        <v>6</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D46" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E46" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F46" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G46" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D47" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="E47" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F47" t="str">
+        <v>2</v>
+      </c>
+      <c r="G47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D48" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="E48" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F48" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="G48" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D49" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E49" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F49" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G49" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B50" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D50" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E50" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F50" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G50" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B51" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D51" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F51" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G51" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D52" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E52" t="str">
+        <v>6</v>
+      </c>
+      <c r="F52" t="str">
+        <v>6</v>
+      </c>
+      <c r="G52" t="str">
+        <v>6</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D53" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E53" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F53" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G53" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D54" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E54" t="str">
+        <v>4</v>
+      </c>
+      <c r="F54" t="str">
+        <v>4</v>
+      </c>
+      <c r="G54" t="str">
+        <v>4</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D55" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E55" t="str">
+        <v>9</v>
+      </c>
+      <c r="F55" t="str">
+        <v>9</v>
+      </c>
+      <c r="G55" t="str">
+        <v>9</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D56" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D57" t="str">
+        <v>09:15-14:45</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F57" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G57" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D58" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E58" t="str">
+        <v>6</v>
+      </c>
+      <c r="F58" t="str">
+        <v>6</v>
+      </c>
+      <c r="G58" t="str">
+        <v>6</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D59" t="str">
+        <v>08:30-21:30</v>
+      </c>
+      <c r="E59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G59" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D60" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E60" t="str">
+        <v>6</v>
+      </c>
+      <c r="F60" t="str">
+        <v>6</v>
+      </c>
+      <c r="G60" t="str">
+        <v>6</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D61" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G61" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D62" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="E62" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F62" t="str">
+        <v>2</v>
+      </c>
+      <c r="G62" t="str">
+        <v>0</v>
+      </c>
+      <c r="H62" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D63" t="str">
+        <v>09:15-16:30</v>
+      </c>
+      <c r="E63" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F63" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="G63" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D64" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G64" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D65" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E65" t="str">
+        <v>4</v>
+      </c>
+      <c r="F65" t="str">
+        <v>4</v>
+      </c>
+      <c r="G65" t="str">
+        <v>4</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B66" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D66" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E66" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F66" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G66" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B67" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D67" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F67" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G67" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D68" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E68" t="str">
+        <v>6</v>
+      </c>
+      <c r="F68" t="str">
+        <v>6</v>
+      </c>
+      <c r="G68" t="str">
+        <v>6</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D69" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E69" t="str">
+        <v>4</v>
+      </c>
+      <c r="F69" t="str">
+        <v>4</v>
+      </c>
+      <c r="G69" t="str">
+        <v>4</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D70" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E70" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F70" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G70" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D71" t="str">
+        <v>10:30-14:00</v>
+      </c>
+      <c r="E71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G71" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D72" t="str">
+        <v>09:15-14:45</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G72" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D73" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E73" t="str">
+        <v>6</v>
+      </c>
+      <c r="F73" t="str">
+        <v>6</v>
+      </c>
+      <c r="G73" t="str">
+        <v>6</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D74" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E74" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F74" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G74" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D75" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E75" t="str">
+        <v>6</v>
+      </c>
+      <c r="F75" t="str">
+        <v>6</v>
+      </c>
+      <c r="G75" t="str">
+        <v>6</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D76" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E76" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F76" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G76" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D77" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="E77" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F77" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G77" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D78" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E78" t="str">
+        <v>4</v>
+      </c>
+      <c r="F78" t="str">
+        <v>4</v>
+      </c>
+      <c r="G78" t="str">
+        <v>4</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B79" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D79" t="str">
+        <v>09:15-21:30</v>
+      </c>
+      <c r="E79" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F79" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G79" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B80" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Pre-Agreed Appointment</v>
+      </c>
+      <c r="D80" t="str">
+        <v>10:20-12:50</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F80" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="G80" t="str">
+        <v>0</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B81" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D81" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F81" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="G81" t="str">
+        <v>0.17</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D82" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E82" t="str">
+        <v>6</v>
+      </c>
+      <c r="F82" t="str">
+        <v>6</v>
+      </c>
+      <c r="G82" t="str">
+        <v>6</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D83" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E83" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F83" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G83" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D84" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E84" t="str">
+        <v>4</v>
+      </c>
+      <c r="F84" t="str">
+        <v>4</v>
+      </c>
+      <c r="G84" t="str">
+        <v>4</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D85" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F85" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G85" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D86" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E86" t="str">
+        <v>9</v>
+      </c>
+      <c r="F86" t="str">
+        <v>9</v>
+      </c>
+      <c r="G86" t="str">
+        <v>9</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D87" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E87" t="str">
+        <v>10</v>
+      </c>
+      <c r="F87" t="str">
+        <v>10</v>
+      </c>
+      <c r="G87" t="str">
+        <v>10</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D88" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D89" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F89" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G89" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D90" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E90" t="str">
+        <v>6</v>
+      </c>
+      <c r="F90" t="str">
+        <v>6</v>
+      </c>
+      <c r="G90" t="str">
+        <v>6</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D91" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D92" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D93" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="E93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D94" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E94" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F94" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G94" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B95" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D95" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E95" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F95" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G95" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D96" t="str">
+        <v>08:00-17:15</v>
+      </c>
+      <c r="E96" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F96" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G96" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B97" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D97" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F97" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G97" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E98" t="str">
+        <v>6</v>
+      </c>
+      <c r="F98" t="str">
+        <v>6</v>
+      </c>
+      <c r="G98" t="str">
+        <v>6</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -34,7 +34,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -399,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I98"/>
+  <dimension ref="A1:I99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -711,74 +715,74 @@
         <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v>10:20-12:50</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B12" t="str">
         <v>16</v>
       </c>
       <c r="C12" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E12" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F12" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B13" t="str">
         <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E13" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F13" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H13" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="14">
@@ -792,13 +796,13 @@
         <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G14" t="str">
         <v>3.2</v>
@@ -807,7 +811,7 @@
         <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="15">
@@ -821,7 +825,7 @@
         <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
@@ -850,13 +854,13 @@
         <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G16" t="str">
         <v>3.2</v>
@@ -865,65 +869,65 @@
         <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G17" t="str">
-        <v>0.17</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>0.17</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B18" t="str">
         <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="19">
@@ -937,7 +941,7 @@
         <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -946,10 +950,10 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
         <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
@@ -966,7 +970,7 @@
         <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -975,13 +979,13 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
@@ -995,13 +999,13 @@
         <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
       </c>
       <c r="F21" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
         <v>2.67</v>
@@ -1010,7 +1014,7 @@
         <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="22">
@@ -1024,7 +1028,7 @@
         <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1044,28 +1048,28 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1073,28 +1077,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B24" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G24" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1111,13 +1115,13 @@
         <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:30-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1140,25 +1144,25 @@
         <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
     </row>
-    <row r="27" xml:space="preserve">
+    <row r="27">
       <c r="A27" t="str">
         <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
@@ -1169,81 +1173,81 @@
         <v>7.5</v>
       </c>
       <c r="D27" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F27" t="str">
+        <v>08:30-21:30</v>
+      </c>
+      <c r="G27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B28" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F28" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H28" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="B29" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="C29" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="D29" t="str">
         <v>2025-09-05</v>
       </c>
-      <c r="E27" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F27" t="str">
+      <c r="E29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F29" t="str">
         <v>08:30-14:30</v>
       </c>
-      <c r="G27" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H27" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="I27" t="str" xml:space="preserve">
+      <c r="G29" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H29" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="I29" t="str" xml:space="preserve">
         <v xml:space="preserve">Office hours
 Eilidh 27/08/2025</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="B28" t="str">
-        <v>20</v>
-      </c>
-      <c r="C28" t="str">
-        <v>4</v>
-      </c>
-      <c r="D28" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F28" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G28" t="str">
-        <v>4</v>
-      </c>
-      <c r="H28" t="str">
-        <v>4</v>
-      </c>
-      <c r="I28" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="B29" t="str">
-        <v>20</v>
-      </c>
-      <c r="C29" t="str">
-        <v>4</v>
-      </c>
-      <c r="D29" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E29" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F29" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G29" t="str">
-        <v>4</v>
-      </c>
-      <c r="H29" t="str">
-        <v>4</v>
-      </c>
-      <c r="I29" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="30">
@@ -1257,7 +1261,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
@@ -1286,7 +1290,7 @@
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
@@ -1315,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
@@ -1335,60 +1339,60 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B33" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>09:15-14:45</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B34" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>09:15-11:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="35">
@@ -1402,7 +1406,7 @@
         <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
@@ -1431,7 +1435,7 @@
         <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1460,13 +1464,13 @@
         <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>09:15-10:15</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G37" t="str">
         <v>2.8</v>
@@ -1480,74 +1484,74 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B38" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B39" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C39" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="G39" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="str">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B40" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1556,27 +1560,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B41" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1585,13 +1589,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="42">
@@ -1605,7 +1609,7 @@
         <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1634,7 +1638,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1654,16 +1658,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B44" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C44" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
@@ -1672,10 +1676,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G44" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1683,28 +1687,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B45" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C45" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
       </c>
       <c r="F45" t="str">
-        <v>08:00-17:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G45" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H45" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1712,28 +1716,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B46" t="str">
         <v>16</v>
       </c>
       <c r="C46" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-17:45</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G46" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1750,7 +1754,7 @@
         <v>4</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1779,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1808,7 +1812,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
@@ -1828,28 +1832,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B50" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C50" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G50" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="H50" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1863,7 +1867,7 @@
         <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="D51" t="str">
         <v>2025-09-04</v>
@@ -1875,10 +1879,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="H51" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1892,7 +1896,7 @@
         <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="D52" t="str">
         <v>2025-09-05</v>
@@ -1904,10 +1908,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="H52" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -3247,9 +3251,38 @@
         <v/>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B99" t="str">
+        <v>30</v>
+      </c>
+      <c r="C99" t="str">
+        <v>6</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Dependant Leave</v>
+      </c>
+      <c r="F99" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G99" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="H99" t="str">
+        <v>0</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3295,16 +3328,16 @@
         <v>56.83</v>
       </c>
       <c r="D2" t="str">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>69</v>
+        <v>77.55</v>
       </c>
       <c r="G2" t="str">
-        <v>-12.17</v>
+        <v>-20.72</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3315,25 +3348,25 @@
         <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>68.57</v>
+        <v>66.57</v>
       </c>
       <c r="C3" t="str">
-        <v>68.57</v>
+        <v>72.57</v>
       </c>
       <c r="D3" t="str">
-        <v>9</v>
+        <v>11.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>68</v>
+        <v>78.36</v>
       </c>
       <c r="G3" t="str">
-        <v>0.57</v>
+        <v>-5.79</v>
       </c>
       <c r="H3" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="4">
@@ -3353,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>82</v>
+        <v>69.07</v>
       </c>
       <c r="G4" t="str">
-        <v>-9.43</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="5">
@@ -3367,10 +3400,10 @@
         <v>2025-09-04</v>
       </c>
       <c r="B5" t="str">
-        <v>86.66</v>
+        <v>78</v>
       </c>
       <c r="C5" t="str">
-        <v>86.66</v>
+        <v>78</v>
       </c>
       <c r="D5" t="str">
         <v>0</v>
@@ -3379,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>71</v>
+        <v>66.58</v>
       </c>
       <c r="G5" t="str">
-        <v>15.66</v>
+        <v>11.42</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3393,10 +3426,10 @@
         <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>71.56</v>
+        <v>62.9</v>
       </c>
       <c r="C6" t="str">
-        <v>71.56</v>
+        <v>62.9</v>
       </c>
       <c r="D6" t="str">
         <v>2</v>
@@ -3405,10 +3438,10 @@
         <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>55</v>
+        <v>51.5</v>
       </c>
       <c r="G6" t="str">
-        <v>16.56</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3431,10 +3464,10 @@
         <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>43</v>
+        <v>42.75</v>
       </c>
       <c r="G7" t="str">
-        <v>-12.83</v>
+        <v>-12.58</v>
       </c>
       <c r="H7" t="str">
         <v>Shortage</v>
@@ -3445,22 +3478,22 @@
         <v>2025-09-07</v>
       </c>
       <c r="B8" t="str">
-        <v>40.83</v>
+        <v>32.83</v>
       </c>
       <c r="C8" t="str">
-        <v>40.83</v>
+        <v>32.83</v>
       </c>
       <c r="D8" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="E8" t="str">
         <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>-0.17</v>
+        <v>-7.17</v>
       </c>
       <c r="H8" t="str">
         <v>Shortage</v>
@@ -3475,7 +3508,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3560,25 +3593,25 @@
         <v>2025-09-05</v>
       </c>
       <c r="B4" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C4" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D4" t="str">
-        <v>08:00-17:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="G4" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
@@ -3589,7 +3622,7 @@
         <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C5" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D5" t="str">
         <v>08:00-21:30</v>
@@ -3598,13 +3631,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
         <v>0</v>
       </c>
       <c r="H5" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -3612,7 +3645,7 @@
         <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
@@ -3621,13 +3654,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E6" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="G6" t="str">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -3638,25 +3671,25 @@
         <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E7" t="str">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>10</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
@@ -3664,78 +3697,78 @@
         <v>2025-09-05</v>
       </c>
       <c r="B8" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
-    <row r="9">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>2025-09-05</v>
       </c>
       <c r="B9" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>09:15-10:15</v>
+        <v>08:30-14:30</v>
       </c>
       <c r="E9" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F9" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>7.5</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="str">
         <v>2025-09-05</v>
       </c>
       <c r="B10" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>08:30-14:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E10" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Office hours
-Eilidh 27/08/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3743,25 +3776,25 @@
         <v>2025-09-05</v>
       </c>
       <c r="B11" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E11" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F11" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="12">
@@ -3769,28 +3802,28 @@
         <v>2025-09-05</v>
       </c>
       <c r="B12" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D12" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E12" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="F12" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="G12" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>2025-09-05</v>
       </c>
@@ -3798,25 +3831,26 @@
         <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15-17:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E13" t="str">
         <v>3.43</v>
       </c>
       <c r="F13" t="str">
-        <v>3.43</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
         <v>0</v>
       </c>
-      <c r="H13" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="str">
         <v>2025-09-05</v>
       </c>
@@ -3824,23 +3858,22 @@
         <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E14" t="str">
         <v>3.43</v>
       </c>
       <c r="F14" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="str">
         <v>0</v>
       </c>
-      <c r="H14" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+      <c r="H14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3848,22 +3881,22 @@
         <v>2025-09-05</v>
       </c>
       <c r="B15" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E15" t="str">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -3874,22 +3907,22 @@
         <v>2025-09-05</v>
       </c>
       <c r="B16" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3900,22 +3933,22 @@
         <v>2025-09-05</v>
       </c>
       <c r="B17" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E17" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="F17" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3926,22 +3959,22 @@
         <v>2025-09-05</v>
       </c>
       <c r="B18" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E18" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="F18" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="G18" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3949,25 +3982,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B19" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -3978,25 +4011,25 @@
         <v>2025-09-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C20" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D20" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F20" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G20" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="21">
@@ -4007,7 +4040,7 @@
         <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C21" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D21" t="str">
         <v>08:00-21:30</v>
@@ -4016,13 +4049,13 @@
         <v>9</v>
       </c>
       <c r="F21" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G21" t="str">
         <v>0</v>
       </c>
       <c r="H21" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -4030,7 +4063,7 @@
         <v>2025-09-06</v>
       </c>
       <c r="B22" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C22" t="str">
         <v>Available</v>
@@ -4039,13 +4072,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E22" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -4056,25 +4089,25 @@
         <v>2025-09-06</v>
       </c>
       <c r="B23" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C23" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D23" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E23" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F23" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="G23" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="24">
@@ -4082,25 +4115,25 @@
         <v>2025-09-06</v>
       </c>
       <c r="B24" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C24" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E24" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="G24" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -4108,22 +4141,22 @@
         <v>2025-09-06</v>
       </c>
       <c r="B25" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -4134,7 +4167,7 @@
         <v>2025-09-06</v>
       </c>
       <c r="B26" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
@@ -4143,24 +4176,24 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E26" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F26" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="G26" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B27" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
@@ -4169,16 +4202,16 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E27" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F27" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -4186,7 +4219,7 @@
         <v>2025-09-07</v>
       </c>
       <c r="B28" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
@@ -4195,13 +4228,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E28" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F28" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -4212,25 +4245,25 @@
         <v>2025-09-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C29" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00-17:45</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E29" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="F29" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="G29" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="30">
@@ -4238,22 +4271,22 @@
         <v>2025-09-07</v>
       </c>
       <c r="B30" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C30" t="str">
         <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E30" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H30" t="str">
         <v/>
@@ -4264,25 +4297,25 @@
         <v>2025-09-07</v>
       </c>
       <c r="B31" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C31" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E31" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="F31" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="G31" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H31" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -4290,25 +4323,25 @@
         <v>2025-09-07</v>
       </c>
       <c r="B32" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C32" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D32" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E32" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G32" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="33">
@@ -4316,22 +4349,22 @@
         <v>2025-09-07</v>
       </c>
       <c r="B33" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E33" t="str">
-        <v>5.33</v>
+        <v>2.67</v>
       </c>
       <c r="F33" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -4342,33 +4375,33 @@
         <v>2025-09-07</v>
       </c>
       <c r="B34" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E34" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F34" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="G34" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B35" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
@@ -4377,16 +4410,16 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E35" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F35" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G35" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H35" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4394,25 +4427,25 @@
         <v>2025-09-02</v>
       </c>
       <c r="B36" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E36" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G36" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="37">
@@ -4420,25 +4453,25 @@
         <v>2025-09-02</v>
       </c>
       <c r="B37" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
       </c>
       <c r="D37" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E37" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F37" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G37" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H37" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -4446,7 +4479,7 @@
         <v>2025-09-02</v>
       </c>
       <c r="B38" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
@@ -4455,13 +4488,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -4472,22 +4505,22 @@
         <v>2025-09-02</v>
       </c>
       <c r="B39" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E39" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="F39" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="G39" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4788,7 +4821,7 @@
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C51" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D51" t="str">
         <v>09:15-14:00</v>
@@ -4800,10 +4833,10 @@
         <v>2.67</v>
       </c>
       <c r="G51" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H51" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="52">
@@ -4811,7 +4844,7 @@
         <v>2025-09-02</v>
       </c>
       <c r="B52" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
@@ -4820,39 +4853,39 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E52" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F52" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B53" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E53" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F53" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G53" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4860,28 +4893,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B54" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C54" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D54" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E54" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" t="str">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="G54" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
     <row r="55">
@@ -4889,7 +4922,7 @@
         <v>2025-09-03</v>
       </c>
       <c r="B55" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
@@ -4898,13 +4931,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E55" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F55" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G55" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4915,25 +4948,25 @@
         <v>2025-09-03</v>
       </c>
       <c r="B56" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E56" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F56" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="57">
@@ -4941,22 +4974,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B57" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
       </c>
       <c r="D57" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="F57" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="G57" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4967,22 +5000,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B58" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -4993,22 +5026,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B59" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:30-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="F59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -5019,7 +5052,7 @@
         <v>2025-09-03</v>
       </c>
       <c r="B60" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
@@ -5045,52 +5078,51 @@
         <v>2025-09-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>09:15-15:00</v>
+        <v>08:30-21:30</v>
       </c>
       <c r="E61" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F61" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G61" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="62" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" t="str">
         <v>2025-09-03</v>
       </c>
       <c r="B62" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C62" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D62" t="str">
-        <v>10:30-12:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E62" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G62" t="str">
-        <v>0</v>
-      </c>
-      <c r="H62" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -5098,51 +5130,52 @@
         <v>2025-09-03</v>
       </c>
       <c r="B63" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-16:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E63" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="str">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="G63" t="str">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="H63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v>2025-09-03</v>
       </c>
       <c r="B64" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C64" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D64" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E64" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="F64" t="str">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="G64" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="65">
@@ -5150,22 +5183,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-16:30</v>
       </c>
       <c r="E65" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="G65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -5176,22 +5209,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B66" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
       </c>
       <c r="D66" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E66" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F66" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G66" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -5202,25 +5235,25 @@
         <v>2025-09-03</v>
       </c>
       <c r="B67" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E67" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G67" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H67" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -5228,22 +5261,22 @@
         <v>2025-09-03</v>
       </c>
       <c r="B68" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
       </c>
       <c r="D68" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F68" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G68" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -5251,10 +5284,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B69" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
@@ -5263,39 +5296,39 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E69" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F69" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G69" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H69" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B70" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E70" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F70" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G70" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -5306,25 +5339,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B71" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E71" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F71" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G71" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H71" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="72">
@@ -5332,22 +5365,22 @@
         <v>2025-09-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E72" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F72" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="G72" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -5358,25 +5391,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="74">
@@ -5384,22 +5417,22 @@
         <v>2025-09-01</v>
       </c>
       <c r="B74" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E74" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="F74" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G74" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5410,7 +5443,7 @@
         <v>2025-09-01</v>
       </c>
       <c r="B75" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
@@ -5436,25 +5469,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B76" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E76" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F76" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G76" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H76" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -5462,22 +5495,22 @@
         <v>2025-09-01</v>
       </c>
       <c r="B77" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E77" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F77" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="G77" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -5488,25 +5521,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B78" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
@@ -5514,25 +5547,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B79" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>09:15-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E79" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="F79" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="G79" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="H79" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -5540,25 +5573,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B80" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C80" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>10:20-12:50</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E80" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F80" t="str">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="G80" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H80" t="str">
-        <v>Brooke has an appointment to get bloods taken at 11.45 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -5566,25 +5599,25 @@
         <v>2025-09-01</v>
       </c>
       <c r="B81" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F81" t="str">
-        <v>0.17</v>
+        <v>3.2</v>
       </c>
       <c r="G81" t="str">
-        <v>0.17</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="82">
@@ -5592,59 +5625,59 @@
         <v>2025-09-01</v>
       </c>
       <c r="B82" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D82" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E82" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F82" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B83" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E83" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F83" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B84" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C84" t="str">
         <v>Available</v>
@@ -5653,16 +5686,16 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G84" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H84" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -5670,7 +5703,7 @@
         <v>2025-09-04</v>
       </c>
       <c r="B85" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C85" t="str">
         <v>Available</v>
@@ -5679,13 +5712,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E85" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F85" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G85" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H85" t="str">
         <v/>
@@ -5696,25 +5729,25 @@
         <v>2025-09-04</v>
       </c>
       <c r="B86" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C86" t="str">
         <v>Available</v>
       </c>
       <c r="D86" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E86" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F86" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G86" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="87">
@@ -5722,7 +5755,7 @@
         <v>2025-09-04</v>
       </c>
       <c r="B87" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C87" t="str">
         <v>Available</v>
@@ -5731,13 +5764,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E87" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F87" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G87" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -5748,22 +5781,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B88" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C88" t="str">
         <v>Available</v>
       </c>
       <c r="D88" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E88" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F88" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G88" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H88" t="str">
         <v/>
@@ -5774,22 +5807,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B89" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C89" t="str">
         <v>Available</v>
       </c>
       <c r="D89" t="str">
-        <v>09:15-11:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E89" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F89" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G89" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H89" t="str">
         <v/>
@@ -5800,22 +5833,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B90" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C90" t="str">
         <v>Available</v>
       </c>
       <c r="D90" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="E90" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F90" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G90" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -5826,7 +5859,7 @@
         <v>2025-09-04</v>
       </c>
       <c r="B91" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C91" t="str">
         <v>Available</v>
@@ -5835,13 +5868,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E91" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F91" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G91" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -5852,25 +5885,25 @@
         <v>2025-09-04</v>
       </c>
       <c r="B92" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C92" t="str">
         <v>Available</v>
       </c>
       <c r="D92" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E92" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F92" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G92" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H92" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -5878,25 +5911,25 @@
         <v>2025-09-04</v>
       </c>
       <c r="B93" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C93" t="str">
         <v>Available</v>
       </c>
       <c r="D93" t="str">
-        <v>09:15-16:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E93" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="F93" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="G93" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="94">
@@ -5904,22 +5937,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B94" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C94" t="str">
         <v>Available</v>
       </c>
       <c r="D94" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-16:15</v>
       </c>
       <c r="E94" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="F94" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="G94" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="H94" t="str">
         <v/>
@@ -5930,22 +5963,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B95" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C95" t="str">
         <v>Available</v>
       </c>
       <c r="D95" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E95" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F95" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G95" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H95" t="str">
         <v/>
@@ -5956,22 +5989,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B96" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C96" t="str">
         <v>Available</v>
       </c>
       <c r="D96" t="str">
-        <v>08:00-17:15</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E96" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="F96" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="G96" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H96" t="str">
         <v/>
@@ -5982,22 +6015,22 @@
         <v>2025-09-04</v>
       </c>
       <c r="B97" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C97" t="str">
         <v>Available</v>
       </c>
       <c r="D97" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="E97" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="F97" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="G97" t="str">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="H97" t="str">
         <v/>
@@ -6008,7 +6041,7 @@
         <v>2025-09-04</v>
       </c>
       <c r="B98" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C98" t="str">
         <v>Available</v>
@@ -6017,21 +6050,47 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E98" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F98" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G98" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D99" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E99" t="str">
+        <v>6</v>
+      </c>
+      <c r="F99" t="str">
+        <v>6</v>
+      </c>
+      <c r="G99" t="str">
+        <v>6</v>
+      </c>
+      <c r="H99" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3334,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>77.55</v>
+        <v>72.91</v>
       </c>
       <c r="G2" t="str">
-        <v>-20.72</v>
+        <v>-16.08</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3360,10 +3360,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>78.36</v>
+        <v>73.67</v>
       </c>
       <c r="G3" t="str">
-        <v>-5.79</v>
+        <v>-1.1</v>
       </c>
       <c r="H3" t="str">
         <v>Shortage</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>69.07</v>
+        <v>64.94</v>
       </c>
       <c r="G4" t="str">
-        <v>3.5</v>
+        <v>7.63</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -3412,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>66.58</v>
+        <v>62.6</v>
       </c>
       <c r="G5" t="str">
-        <v>11.42</v>
+        <v>15.4</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3438,10 +3438,10 @@
         <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>51.5</v>
+        <v>48.42</v>
       </c>
       <c r="G6" t="str">
-        <v>11.4</v>
+        <v>14.48</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3464,10 +3464,10 @@
         <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>42.75</v>
+        <v>40.19</v>
       </c>
       <c r="G7" t="str">
-        <v>-12.58</v>
+        <v>-10.02</v>
       </c>
       <c r="H7" t="str">
         <v>Shortage</v>
@@ -3490,10 +3490,10 @@
         <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>40</v>
+        <v>37.61</v>
       </c>
       <c r="G8" t="str">
-        <v>-7.17</v>
+        <v>-4.78</v>
       </c>
       <c r="H8" t="str">
         <v>Shortage</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3334,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>72.91</v>
+        <v>77.55</v>
       </c>
       <c r="G2" t="str">
-        <v>-16.08</v>
+        <v>-20.72</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3360,10 +3360,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>73.67</v>
+        <v>78.36</v>
       </c>
       <c r="G3" t="str">
-        <v>-1.1</v>
+        <v>-5.79</v>
       </c>
       <c r="H3" t="str">
         <v>Shortage</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>64.94</v>
+        <v>69.07</v>
       </c>
       <c r="G4" t="str">
-        <v>7.63</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -3412,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>62.6</v>
+        <v>66.58</v>
       </c>
       <c r="G5" t="str">
-        <v>15.4</v>
+        <v>11.42</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3438,10 +3438,10 @@
         <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>48.42</v>
+        <v>51.5</v>
       </c>
       <c r="G6" t="str">
-        <v>14.48</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3464,10 +3464,10 @@
         <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>40.19</v>
+        <v>42.75</v>
       </c>
       <c r="G7" t="str">
-        <v>-10.02</v>
+        <v>-12.58</v>
       </c>
       <c r="H7" t="str">
         <v>Shortage</v>
@@ -3490,10 +3490,10 @@
         <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>37.61</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>-4.78</v>
+        <v>-7.17</v>
       </c>
       <c r="H8" t="str">
         <v>Shortage</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -3334,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>77.55</v>
+        <v>64.5</v>
       </c>
       <c r="G2" t="str">
-        <v>-20.72</v>
+        <v>-7.67</v>
       </c>
       <c r="H2" t="str">
         <v>Shortage</v>
@@ -3360,13 +3360,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>78.36</v>
+        <v>65.25</v>
       </c>
       <c r="G3" t="str">
-        <v>-5.79</v>
+        <v>7.32</v>
       </c>
       <c r="H3" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="4">
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>69.07</v>
+        <v>69.75</v>
       </c>
       <c r="G4" t="str">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>

--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,297 +434,297 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B2" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E2" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B3" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E3" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="I3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B4" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E4" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F4" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str">
-        <v>Created by new vacation process.</v>
+      <c r="I4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B5" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E5" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B6" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E6" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B7" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C7" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F7" t="str">
-        <v>08:00-15:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G7" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v>0</v>
-      </c>
-      <c r="I7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Moved day to Friday
-Eilidh 27/08/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B8" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E8" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F8" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G8" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B9" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E9" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F9" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G9" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="str">
-        <v>0</v>
-      </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>3.2</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B10" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E10" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F10" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G10" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="str">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E11" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F11" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="12">
@@ -738,22 +738,22 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E12" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="13">
@@ -767,77 +767,77 @@
         <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E13" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F13" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I14" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,28 +845,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -874,28 +874,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -903,45 +903,45 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B18" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I18" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B19" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B20" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C20" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B21" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,27 +1008,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B22" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C22" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1037,27 +1037,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1066,62 +1066,62 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="H23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B24" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C24" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G24" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H24" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B25" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C25" t="str">
         <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1135,28 +1135,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B26" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C26" t="str">
         <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G26" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1164,22 +1164,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B27" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C27" t="str">
         <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:30-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G27" t="str">
         <v>7.5</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B28" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C28" t="str">
         <v>7.5</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1220,83 +1220,82 @@
         <v/>
       </c>
     </row>
-    <row r="29" xml:space="preserve">
+    <row r="29">
       <c r="A29" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B29" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C29" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:30-14:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G29" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="H29" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="I29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Office hours
-Eilidh 27/08/2025</v>
+        <v>8</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B30" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I30" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B31" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C31" t="str">
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G31" t="str">
         <v>4</v>
@@ -1305,56 +1304,56 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B32" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C32" t="str">
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G32" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B33" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C33" t="str">
         <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G33" t="str">
         <v>4</v>
@@ -1363,27 +1362,27 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B34" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C34" t="str">
         <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G34" t="str">
         <v>4</v>
@@ -1392,33 +1391,33 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B35" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>09:15-14:45</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="H35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1426,28 +1425,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B36" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="H36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1455,28 +1454,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B37" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C37" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G37" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1484,28 +1483,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B38" t="str">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1513,28 +1512,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B39" t="str">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="H39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1542,16 +1541,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B40" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1560,27 +1559,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I40" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B41" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1589,27 +1588,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I41" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B42" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1618,10 +1617,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1629,7 +1628,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B43" t="str">
         <v>30</v>
@@ -1638,7 +1637,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1658,7 +1657,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B44" t="str">
         <v>30</v>
@@ -1667,13 +1666,13 @@
         <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G44" t="str">
         <v>7.5</v>
@@ -1687,7 +1686,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B45" t="str">
         <v>30</v>
@@ -1696,7 +1695,7 @@
         <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1716,28 +1715,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B46" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1745,28 +1744,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B47" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1774,28 +1773,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B48" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1803,28 +1802,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B49" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1832,28 +1831,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B50" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1861,16 +1860,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B51" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1879,10 +1878,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1890,16 +1889,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B52" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1908,10 +1907,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1919,16 +1918,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B53" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1937,10 +1936,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1948,16 +1947,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B54" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1966,10 +1965,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1977,16 +1976,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B55" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1995,10 +1994,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2006,161 +2005,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B56" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C56" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G56" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H56" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B57" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C57" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G57" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H57" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B58" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B59" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B60" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2169,10 +2168,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2180,16 +2179,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
       </c>
       <c r="C62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2198,10 +2197,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2209,16 +2208,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2227,10 +2226,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2238,16 +2237,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2256,10 +2255,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2267,16 +2266,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2285,10 +2284,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2296,28 +2295,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B66" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2325,28 +2324,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B67" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2354,28 +2353,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B68" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2383,28 +2382,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B69" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2412,28 +2411,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B70" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2441,7 +2440,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2450,13 +2449,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2465,12 +2464,12 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B72" t="str">
         <v>16</v>
@@ -2479,13 +2478,13 @@
         <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G72" t="str">
         <v>3.2</v>
@@ -2494,12 +2493,12 @@
         <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B73" t="str">
         <v>16</v>
@@ -2508,13 +2507,13 @@
         <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G73" t="str">
         <v>3.2</v>
@@ -2523,91 +2522,91 @@
         <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B74" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I74" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B75" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2615,28 +2614,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2644,28 +2643,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2673,7 +2672,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B79" t="str">
         <v>30</v>
@@ -2682,13 +2681,13 @@
         <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G79" t="str">
         <v>6</v>
@@ -2702,7 +2701,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B80" t="str">
         <v>30</v>
@@ -2711,13 +2710,13 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G80" t="str">
         <v>6</v>
@@ -2731,28 +2730,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B81" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>08:00-17:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2760,28 +2759,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B82" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2789,500 +2788,36 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B83" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
       </c>
       <c r="F83" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B84" t="str">
-        <v>16</v>
-      </c>
-      <c r="C84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D84" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F84" t="str">
-        <v>09:15-21:30</v>
-      </c>
-      <c r="G84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I84" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B85" t="str">
-        <v>16</v>
-      </c>
-      <c r="C85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D85" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F85" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B86" t="str">
-        <v>16</v>
-      </c>
-      <c r="C86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D86" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F86" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B87" t="str">
-        <v>16</v>
-      </c>
-      <c r="C87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D87" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F87" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B88" t="str">
-        <v>16</v>
-      </c>
-      <c r="C88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D88" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F88" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B89" t="str">
-        <v>24</v>
-      </c>
-      <c r="C89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D89" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F89" t="str">
-        <v>09:15-10:15</v>
-      </c>
-      <c r="G89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B90" t="str">
-        <v>24</v>
-      </c>
-      <c r="C90" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D90" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F90" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G90" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H90" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B91" t="str">
-        <v>24</v>
-      </c>
-      <c r="C91" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D91" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F91" t="str">
-        <v>09:15-16:30</v>
-      </c>
-      <c r="G91" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H91" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B92" t="str">
-        <v>24</v>
-      </c>
-      <c r="C92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F92" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B93" t="str">
-        <v>24</v>
-      </c>
-      <c r="C93" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D93" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F93" t="str">
-        <v>09:15-17:00</v>
-      </c>
-      <c r="G93" t="str">
-        <v>0</v>
-      </c>
-      <c r="H93" t="str">
-        <v>0</v>
-      </c>
-      <c r="I93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B94" t="str">
-        <v>30</v>
-      </c>
-      <c r="C94" t="str">
-        <v>6</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F94" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G94" t="str">
-        <v>6</v>
-      </c>
-      <c r="H94" t="str">
-        <v>6</v>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B95" t="str">
-        <v>30</v>
-      </c>
-      <c r="C95" t="str">
-        <v>6</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E95" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F95" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G95" t="str">
-        <v>6</v>
-      </c>
-      <c r="H95" t="str">
-        <v>6</v>
-      </c>
-      <c r="I95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B96" t="str">
-        <v>30</v>
-      </c>
-      <c r="C96" t="str">
-        <v>6</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E96" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F96" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G96" t="str">
-        <v>6</v>
-      </c>
-      <c r="H96" t="str">
-        <v>6</v>
-      </c>
-      <c r="I96" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B97" t="str">
-        <v>30</v>
-      </c>
-      <c r="C97" t="str">
-        <v>6</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E97" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F97" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G97" t="str">
-        <v>6</v>
-      </c>
-      <c r="H97" t="str">
-        <v>6</v>
-      </c>
-      <c r="I97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B98" t="str">
-        <v>30</v>
-      </c>
-      <c r="C98" t="str">
-        <v>6</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F98" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G98" t="str">
-        <v>6</v>
-      </c>
-      <c r="H98" t="str">
-        <v>6</v>
-      </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B99" t="str">
-        <v>30</v>
-      </c>
-      <c r="C99" t="str">
-        <v>6</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E99" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="F99" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G99" t="str">
-        <v>5.75</v>
-      </c>
-      <c r="H99" t="str">
-        <v>0</v>
-      </c>
-      <c r="I99" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3319,13 +2854,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B2" t="str">
-        <v>56.83</v>
+        <v>58.6</v>
       </c>
       <c r="C2" t="str">
-        <v>56.83</v>
+        <v>58.6</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -3334,36 +2869,36 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>64.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>-7.67</v>
+        <v>58.6</v>
       </c>
       <c r="H2" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B3" t="str">
-        <v>66.57</v>
+        <v>75.1</v>
       </c>
       <c r="C3" t="str">
-        <v>72.57</v>
+        <v>75.1</v>
       </c>
       <c r="D3" t="str">
-        <v>11.67</v>
+        <v>2.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>65.25</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>7.32</v>
+        <v>75.1</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -3371,25 +2906,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B4" t="str">
-        <v>72.57</v>
+        <v>65.44</v>
       </c>
       <c r="C4" t="str">
-        <v>72.57</v>
+        <v>65.44</v>
       </c>
       <c r="D4" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>69.75</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>2.82</v>
+        <v>65.44</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -3397,25 +2932,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B5" t="str">
-        <v>78</v>
+        <v>60.77</v>
       </c>
       <c r="C5" t="str">
-        <v>78</v>
+        <v>60.77</v>
       </c>
       <c r="D5" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>66.58</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>11.42</v>
+        <v>60.77</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3423,25 +2958,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>62.9</v>
+        <v>54.1</v>
       </c>
       <c r="C6" t="str">
-        <v>62.9</v>
+        <v>54.1</v>
       </c>
       <c r="D6" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>51.5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>11.4</v>
+        <v>54.1</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3449,54 +2984,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="C7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>-12.58</v>
+        <v>42.67</v>
       </c>
       <c r="H7" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="C8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="D8" t="str">
-        <v>2.67</v>
+        <v>6.67</v>
       </c>
       <c r="E8" t="str">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>-7.17</v>
+        <v>40.33</v>
       </c>
       <c r="H8" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3536,35 +3071,36 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B2" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C2" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3579,10 +3115,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3590,33 +3126,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B4" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C4" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G4" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3631,10 +3167,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3642,130 +3178,129 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B8" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-10:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B9" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:30-14:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E9" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Office hours
-Eilidh 27/08/2025</v>
+        <v>4</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B10" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -3773,104 +3308,103 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B11" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B12" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C12" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D12" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E12" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="F12" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H12" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C13" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D13" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E13" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F13" t="str">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
-      </c>
-      <c r="H13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>2.67</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B14" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E14" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3878,51 +3412,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B15" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B16" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3930,25 +3464,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B17" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="F17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="G17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3956,25 +3490,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B18" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3982,25 +3516,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B19" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -4008,129 +3542,130 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B20" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C20" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D20" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B21" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E21" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>2025-09-11</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D22" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="E22" t="str">
+        <v>4</v>
+      </c>
+      <c r="F22" t="str">
+        <v>4</v>
+      </c>
+      <c r="G22" t="str">
         <v>0</v>
       </c>
-      <c r="G21" t="str">
-        <v>0</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2025-09-06</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D22" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E22" t="str">
-        <v>6</v>
-      </c>
-      <c r="F22" t="str">
-        <v>6</v>
-      </c>
-      <c r="G22" t="str">
-        <v>6</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B23" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C23" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D23" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E23" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="G23" t="str">
         <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B24" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>08:00-15:15</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -4138,25 +3673,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B25" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -4164,51 +3699,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B26" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="E26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="F26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="G26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="H26" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -4216,16 +3751,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B28" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E28" t="str">
         <v>6</v>
@@ -4242,77 +3777,78 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B29" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C29" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E29" t="str">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="F29" t="str">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="G29" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>2025-09-14</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D30" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E30" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F30" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G30" t="str">
         <v>0</v>
       </c>
-      <c r="H29" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2025-09-07</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D30" t="str">
-        <v>08:00-15:15</v>
-      </c>
-      <c r="E30" t="str">
-        <v>4</v>
-      </c>
-      <c r="F30" t="str">
-        <v>4</v>
-      </c>
-      <c r="G30" t="str">
-        <v>4</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B31" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C31" t="str">
         <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E31" t="str">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="F31" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="G31" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -4320,51 +3856,51 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B32" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C32" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E32" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H32" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B33" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E33" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F33" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G33" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -4372,51 +3908,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B34" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B35" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -4424,36 +3960,36 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B36" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B37" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
@@ -4476,51 +4012,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B39" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="F39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4528,7 +4064,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4537,7 +4073,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4549,30 +4085,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B41" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4580,10 +4116,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B42" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4604,54 +4140,53 @@
         <v/>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
+    <row r="43">
       <c r="A43" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B43" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C43" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D43" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F43" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="G43" t="str">
-        <v>0</v>
-      </c>
-      <c r="H43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Moved day to Friday
-Eilidh 27/08/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B44" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E44" t="str">
         <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="G44" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4659,25 +4194,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B45" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4685,103 +4220,103 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B46" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B47" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C47" t="str">
-        <v>Other Unavailable</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D47" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E47" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F47" t="str">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B48" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>09:15-16:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E48" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F48" t="str">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B49" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -4789,25 +4324,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B50" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -4815,77 +4350,77 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B51" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C51" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D51" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F51" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G51" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B52" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E52" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F52" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H52" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B53" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4893,51 +4428,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B54" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C54" t="str">
-        <v>Dependant Leave</v>
+        <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F54" t="str">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="G54" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B55" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4945,36 +4480,36 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B56" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H56" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -4983,13 +4518,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4997,16 +4532,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B58" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E58" t="str">
         <v>3.2</v>
@@ -5018,30 +4553,30 @@
         <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B59" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="G59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -5049,25 +4584,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B60" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -5075,25 +4610,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B61" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>08:30-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -5101,115 +4636,114 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B62" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C62" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D62" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E62" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F62" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B63" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E63" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F63" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B64" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C64" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D64" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E64" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F64" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G64" t="str">
-        <v>0</v>
-      </c>
-      <c r="H64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B65" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>09:15-16:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E65" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F65" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B66" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -5232,25 +4766,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B67" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5258,10 +4792,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B68" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -5270,13 +4804,13 @@
         <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -5284,42 +4818,42 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B69" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="G69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H69" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B70" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E70" t="str">
         <v>6</v>
@@ -5336,103 +4870,103 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B71" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B72" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B73" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H73" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B74" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>09:15-14:45</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5440,25 +4974,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B75" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5466,42 +5000,42 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B76" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B77" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E77" t="str">
         <v>6</v>
@@ -5518,51 +5052,51 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B78" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H78" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B79" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="F79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="G79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -5570,25 +5104,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B80" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -5596,42 +5130,42 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B81" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>09:15-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H81" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B82" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D82" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E82" t="str">
         <v>2.67</v>
@@ -5640,457 +5174,41 @@
         <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H82" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B83" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E83" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F83" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G83" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H83" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D84" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E84" t="str">
-        <v>6</v>
-      </c>
-      <c r="F84" t="str">
-        <v>6</v>
-      </c>
-      <c r="G84" t="str">
-        <v>6</v>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D85" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D86" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E86" t="str">
-        <v>4</v>
-      </c>
-      <c r="F86" t="str">
-        <v>4</v>
-      </c>
-      <c r="G86" t="str">
-        <v>4</v>
-      </c>
-      <c r="H86" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D87" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E87" t="str">
-        <v>9</v>
-      </c>
-      <c r="F87" t="str">
-        <v>9</v>
-      </c>
-      <c r="G87" t="str">
-        <v>9</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D88" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D89" t="str">
-        <v>09:15-15:15</v>
-      </c>
-      <c r="E89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D90" t="str">
-        <v>09:15-11:30</v>
-      </c>
-      <c r="E90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D91" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E91" t="str">
-        <v>6</v>
-      </c>
-      <c r="F91" t="str">
-        <v>6</v>
-      </c>
-      <c r="G91" t="str">
-        <v>6</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D92" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D93" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="E93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H93" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D94" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="E94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="F94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="G94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D95" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B96" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D96" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="E96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H96" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D97" t="str">
-        <v>08:00-17:15</v>
-      </c>
-      <c r="E97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B98" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D98" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D99" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E99" t="str">
-        <v>6</v>
-      </c>
-      <c r="F99" t="str">
-        <v>6</v>
-      </c>
-      <c r="G99" t="str">
-        <v>6</v>
-      </c>
-      <c r="H99" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,297 +434,297 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E2" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+      <c r="I2" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E3" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+      <c r="I3" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B4" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E4" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+      <c r="I4" t="str">
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B5" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E5" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B6" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E6" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B7" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C7" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E7" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="H7" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>0</v>
+      </c>
+      <c r="I7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E8" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E9" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G9" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B10" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C10" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E10" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H10" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E11" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="12">
@@ -738,22 +738,22 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E12" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="13">
@@ -767,77 +767,77 @@
         <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E13" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F13" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,28 +845,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -874,28 +874,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -903,45 +903,45 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B18" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B20" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B21" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,27 +1008,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B22" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1037,27 +1037,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1066,62 +1066,62 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="I23" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B24" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G24" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H24" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I24" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B25" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C25" t="str">
         <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1135,28 +1135,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B26" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C26" t="str">
         <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1164,22 +1164,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B27" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C27" t="str">
         <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:00-21:30</v>
+        <v>08:30-21:30</v>
       </c>
       <c r="G27" t="str">
         <v>7.5</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B28" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C28" t="str">
         <v>7.5</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1220,82 +1220,83 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B29" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C29" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:00-18:00</v>
+        <v>08:30-14:30</v>
       </c>
       <c r="G29" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="str">
-        <v>8</v>
-      </c>
-      <c r="I29" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="I29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B30" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B31" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C31" t="str">
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G31" t="str">
         <v>4</v>
@@ -1304,56 +1305,56 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B32" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C32" t="str">
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B33" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C33" t="str">
         <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G33" t="str">
         <v>4</v>
@@ -1362,27 +1363,27 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B34" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
         <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G34" t="str">
         <v>4</v>
@@ -1391,33 +1392,33 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B35" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="H35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1425,28 +1426,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B36" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1454,28 +1455,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C37" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G37" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1483,28 +1484,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B38" t="str">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1512,28 +1513,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B39" t="str">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="G39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1541,16 +1542,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B40" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1559,27 +1560,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B41" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1588,27 +1589,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B42" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1617,10 +1618,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1628,7 +1629,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B43" t="str">
         <v>30</v>
@@ -1637,7 +1638,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1657,7 +1658,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B44" t="str">
         <v>30</v>
@@ -1666,13 +1667,13 @@
         <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G44" t="str">
         <v>7.5</v>
@@ -1686,7 +1687,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B45" t="str">
         <v>30</v>
@@ -1695,7 +1696,7 @@
         <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1715,28 +1716,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B46" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1744,28 +1745,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B47" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1773,28 +1774,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B48" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1802,28 +1803,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B49" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1831,28 +1832,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B50" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1860,16 +1861,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B51" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1878,10 +1879,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1889,16 +1890,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B52" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1907,10 +1908,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1918,16 +1919,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B53" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1936,10 +1937,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1947,16 +1948,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B54" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1965,10 +1966,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1976,16 +1977,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B55" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1994,10 +1995,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2005,161 +2006,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B56" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C56" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B57" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C57" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G57" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B58" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B59" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I59" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B60" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2168,10 +2169,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2179,16 +2180,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
       </c>
       <c r="C62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2197,10 +2198,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2208,16 +2209,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2226,10 +2227,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2237,16 +2238,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2255,10 +2256,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2266,16 +2267,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2284,10 +2285,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2295,28 +2296,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B66" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2324,28 +2325,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B67" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2353,28 +2354,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B68" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2382,28 +2383,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B69" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2411,28 +2412,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B70" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2440,7 +2441,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2449,13 +2450,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2464,12 +2465,12 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B72" t="str">
         <v>16</v>
@@ -2478,13 +2479,13 @@
         <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G72" t="str">
         <v>3.2</v>
@@ -2493,12 +2494,12 @@
         <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B73" t="str">
         <v>16</v>
@@ -2507,13 +2508,13 @@
         <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G73" t="str">
         <v>3.2</v>
@@ -2522,91 +2523,91 @@
         <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B74" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B75" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2614,28 +2615,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2643,28 +2644,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2672,7 +2673,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B79" t="str">
         <v>30</v>
@@ -2681,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G79" t="str">
         <v>6</v>
@@ -2701,7 +2702,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B80" t="str">
         <v>30</v>
@@ -2710,13 +2711,13 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G80" t="str">
         <v>6</v>
@@ -2730,28 +2731,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B81" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2759,28 +2760,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2788,36 +2789,500 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="B83" t="str">
+        <v>16</v>
+      </c>
+      <c r="C83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F83" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="G83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B84" t="str">
+        <v>16</v>
+      </c>
+      <c r="C84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F84" t="str">
+        <v>09:15-21:30</v>
+      </c>
+      <c r="G84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B85" t="str">
+        <v>16</v>
+      </c>
+      <c r="C85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F85" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B86" t="str">
+        <v>16</v>
+      </c>
+      <c r="C86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F86" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B87" t="str">
+        <v>16</v>
+      </c>
+      <c r="C87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F87" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B88" t="str">
+        <v>16</v>
+      </c>
+      <c r="C88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F88" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B89" t="str">
+        <v>24</v>
+      </c>
+      <c r="C89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F89" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B90" t="str">
+        <v>24</v>
+      </c>
+      <c r="C90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F90" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B91" t="str">
+        <v>24</v>
+      </c>
+      <c r="C91" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F91" t="str">
+        <v>09:15-16:30</v>
+      </c>
+      <c r="G91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B92" t="str">
+        <v>24</v>
+      </c>
+      <c r="C92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F92" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B93" t="str">
+        <v>24</v>
+      </c>
+      <c r="C93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F93" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0</v>
+      </c>
+      <c r="H93" t="str">
+        <v>0</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B94" t="str">
         <v>30</v>
       </c>
-      <c r="C83" t="str">
-        <v>6</v>
-      </c>
-      <c r="D83" t="str">
-        <v>2025-09-12</v>
-      </c>
-      <c r="E83" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F83" t="str">
+      <c r="C94" t="str">
+        <v>6</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F94" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="G83" t="str">
-        <v>6</v>
-      </c>
-      <c r="H83" t="str">
-        <v>6</v>
-      </c>
-      <c r="I83" t="str">
-        <v/>
+      <c r="G94" t="str">
+        <v>6</v>
+      </c>
+      <c r="H94" t="str">
+        <v>6</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B95" t="str">
+        <v>30</v>
+      </c>
+      <c r="C95" t="str">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F95" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G95" t="str">
+        <v>6</v>
+      </c>
+      <c r="H95" t="str">
+        <v>6</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B96" t="str">
+        <v>30</v>
+      </c>
+      <c r="C96" t="str">
+        <v>6</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F96" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G96" t="str">
+        <v>6</v>
+      </c>
+      <c r="H96" t="str">
+        <v>6</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B97" t="str">
+        <v>30</v>
+      </c>
+      <c r="C97" t="str">
+        <v>6</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F97" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G97" t="str">
+        <v>6</v>
+      </c>
+      <c r="H97" t="str">
+        <v>6</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B98" t="str">
+        <v>30</v>
+      </c>
+      <c r="C98" t="str">
+        <v>6</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G98" t="str">
+        <v>6</v>
+      </c>
+      <c r="H98" t="str">
+        <v>6</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B99" t="str">
+        <v>30</v>
+      </c>
+      <c r="C99" t="str">
+        <v>6</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Dependant Leave</v>
+      </c>
+      <c r="F99" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G99" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="H99" t="str">
+        <v>0</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2854,13 +3319,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B2" t="str">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="C2" t="str">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -2869,62 +3334,62 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>77.55</v>
       </c>
       <c r="G2" t="str">
-        <v>58.6</v>
+        <v>-20.72</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>75.1</v>
+        <v>66.57</v>
       </c>
       <c r="C3" t="str">
-        <v>75.1</v>
+        <v>72.57</v>
       </c>
       <c r="D3" t="str">
-        <v>2.67</v>
+        <v>11.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>78.36</v>
       </c>
       <c r="G3" t="str">
-        <v>75.1</v>
+        <v>-5.79</v>
       </c>
       <c r="H3" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B4" t="str">
-        <v>65.44</v>
+        <v>72.57</v>
       </c>
       <c r="C4" t="str">
-        <v>65.44</v>
+        <v>72.57</v>
       </c>
       <c r="D4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>69.07</v>
       </c>
       <c r="G4" t="str">
-        <v>65.44</v>
+        <v>3.5</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -2932,25 +3397,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B5" t="str">
-        <v>60.77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="str">
-        <v>60.77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>66.58</v>
       </c>
       <c r="G5" t="str">
-        <v>60.77</v>
+        <v>11.42</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -2958,25 +3423,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>54.1</v>
+        <v>62.9</v>
       </c>
       <c r="C6" t="str">
-        <v>54.1</v>
+        <v>62.9</v>
       </c>
       <c r="D6" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="G6" t="str">
-        <v>54.1</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -2984,54 +3449,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="C7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>42.75</v>
       </c>
       <c r="G7" t="str">
-        <v>42.67</v>
+        <v>-12.58</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="C8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="D8" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="E8" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>40.33</v>
+        <v>-7.17</v>
       </c>
       <c r="H8" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +3508,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3071,36 +3536,35 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C2" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="str">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3115,10 +3579,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3126,33 +3590,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B4" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C4" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G4" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3167,10 +3631,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3178,129 +3642,130 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H6" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="9">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B9" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:00-15:15</v>
+        <v>08:30-14:30</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F9" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="str">
-        <v>4</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B10" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -3308,103 +3773,104 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B11" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>08:00-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B12" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D12" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E12" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="F12" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="G12" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E13" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F13" t="str">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B14" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E14" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F14" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3412,51 +3878,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B15" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B16" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3464,25 +3930,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B17" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="F17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="G17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3490,25 +3956,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B18" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="F18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="G18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3516,25 +3982,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B19" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -3542,130 +4008,129 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C20" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D20" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B21" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E21" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F21" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B22" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D22" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
-      </c>
-      <c r="H22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B23" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C23" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D23" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E23" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F23" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="G23" t="str">
         <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B24" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -3673,25 +4138,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B25" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -3699,51 +4164,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B26" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="F26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="G26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B27" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -3751,16 +4216,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B28" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E28" t="str">
         <v>6</v>
@@ -3777,78 +4242,77 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C29" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E29" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="F29" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="G29" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B30" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C30" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E30" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="G30" t="str">
-        <v>0</v>
-      </c>
-      <c r="H30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+        <v>4</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B31" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C31" t="str">
         <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E31" t="str">
-        <v>6.67</v>
+        <v>5.33</v>
       </c>
       <c r="F31" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G31" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -3856,51 +4320,51 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B32" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C32" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D32" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G32" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B33" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E33" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F33" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -3908,51 +4372,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B35" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -3960,36 +4424,36 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B36" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H36" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B37" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
@@ -4012,51 +4476,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B38" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B39" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="F39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="G39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4064,7 +4528,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4073,7 +4537,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4085,30 +4549,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B41" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="E41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4116,10 +4580,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B42" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4140,53 +4604,54 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B43" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C43" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D43" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F43" t="str">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="G43" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>0</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E44" t="str">
         <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4194,25 +4659,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B45" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4220,103 +4685,103 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B46" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B47" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C47" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D47" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E47" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F47" t="str">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B48" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-16:15</v>
       </c>
       <c r="E48" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F48" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="H48" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B49" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -4324,25 +4789,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -4350,77 +4815,77 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B51" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C51" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D51" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F51" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G51" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B52" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E52" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F52" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B53" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4428,51 +4893,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C54" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D54" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="str">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="G54" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B55" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4480,36 +4945,36 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B56" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B57" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -4518,13 +4983,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4532,16 +4997,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E58" t="str">
         <v>3.2</v>
@@ -4553,30 +5018,30 @@
         <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="F59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -4584,25 +5049,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B60" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -4610,25 +5075,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>08:00-15:00</v>
+        <v>08:30-21:30</v>
       </c>
       <c r="E61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -4636,114 +5101,115 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B62" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C62" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D62" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E62" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G62" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H62" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B63" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E63" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G63" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D64" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="E64" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2</v>
+      </c>
+      <c r="G64" t="str">
         <v>0</v>
       </c>
-      <c r="G63" t="str">
-        <v>0</v>
-      </c>
-      <c r="H63" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>2025-09-09</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D64" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E64" t="str">
-        <v>6</v>
-      </c>
-      <c r="F64" t="str">
-        <v>6</v>
-      </c>
-      <c r="G64" t="str">
-        <v>6</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
+      <c r="H64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-16:30</v>
       </c>
       <c r="E65" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="G65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B66" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -4766,25 +5232,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B67" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -4792,10 +5258,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B68" t="str">
-        <v>Ferris, Marykate</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -4804,13 +5270,13 @@
         <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="F68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="G68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -4818,42 +5284,42 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B69" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B70" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E70" t="str">
         <v>6</v>
@@ -4870,103 +5336,103 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B71" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>08:00-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B74" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -4974,25 +5440,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5000,42 +5466,42 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B76" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H76" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B77" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E77" t="str">
         <v>6</v>
@@ -5052,51 +5518,51 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B78" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B79" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="F79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="G79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -5104,25 +5570,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B80" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -5130,42 +5596,42 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B81" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B82" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D82" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E82" t="str">
         <v>2.67</v>
@@ -5174,41 +5640,457 @@
         <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B83" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E83" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="F83" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H83" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D84" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E84" t="str">
+        <v>6</v>
+      </c>
+      <c r="F84" t="str">
+        <v>6</v>
+      </c>
+      <c r="G84" t="str">
+        <v>6</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D85" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D86" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E86" t="str">
+        <v>4</v>
+      </c>
+      <c r="F86" t="str">
+        <v>4</v>
+      </c>
+      <c r="G86" t="str">
+        <v>4</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D87" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E87" t="str">
+        <v>9</v>
+      </c>
+      <c r="F87" t="str">
+        <v>9</v>
+      </c>
+      <c r="G87" t="str">
+        <v>9</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D88" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D89" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D90" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D91" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E91" t="str">
+        <v>6</v>
+      </c>
+      <c r="F91" t="str">
+        <v>6</v>
+      </c>
+      <c r="G91" t="str">
+        <v>6</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D92" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D93" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D94" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="E94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D95" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B96" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D96" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D97" t="str">
+        <v>08:00-17:15</v>
+      </c>
+      <c r="E97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B98" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D99" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E99" t="str">
+        <v>6</v>
+      </c>
+      <c r="F99" t="str">
+        <v>6</v>
+      </c>
+      <c r="G99" t="str">
+        <v>6</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,297 +434,297 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B2" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E2" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B3" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E3" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="I3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B4" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E4" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F4" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str">
-        <v>Created by new vacation process.</v>
+      <c r="I4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B5" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E5" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B6" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E6" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B7" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C7" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F7" t="str">
-        <v>08:00-15:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G7" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v>0</v>
-      </c>
-      <c r="I7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Moved day to Friday
-Eilidh 27/08/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B8" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E8" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F8" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G8" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B9" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E9" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F9" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G9" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="str">
-        <v>0</v>
-      </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>3.2</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B10" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E10" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F10" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G10" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="str">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E11" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F11" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="12">
@@ -738,22 +738,22 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E12" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="13">
@@ -767,77 +767,77 @@
         <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E13" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F13" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I14" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,28 +845,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -874,28 +874,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -903,45 +903,45 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B18" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I18" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B19" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B20" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C20" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B21" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,27 +1008,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B22" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C22" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1037,27 +1037,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1066,62 +1066,62 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="H23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B24" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C24" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G24" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H24" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B25" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C25" t="str">
         <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1135,28 +1135,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B26" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C26" t="str">
         <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G26" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1164,22 +1164,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B27" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C27" t="str">
         <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:30-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G27" t="str">
         <v>7.5</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B28" t="str">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="C28" t="str">
         <v>7.5</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1220,83 +1220,82 @@
         <v/>
       </c>
     </row>
-    <row r="29" xml:space="preserve">
+    <row r="29">
       <c r="A29" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B29" t="str">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="C29" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:30-14:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G29" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="H29" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="I29" t="str" xml:space="preserve">
-        <v xml:space="preserve">Office hours
-Eilidh 27/08/2025</v>
+        <v>8</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B30" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H30" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I30" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B31" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C31" t="str">
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G31" t="str">
         <v>4</v>
@@ -1305,56 +1304,56 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B32" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C32" t="str">
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G32" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B33" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C33" t="str">
         <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G33" t="str">
         <v>4</v>
@@ -1363,27 +1362,27 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B34" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C34" t="str">
         <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G34" t="str">
         <v>4</v>
@@ -1392,33 +1391,33 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B35" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>09:15-14:45</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="H35" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1426,28 +1425,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B36" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="H36" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1455,28 +1454,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B37" t="str">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C37" t="str">
-        <v>2.8</v>
+        <v>6.67</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G37" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H37" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1484,28 +1483,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B38" t="str">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1513,28 +1512,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B39" t="str">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="H39" t="str">
-        <v>2.8</v>
+        <v>9</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1542,16 +1541,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B40" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1560,27 +1559,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H40" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I40" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B41" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1589,27 +1588,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H41" t="str">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I41" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B42" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1618,10 +1617,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H42" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1629,7 +1628,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B43" t="str">
         <v>30</v>
@@ -1638,7 +1637,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1658,7 +1657,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B44" t="str">
         <v>30</v>
@@ -1667,13 +1666,13 @@
         <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G44" t="str">
         <v>7.5</v>
@@ -1687,7 +1686,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B45" t="str">
         <v>30</v>
@@ -1696,7 +1695,7 @@
         <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1716,28 +1715,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B46" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H46" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1745,28 +1744,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B47" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H47" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1774,28 +1773,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B48" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H48" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1803,28 +1802,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B49" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1832,28 +1831,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B50" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1861,16 +1860,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B51" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1879,10 +1878,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H51" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1890,16 +1889,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B52" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1908,10 +1907,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H52" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1919,16 +1918,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B53" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1937,10 +1936,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1948,16 +1947,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B54" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1966,10 +1965,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1977,16 +1976,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B55" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1995,10 +1994,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H55" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2006,161 +2005,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B56" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C56" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G56" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H56" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B57" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C57" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G57" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H57" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B58" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B59" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B60" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2169,10 +2168,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2180,16 +2179,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
       </c>
       <c r="C62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2198,10 +2197,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H62" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2209,16 +2208,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2227,10 +2226,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H63" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2238,16 +2237,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2256,10 +2255,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H64" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2267,16 +2266,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2285,10 +2284,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H65" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2296,28 +2295,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B66" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2325,28 +2324,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B67" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H67" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2354,28 +2353,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B68" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H68" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2383,28 +2382,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B69" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H69" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2412,28 +2411,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B70" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H70" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2441,7 +2440,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2450,13 +2449,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2465,12 +2464,12 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B72" t="str">
         <v>16</v>
@@ -2479,13 +2478,13 @@
         <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G72" t="str">
         <v>3.2</v>
@@ -2494,12 +2493,12 @@
         <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B73" t="str">
         <v>16</v>
@@ -2508,13 +2507,13 @@
         <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G73" t="str">
         <v>3.2</v>
@@ -2523,91 +2522,91 @@
         <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B74" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H74" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I74" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B75" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2615,28 +2614,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2644,28 +2643,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H78" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2673,7 +2672,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B79" t="str">
         <v>30</v>
@@ -2682,13 +2681,13 @@
         <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G79" t="str">
         <v>6</v>
@@ -2702,7 +2701,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B80" t="str">
         <v>30</v>
@@ -2711,13 +2710,13 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G80" t="str">
         <v>6</v>
@@ -2731,28 +2730,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B81" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>08:00-17:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2760,28 +2759,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B82" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2789,500 +2788,36 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B83" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
       </c>
       <c r="F83" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B84" t="str">
-        <v>16</v>
-      </c>
-      <c r="C84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D84" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F84" t="str">
-        <v>09:15-21:30</v>
-      </c>
-      <c r="G84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I84" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B85" t="str">
-        <v>16</v>
-      </c>
-      <c r="C85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D85" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F85" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H85" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B86" t="str">
-        <v>16</v>
-      </c>
-      <c r="C86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D86" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F86" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B87" t="str">
-        <v>16</v>
-      </c>
-      <c r="C87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D87" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F87" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H87" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B88" t="str">
-        <v>16</v>
-      </c>
-      <c r="C88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D88" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F88" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H88" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B89" t="str">
-        <v>24</v>
-      </c>
-      <c r="C89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D89" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F89" t="str">
-        <v>09:15-10:15</v>
-      </c>
-      <c r="G89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B90" t="str">
-        <v>24</v>
-      </c>
-      <c r="C90" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D90" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F90" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G90" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H90" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B91" t="str">
-        <v>24</v>
-      </c>
-      <c r="C91" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D91" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F91" t="str">
-        <v>09:15-16:30</v>
-      </c>
-      <c r="G91" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H91" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B92" t="str">
-        <v>24</v>
-      </c>
-      <c r="C92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F92" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H92" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B93" t="str">
-        <v>24</v>
-      </c>
-      <c r="C93" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D93" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F93" t="str">
-        <v>09:15-17:00</v>
-      </c>
-      <c r="G93" t="str">
-        <v>0</v>
-      </c>
-      <c r="H93" t="str">
-        <v>0</v>
-      </c>
-      <c r="I93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B94" t="str">
-        <v>30</v>
-      </c>
-      <c r="C94" t="str">
-        <v>6</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F94" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G94" t="str">
-        <v>6</v>
-      </c>
-      <c r="H94" t="str">
-        <v>6</v>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B95" t="str">
-        <v>30</v>
-      </c>
-      <c r="C95" t="str">
-        <v>6</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E95" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F95" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G95" t="str">
-        <v>6</v>
-      </c>
-      <c r="H95" t="str">
-        <v>6</v>
-      </c>
-      <c r="I95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B96" t="str">
-        <v>30</v>
-      </c>
-      <c r="C96" t="str">
-        <v>6</v>
-      </c>
-      <c r="D96" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E96" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F96" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G96" t="str">
-        <v>6</v>
-      </c>
-      <c r="H96" t="str">
-        <v>6</v>
-      </c>
-      <c r="I96" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B97" t="str">
-        <v>30</v>
-      </c>
-      <c r="C97" t="str">
-        <v>6</v>
-      </c>
-      <c r="D97" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E97" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F97" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G97" t="str">
-        <v>6</v>
-      </c>
-      <c r="H97" t="str">
-        <v>6</v>
-      </c>
-      <c r="I97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B98" t="str">
-        <v>30</v>
-      </c>
-      <c r="C98" t="str">
-        <v>6</v>
-      </c>
-      <c r="D98" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F98" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G98" t="str">
-        <v>6</v>
-      </c>
-      <c r="H98" t="str">
-        <v>6</v>
-      </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B99" t="str">
-        <v>30</v>
-      </c>
-      <c r="C99" t="str">
-        <v>6</v>
-      </c>
-      <c r="D99" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E99" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="F99" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G99" t="str">
-        <v>5.75</v>
-      </c>
-      <c r="H99" t="str">
-        <v>0</v>
-      </c>
-      <c r="I99" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3319,13 +2854,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B2" t="str">
-        <v>56.83</v>
+        <v>58.6</v>
       </c>
       <c r="C2" t="str">
-        <v>56.83</v>
+        <v>58.6</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -3334,62 +2869,62 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>77.55</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>-20.72</v>
+        <v>58.6</v>
       </c>
       <c r="H2" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B3" t="str">
-        <v>66.57</v>
+        <v>75.1</v>
       </c>
       <c r="C3" t="str">
-        <v>72.57</v>
+        <v>75.1</v>
       </c>
       <c r="D3" t="str">
-        <v>11.67</v>
+        <v>2.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>78.36</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>-5.79</v>
+        <v>75.1</v>
       </c>
       <c r="H3" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B4" t="str">
-        <v>72.57</v>
+        <v>65.44</v>
       </c>
       <c r="C4" t="str">
-        <v>72.57</v>
+        <v>65.44</v>
       </c>
       <c r="D4" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>69.07</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>3.5</v>
+        <v>65.44</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -3397,25 +2932,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B5" t="str">
-        <v>78</v>
+        <v>60.77</v>
       </c>
       <c r="C5" t="str">
-        <v>78</v>
+        <v>60.77</v>
       </c>
       <c r="D5" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>66.58</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>11.42</v>
+        <v>60.77</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3423,25 +2958,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>62.9</v>
+        <v>54.1</v>
       </c>
       <c r="C6" t="str">
-        <v>62.9</v>
+        <v>54.1</v>
       </c>
       <c r="D6" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>51.5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>11.4</v>
+        <v>54.1</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3449,54 +2984,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="C7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>-12.58</v>
+        <v>42.67</v>
       </c>
       <c r="H7" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="C8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="D8" t="str">
-        <v>2.67</v>
+        <v>6.67</v>
       </c>
       <c r="E8" t="str">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>-7.17</v>
+        <v>40.33</v>
       </c>
       <c r="H8" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3536,35 +3071,36 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B2" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C2" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3579,10 +3115,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3590,33 +3126,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B4" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C4" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G4" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3631,10 +3167,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3642,130 +3178,129 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B8" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-10:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B9" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:30-14:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E9" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Office hours
-Eilidh 27/08/2025</v>
+        <v>4</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B10" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -3773,104 +3308,103 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B11" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B12" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C12" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D12" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E12" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="F12" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H12" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C13" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D13" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E13" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F13" t="str">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
-      </c>
-      <c r="H13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>2.67</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B14" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E14" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G14" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3878,51 +3412,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B15" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B16" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3930,25 +3464,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B17" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="F17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="G17" t="str">
-        <v>5.33</v>
+        <v>9</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3956,25 +3490,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B18" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="F18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3982,25 +3516,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B19" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -4008,129 +3542,130 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B20" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C20" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D20" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B21" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E21" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>2025-09-11</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D22" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="E22" t="str">
+        <v>4</v>
+      </c>
+      <c r="F22" t="str">
+        <v>4</v>
+      </c>
+      <c r="G22" t="str">
         <v>0</v>
       </c>
-      <c r="G21" t="str">
-        <v>0</v>
-      </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2025-09-06</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D22" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E22" t="str">
-        <v>6</v>
-      </c>
-      <c r="F22" t="str">
-        <v>6</v>
-      </c>
-      <c r="G22" t="str">
-        <v>6</v>
-      </c>
-      <c r="H22" t="str">
-        <v/>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B23" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C23" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D23" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E23" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="G23" t="str">
         <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B24" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>08:00-15:15</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -4138,25 +3673,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B25" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -4164,51 +3699,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B26" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="E26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="F26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="G26" t="str">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="H26" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G27" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -4216,16 +3751,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B28" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E28" t="str">
         <v>6</v>
@@ -4242,77 +3777,78 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B29" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C29" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E29" t="str">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="F29" t="str">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="G29" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
+        <v>2025-09-14</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D30" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E30" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F30" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G30" t="str">
         <v>0</v>
       </c>
-      <c r="H29" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2025-09-07</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D30" t="str">
-        <v>08:00-15:15</v>
-      </c>
-      <c r="E30" t="str">
-        <v>4</v>
-      </c>
-      <c r="F30" t="str">
-        <v>4</v>
-      </c>
-      <c r="G30" t="str">
-        <v>4</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B31" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C31" t="str">
         <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E31" t="str">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="F31" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="G31" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -4320,51 +3856,51 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B32" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C32" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E32" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H32" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B33" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E33" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F33" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G33" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -4372,51 +3908,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B34" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B35" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G35" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -4424,36 +3960,36 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B36" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G36" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B37" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
@@ -4476,51 +4012,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B39" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="F39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4528,7 +4064,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4537,7 +4073,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4549,30 +4085,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B41" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4580,10 +4116,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B42" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4604,54 +4140,53 @@
         <v/>
       </c>
     </row>
-    <row r="43" xml:space="preserve">
+    <row r="43">
       <c r="A43" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B43" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C43" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D43" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F43" t="str">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="G43" t="str">
-        <v>0</v>
-      </c>
-      <c r="H43" t="str" xml:space="preserve">
-        <v xml:space="preserve">Moved day to Friday
-Eilidh 27/08/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B44" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E44" t="str">
         <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="G44" t="str">
-        <v>0.5</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4659,25 +4194,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B45" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G45" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4685,103 +4220,103 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B46" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G46" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B47" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C47" t="str">
-        <v>Other Unavailable</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D47" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E47" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F47" t="str">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B48" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>09:15-16:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E48" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F48" t="str">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B49" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G49" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -4789,25 +4324,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B50" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G50" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -4815,77 +4350,77 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B51" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C51" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D51" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="F51" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="G51" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B52" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E52" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F52" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H52" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B53" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4893,51 +4428,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B54" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C54" t="str">
-        <v>Dependant Leave</v>
+        <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F54" t="str">
-        <v>5.75</v>
+        <v>9</v>
       </c>
       <c r="G54" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B55" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G55" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4945,36 +4480,36 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B56" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G56" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H56" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B57" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -4983,13 +4518,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G57" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4997,16 +4532,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B58" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E58" t="str">
         <v>3.2</v>
@@ -5018,30 +4553,30 @@
         <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B59" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="F59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="G59" t="str">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -5049,25 +4584,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B60" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G60" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -5075,25 +4610,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B61" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>08:30-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G61" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -5101,115 +4636,114 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B62" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C62" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D62" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E62" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F62" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B63" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E63" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F63" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="64">
       <c r="A64" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B64" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C64" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D64" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E64" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F64" t="str">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G64" t="str">
-        <v>0</v>
-      </c>
-      <c r="H64" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B65" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>09:15-16:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E65" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F65" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B66" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -5232,25 +4766,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B67" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G67" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5258,10 +4792,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B68" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -5270,13 +4804,13 @@
         <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G68" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -5284,42 +4818,42 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B69" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="G69" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H69" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B70" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E70" t="str">
         <v>6</v>
@@ -5336,103 +4870,103 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B71" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G71" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B72" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G72" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B73" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H73" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B74" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>09:15-14:45</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G74" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5440,25 +4974,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B75" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5466,42 +5000,42 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B76" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G76" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B77" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E77" t="str">
         <v>6</v>
@@ -5518,51 +5052,51 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B78" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H78" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B79" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="F79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="G79" t="str">
-        <v>3.43</v>
+        <v>9</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -5570,25 +5104,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B80" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G80" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -5596,42 +5130,42 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B81" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>09:15-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G81" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H81" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B82" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D82" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E82" t="str">
         <v>2.67</v>
@@ -5640,457 +5174,41 @@
         <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H82" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B83" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E83" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="F83" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G83" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H83" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D84" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E84" t="str">
-        <v>6</v>
-      </c>
-      <c r="F84" t="str">
-        <v>6</v>
-      </c>
-      <c r="G84" t="str">
-        <v>6</v>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D85" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G85" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Asokhia (NL), Deborah</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D86" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E86" t="str">
-        <v>4</v>
-      </c>
-      <c r="F86" t="str">
-        <v>4</v>
-      </c>
-      <c r="G86" t="str">
-        <v>4</v>
-      </c>
-      <c r="H86" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D87" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E87" t="str">
-        <v>9</v>
-      </c>
-      <c r="F87" t="str">
-        <v>9</v>
-      </c>
-      <c r="G87" t="str">
-        <v>9</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D88" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G88" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D89" t="str">
-        <v>09:15-15:15</v>
-      </c>
-      <c r="E89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D90" t="str">
-        <v>09:15-11:30</v>
-      </c>
-      <c r="E90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G90" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D91" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E91" t="str">
-        <v>6</v>
-      </c>
-      <c r="F91" t="str">
-        <v>6</v>
-      </c>
-      <c r="G91" t="str">
-        <v>6</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B92" t="str">
-        <v>Hume (NL) (GH), Chelsi-Anne</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D92" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G92" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D93" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="E93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G93" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H93" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B94" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D94" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="E94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="F94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="G94" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D95" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G95" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B96" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D96" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="E96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G96" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H96" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B97" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D97" t="str">
-        <v>08:00-17:15</v>
-      </c>
-      <c r="E97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G97" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B98" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C98" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D98" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G98" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B99" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D99" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E99" t="str">
-        <v>6</v>
-      </c>
-      <c r="F99" t="str">
-        <v>6</v>
-      </c>
-      <c r="G99" t="str">
-        <v>6</v>
-      </c>
-      <c r="H99" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,297 +434,297 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E2" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+      <c r="I2" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E3" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+      <c r="I3" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B4" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E4" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+      <c r="I4" t="str">
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B5" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E5" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B6" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E6" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B7" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C7" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E7" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="H7" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>0</v>
+      </c>
+      <c r="I7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E8" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E9" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G9" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B10" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C10" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E10" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H10" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E11" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="12">
@@ -738,22 +738,22 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E12" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="13">
@@ -767,77 +767,77 @@
         <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E13" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F13" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,28 +845,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -874,28 +874,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -903,45 +903,45 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B18" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
       </c>
       <c r="F18" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B20" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B21" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,27 +1008,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B22" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
@@ -1037,27 +1037,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
@@ -1066,62 +1066,62 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="H23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="I23" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B24" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C24" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G24" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H24" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I24" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B25" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C25" t="str">
         <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G25" t="str">
         <v>7.5</v>
@@ -1135,28 +1135,28 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B26" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C26" t="str">
         <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1164,22 +1164,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B27" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C27" t="str">
         <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:00-21:30</v>
+        <v>08:30-21:30</v>
       </c>
       <c r="G27" t="str">
         <v>7.5</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B28" t="str">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="C28" t="str">
         <v>7.5</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1220,82 +1220,83 @@
         <v/>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="B29" t="str">
-        <v>16</v>
+        <v>37.5</v>
       </c>
       <c r="C29" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:00-18:00</v>
+        <v>08:30-14:30</v>
       </c>
       <c r="G29" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="str">
-        <v>8</v>
-      </c>
-      <c r="I29" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="I29" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B30" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H30" t="str">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B31" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C31" t="str">
         <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G31" t="str">
         <v>4</v>
@@ -1304,56 +1305,56 @@
         <v>4</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B32" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C32" t="str">
         <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B33" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C33" t="str">
         <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G33" t="str">
         <v>4</v>
@@ -1362,27 +1363,27 @@
         <v>4</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B34" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
         <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G34" t="str">
         <v>4</v>
@@ -1391,33 +1392,33 @@
         <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B35" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="H35" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1425,28 +1426,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B36" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1454,28 +1455,28 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C37" t="str">
-        <v>6.67</v>
+        <v>2.8</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G37" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H37" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1483,28 +1484,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B38" t="str">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H38" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1512,28 +1513,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B39" t="str">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="G39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="H39" t="str">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1541,16 +1542,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B40" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
@@ -1559,27 +1560,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H40" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B41" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1588,27 +1589,27 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H41" t="str">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B42" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1617,10 +1618,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H42" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1628,7 +1629,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B43" t="str">
         <v>30</v>
@@ -1637,7 +1638,7 @@
         <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1657,7 +1658,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B44" t="str">
         <v>30</v>
@@ -1666,13 +1667,13 @@
         <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G44" t="str">
         <v>7.5</v>
@@ -1686,7 +1687,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B45" t="str">
         <v>30</v>
@@ -1695,7 +1696,7 @@
         <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1715,28 +1716,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B46" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1744,28 +1745,28 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B47" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
       </c>
       <c r="F47" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H47" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1773,28 +1774,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B48" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
       </c>
       <c r="F48" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1802,28 +1803,28 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B49" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1831,28 +1832,28 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B50" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
       </c>
       <c r="F50" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H50" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1860,16 +1861,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B51" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1878,10 +1879,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H51" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1889,16 +1890,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B52" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1907,10 +1908,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="H52" t="str">
-        <v>6</v>
+        <v>6.67</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1918,16 +1919,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B53" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1936,10 +1937,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1947,16 +1948,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B54" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1965,10 +1966,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1976,16 +1977,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B55" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1994,10 +1995,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H55" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2005,161 +2006,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B56" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C56" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B57" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C57" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G57" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B58" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B59" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I59" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B60" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2168,10 +2169,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2179,16 +2180,16 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
       </c>
       <c r="C62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2197,10 +2198,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H62" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2208,16 +2209,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
       </c>
       <c r="C63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2226,10 +2227,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H63" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2237,16 +2238,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
       </c>
       <c r="C64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2255,10 +2256,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H64" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2266,16 +2267,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
       </c>
       <c r="C65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2284,10 +2285,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H65" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2295,28 +2296,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B66" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2324,28 +2325,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B67" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2353,28 +2354,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B68" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2382,28 +2383,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B69" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2411,28 +2412,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B70" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2440,7 +2441,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2449,13 +2450,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2464,12 +2465,12 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B72" t="str">
         <v>16</v>
@@ -2478,13 +2479,13 @@
         <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G72" t="str">
         <v>3.2</v>
@@ -2493,12 +2494,12 @@
         <v>3.2</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B73" t="str">
         <v>16</v>
@@ -2507,13 +2508,13 @@
         <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G73" t="str">
         <v>3.2</v>
@@ -2522,91 +2523,91 @@
         <v>3.2</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B74" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B75" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2614,28 +2615,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2643,28 +2644,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H78" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2672,7 +2673,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B79" t="str">
         <v>30</v>
@@ -2681,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G79" t="str">
         <v>6</v>
@@ -2701,7 +2702,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B80" t="str">
         <v>30</v>
@@ -2710,13 +2711,13 @@
         <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G80" t="str">
         <v>6</v>
@@ -2730,28 +2731,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B81" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H81" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2759,28 +2760,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2788,36 +2789,500 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="B83" t="str">
+        <v>16</v>
+      </c>
+      <c r="C83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2025-09-07</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F83" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="G83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H83" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B84" t="str">
+        <v>16</v>
+      </c>
+      <c r="C84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F84" t="str">
+        <v>09:15-21:30</v>
+      </c>
+      <c r="G84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B85" t="str">
+        <v>16</v>
+      </c>
+      <c r="C85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F85" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H85" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B86" t="str">
+        <v>16</v>
+      </c>
+      <c r="C86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F86" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B87" t="str">
+        <v>16</v>
+      </c>
+      <c r="C87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F87" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H87" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B88" t="str">
+        <v>16</v>
+      </c>
+      <c r="C88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F88" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H88" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B89" t="str">
+        <v>24</v>
+      </c>
+      <c r="C89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F89" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B90" t="str">
+        <v>24</v>
+      </c>
+      <c r="C90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F90" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H90" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B91" t="str">
+        <v>24</v>
+      </c>
+      <c r="C91" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F91" t="str">
+        <v>09:15-16:30</v>
+      </c>
+      <c r="G91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H91" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B92" t="str">
+        <v>24</v>
+      </c>
+      <c r="C92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F92" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H92" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B93" t="str">
+        <v>24</v>
+      </c>
+      <c r="C93" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F93" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G93" t="str">
+        <v>0</v>
+      </c>
+      <c r="H93" t="str">
+        <v>0</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B94" t="str">
         <v>30</v>
       </c>
-      <c r="C83" t="str">
-        <v>6</v>
-      </c>
-      <c r="D83" t="str">
-        <v>2025-09-12</v>
-      </c>
-      <c r="E83" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F83" t="str">
+      <c r="C94" t="str">
+        <v>6</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F94" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="G83" t="str">
-        <v>6</v>
-      </c>
-      <c r="H83" t="str">
-        <v>6</v>
-      </c>
-      <c r="I83" t="str">
-        <v/>
+      <c r="G94" t="str">
+        <v>6</v>
+      </c>
+      <c r="H94" t="str">
+        <v>6</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B95" t="str">
+        <v>30</v>
+      </c>
+      <c r="C95" t="str">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F95" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G95" t="str">
+        <v>6</v>
+      </c>
+      <c r="H95" t="str">
+        <v>6</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B96" t="str">
+        <v>30</v>
+      </c>
+      <c r="C96" t="str">
+        <v>6</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F96" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G96" t="str">
+        <v>6</v>
+      </c>
+      <c r="H96" t="str">
+        <v>6</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B97" t="str">
+        <v>30</v>
+      </c>
+      <c r="C97" t="str">
+        <v>6</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F97" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G97" t="str">
+        <v>6</v>
+      </c>
+      <c r="H97" t="str">
+        <v>6</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B98" t="str">
+        <v>30</v>
+      </c>
+      <c r="C98" t="str">
+        <v>6</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G98" t="str">
+        <v>6</v>
+      </c>
+      <c r="H98" t="str">
+        <v>6</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B99" t="str">
+        <v>30</v>
+      </c>
+      <c r="C99" t="str">
+        <v>6</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Dependant Leave</v>
+      </c>
+      <c r="F99" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G99" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="H99" t="str">
+        <v>0</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2854,13 +3319,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B2" t="str">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="C2" t="str">
-        <v>58.6</v>
+        <v>56.83</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -2869,36 +3334,36 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="G2" t="str">
-        <v>58.6</v>
+        <v>-7.67</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>75.1</v>
+        <v>66.57</v>
       </c>
       <c r="C3" t="str">
-        <v>75.1</v>
+        <v>72.57</v>
       </c>
       <c r="D3" t="str">
-        <v>2.67</v>
+        <v>11.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>65.25</v>
       </c>
       <c r="G3" t="str">
-        <v>75.1</v>
+        <v>7.32</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -2906,25 +3371,25 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B4" t="str">
-        <v>65.44</v>
+        <v>72.57</v>
       </c>
       <c r="C4" t="str">
-        <v>65.44</v>
+        <v>72.57</v>
       </c>
       <c r="D4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>69.75</v>
       </c>
       <c r="G4" t="str">
-        <v>65.44</v>
+        <v>2.82</v>
       </c>
       <c r="H4" t="str">
         <v>Sufficient</v>
@@ -2932,25 +3397,25 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B5" t="str">
-        <v>60.77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="str">
-        <v>60.77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>66.58</v>
       </c>
       <c r="G5" t="str">
-        <v>60.77</v>
+        <v>11.42</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -2958,25 +3423,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>54.1</v>
+        <v>62.9</v>
       </c>
       <c r="C6" t="str">
-        <v>54.1</v>
+        <v>62.9</v>
       </c>
       <c r="D6" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="G6" t="str">
-        <v>54.1</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -2984,54 +3449,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="C7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>42.75</v>
       </c>
       <c r="G7" t="str">
-        <v>42.67</v>
+        <v>-12.58</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="C8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="D8" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="E8" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>40.33</v>
+        <v>-7.17</v>
       </c>
       <c r="H8" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +3508,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H99"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3071,36 +3536,35 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C2" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="str">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3115,10 +3579,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3126,33 +3590,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B4" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C4" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G4" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3167,10 +3631,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3178,129 +3642,130 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H6" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="9">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B9" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:00-15:15</v>
+        <v>08:30-14:30</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F9" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="str">
-        <v>4</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
+        <v>7.5</v>
+      </c>
+      <c r="H9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Office hours
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B10" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -3308,103 +3773,104 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B11" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C11" t="str">
         <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>08:00-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B12" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D12" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E12" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="F12" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="G12" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E13" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F13" t="str">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="G13" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H13" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B14" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E14" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F14" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3412,51 +3878,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B15" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G15" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B16" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3464,25 +3930,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B17" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="F17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="G17" t="str">
-        <v>9</v>
+        <v>5.33</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3490,25 +3956,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B18" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
       </c>
       <c r="D18" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="F18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="G18" t="str">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3516,25 +3982,25 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B19" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C19" t="str">
         <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -3542,130 +4008,129 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C20" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D20" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B21" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E21" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F21" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G21" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B22" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D22" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
-      </c>
-      <c r="H22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
+        <v>6</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B23" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C23" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D23" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E23" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F23" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="G23" t="str">
         <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B24" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G24" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -3673,25 +4138,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B25" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G25" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -3699,51 +4164,51 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B26" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="F26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="G26" t="str">
-        <v>5.33</v>
+        <v>10</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B27" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G27" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -3751,16 +4216,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B28" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C28" t="str">
         <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E28" t="str">
         <v>6</v>
@@ -3777,78 +4242,77 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C29" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E29" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="F29" t="str">
-        <v>7.5</v>
+        <v>3.43</v>
       </c>
       <c r="G29" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B30" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C30" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E30" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="F30" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="G30" t="str">
-        <v>0</v>
-      </c>
-      <c r="H30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+        <v>4</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B31" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C31" t="str">
         <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E31" t="str">
-        <v>6.67</v>
+        <v>5.33</v>
       </c>
       <c r="F31" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="G31" t="str">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -3856,51 +4320,51 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B32" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C32" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D32" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G32" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B33" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
       </c>
       <c r="D33" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E33" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F33" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G33" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -3908,51 +4372,51 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B35" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G35" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -3960,36 +4424,36 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B36" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
       </c>
       <c r="D36" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G36" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H36" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B37" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
@@ -4012,51 +4476,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B38" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B39" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="F39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="G39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4064,7 +4528,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4073,7 +4537,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4085,30 +4549,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B41" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="E41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4116,10 +4580,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B42" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4140,53 +4604,54 @@
         <v/>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B43" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C43" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D43" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F43" t="str">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="G43" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H43" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v>0</v>
+      </c>
+      <c r="H43" t="str" xml:space="preserve">
+        <v xml:space="preserve">Moved day to Friday
+Eilidh 27/08/2025</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E44" t="str">
         <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -4194,25 +4659,25 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B45" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C45" t="str">
         <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G45" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -4220,103 +4685,103 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B46" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B47" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C47" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D47" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E47" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F47" t="str">
-        <v>2.67</v>
+        <v>2</v>
       </c>
       <c r="G47" t="str">
         <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B48" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-16:15</v>
       </c>
       <c r="E48" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F48" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="G48" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="H48" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B49" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C49" t="str">
         <v>Available</v>
       </c>
       <c r="D49" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G49" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -4324,25 +4789,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H50" t="str">
         <v/>
@@ -4350,77 +4815,77 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B51" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C51" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D51" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="F51" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="G51" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B52" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C52" t="str">
         <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E52" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F52" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B53" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4428,51 +4893,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C54" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D54" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E54" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F54" t="str">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="G54" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B55" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G55" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4480,36 +4945,36 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B56" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G56" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B57" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
@@ -4518,13 +4983,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G57" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4532,16 +4997,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E58" t="str">
         <v>3.2</v>
@@ -4553,30 +5018,30 @@
         <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="F59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -4584,25 +5049,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B60" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H60" t="str">
         <v/>
@@ -4610,25 +5075,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C61" t="str">
         <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>08:00-15:00</v>
+        <v>08:30-21:30</v>
       </c>
       <c r="E61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G61" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
         <v/>
@@ -4636,114 +5101,115 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B62" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C62" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D62" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E62" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F62" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G62" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H62" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B63" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E63" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F63" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G63" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D64" t="str">
+        <v>10:30-12:30</v>
+      </c>
+      <c r="E64" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2</v>
+      </c>
+      <c r="G64" t="str">
         <v>0</v>
       </c>
-      <c r="G63" t="str">
-        <v>0</v>
-      </c>
-      <c r="H63" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>2025-09-09</v>
-      </c>
-      <c r="B64" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D64" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E64" t="str">
-        <v>6</v>
-      </c>
-      <c r="F64" t="str">
-        <v>6</v>
-      </c>
-      <c r="G64" t="str">
-        <v>6</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
+      <c r="H64" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-16:30</v>
       </c>
       <c r="E65" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="G65" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B66" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
@@ -4766,25 +5232,25 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B67" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G67" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -4792,10 +5258,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B68" t="str">
-        <v>Ferris, Marykate</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
@@ -4804,13 +5270,13 @@
         <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="F68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="G68" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -4818,42 +5284,42 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B69" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B70" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E70" t="str">
         <v>6</v>
@@ -4870,103 +5336,103 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B71" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G71" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>08:00-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G73" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B74" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -4974,25 +5440,25 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -5000,42 +5466,42 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B76" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G76" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H76" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B77" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E77" t="str">
         <v>6</v>
@@ -5052,51 +5518,51 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B78" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B79" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C79" t="str">
         <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="F79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="G79" t="str">
-        <v>9</v>
+        <v>3.43</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -5104,25 +5570,25 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B80" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -5130,42 +5596,42 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B81" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G81" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B82" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D82" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E82" t="str">
         <v>2.67</v>
@@ -5174,41 +5640,457 @@
         <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B83" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E83" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="F83" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G83" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H83" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D84" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E84" t="str">
+        <v>6</v>
+      </c>
+      <c r="F84" t="str">
+        <v>6</v>
+      </c>
+      <c r="G84" t="str">
+        <v>6</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D85" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G85" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D86" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E86" t="str">
+        <v>4</v>
+      </c>
+      <c r="F86" t="str">
+        <v>4</v>
+      </c>
+      <c r="G86" t="str">
+        <v>4</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D87" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E87" t="str">
+        <v>9</v>
+      </c>
+      <c r="F87" t="str">
+        <v>9</v>
+      </c>
+      <c r="G87" t="str">
+        <v>9</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D88" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G88" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D89" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D90" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G90" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D91" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E91" t="str">
+        <v>6</v>
+      </c>
+      <c r="F91" t="str">
+        <v>6</v>
+      </c>
+      <c r="G91" t="str">
+        <v>6</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Hume (NL) (GH), Chelsi-Anne</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D92" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G92" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D93" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G93" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D94" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="E94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G94" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D95" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G95" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B96" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D96" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G96" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D97" t="str">
+        <v>08:00-17:15</v>
+      </c>
+      <c r="E97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G97" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B98" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D98" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G98" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D99" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E99" t="str">
+        <v>6</v>
+      </c>
+      <c r="F99" t="str">
+        <v>6</v>
+      </c>
+      <c r="G99" t="str">
+        <v>6</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H99"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,297 +434,296 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B2" t="str">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E2" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G2" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
+      <c r="I2" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B3" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E3" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+      <c r="I3" t="str">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B4" t="str">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E4" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="F4" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G4" t="str">
-        <v>6.67</v>
+        <v>3.43</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+      <c r="I4" t="str">
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B5" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E5" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G5" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B6" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E6" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Holiday</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="G6" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B7" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C7" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E7" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F7" t="str">
-        <v>10:30-14:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H7" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B8" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C8" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E8" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H8" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+        <v>0</v>
+      </c>
+      <c r="I8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="B9" t="str">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C9" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E9" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="G9" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H9" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B10" t="str">
         <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E10" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E11" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="12">
@@ -738,106 +737,106 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E12" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B13" t="str">
         <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E13" t="str">
         <v>Available</v>
       </c>
       <c r="F13" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,28 +844,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -874,45 +873,45 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B18" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -921,27 +920,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +949,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B20" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +978,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B21" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,242 +1007,242 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B22" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
       </c>
       <c r="F22" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B23" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C23" t="str">
-        <v>10</v>
+        <v>2.67</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G23" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B24" t="str">
         <v>20</v>
       </c>
       <c r="C24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I24" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B25" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B26" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B27" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C27" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G27" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H27" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B28" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C28" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
       </c>
       <c r="F28" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G28" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B29" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C29" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G29" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1251,28 +1250,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B30" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C30" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G30" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="H30" t="str">
-        <v>8</v>
+        <v>2.8</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1280,28 +1279,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B31" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C31" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="G31" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1309,28 +1308,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B32" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C32" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H32" t="str">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1338,28 +1337,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="B33" t="str">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="G33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="H33" t="str">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1367,74 +1366,74 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B34" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H34" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B35" t="str">
         <v>20</v>
       </c>
       <c r="C35" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G35" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="H35" t="str">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B36" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C36" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1443,10 +1442,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G36" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H36" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1454,16 +1453,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C37" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1472,10 +1471,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G37" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H37" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1483,16 +1482,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B38" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C38" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1501,10 +1500,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H38" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1512,16 +1511,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B39" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C39" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1530,10 +1529,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G39" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H39" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1541,28 +1540,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B40" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C40" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
       </c>
       <c r="F40" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G40" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1570,28 +1569,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B41" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
       </c>
       <c r="F41" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G41" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" t="str">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1599,28 +1598,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B42" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C42" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
       </c>
       <c r="F42" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G42" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H42" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1628,28 +1627,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B43" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
       </c>
       <c r="F43" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1657,16 +1656,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B44" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
@@ -1675,10 +1674,10 @@
         <v>08:00-15:15</v>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H44" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1686,28 +1685,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B45" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
       </c>
       <c r="F45" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H45" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1715,28 +1714,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B46" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C46" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G46" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H46" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1744,16 +1743,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B47" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C47" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1762,10 +1761,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G47" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H47" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1773,16 +1772,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B48" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C48" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1791,10 +1790,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G48" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H48" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1802,16 +1801,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B49" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C49" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
@@ -1820,10 +1819,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G49" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H49" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1831,16 +1830,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B50" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C50" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1849,10 +1848,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H50" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1860,16 +1859,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B51" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C51" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1878,10 +1877,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H51" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1889,16 +1888,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B52" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C52" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1907,10 +1906,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1918,16 +1917,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B53" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C53" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1936,10 +1935,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H53" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1947,28 +1946,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B54" t="str">
         <v>30</v>
       </c>
       <c r="C54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
       </c>
       <c r="F54" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1976,16 +1975,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B55" t="str">
         <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1994,10 +1993,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2005,161 +2004,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B56" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C56" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H56" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I56" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B57" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C57" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G57" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H57" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I57" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B58" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H58" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B59" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I59" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B60" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2168,10 +2167,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2179,7 +2178,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
@@ -2188,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2208,7 +2207,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
@@ -2217,7 +2216,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2237,7 +2236,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
@@ -2246,7 +2245,7 @@
         <v>6</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2266,7 +2265,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
@@ -2275,7 +2274,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2295,28 +2294,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B66" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2324,65 +2323,65 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B67" t="str">
         <v>16</v>
       </c>
       <c r="C67" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-13:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G67" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H67" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B68" t="str">
         <v>16</v>
       </c>
       <c r="C68" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G68" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="H68" t="str">
-        <v>5.33</v>
+        <v>3.2</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B69" t="str">
         <v>16</v>
@@ -2391,13 +2390,13 @@
         <v>3.2</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G69" t="str">
         <v>3.2</v>
@@ -2406,12 +2405,12 @@
         <v>3.2</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B70" t="str">
         <v>16</v>
@@ -2420,13 +2419,13 @@
         <v>3.2</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G70" t="str">
         <v>3.2</v>
@@ -2435,12 +2434,12 @@
         <v>3.2</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2449,13 +2448,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2464,33 +2463,33 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B72" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H72" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2498,28 +2497,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B73" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2527,28 +2526,28 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B74" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C74" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G74" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H74" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2556,28 +2555,28 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B75" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -2585,28 +2584,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H76" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2614,28 +2613,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B77" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C77" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H77" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2643,28 +2642,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B78" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-14:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G78" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H78" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2672,28 +2671,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B79" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C79" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-07</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G79" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H79" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2701,57 +2700,57 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B80" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C80" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-01</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-21:30</v>
       </c>
       <c r="G80" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H80" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B81" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C81" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-02</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H81" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2759,28 +2758,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-03</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2788,36 +2787,384 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B83" t="str">
+        <v>16</v>
+      </c>
+      <c r="C83" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F83" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G83" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H83" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="B84" t="str">
+        <v>16</v>
+      </c>
+      <c r="C84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F84" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="G84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H84" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B85" t="str">
+        <v>24</v>
+      </c>
+      <c r="C85" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F85" t="str">
+        <v>09:15-10:15</v>
+      </c>
+      <c r="G85" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H85" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B86" t="str">
+        <v>24</v>
+      </c>
+      <c r="C86" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F86" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G86" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H86" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B87" t="str">
+        <v>24</v>
+      </c>
+      <c r="C87" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F87" t="str">
+        <v>09:15-16:30</v>
+      </c>
+      <c r="G87" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="H87" t="str">
+        <v>1.43</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B88" t="str">
+        <v>24</v>
+      </c>
+      <c r="C88" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F88" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="G88" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H88" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="B89" t="str">
+        <v>24</v>
+      </c>
+      <c r="C89" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F89" t="str">
+        <v>09:15-17:00</v>
+      </c>
+      <c r="G89" t="str">
+        <v>0</v>
+      </c>
+      <c r="H89" t="str">
+        <v>0</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B90" t="str">
         <v>30</v>
       </c>
-      <c r="C83" t="str">
-        <v>6</v>
-      </c>
-      <c r="D83" t="str">
-        <v>2025-09-12</v>
-      </c>
-      <c r="E83" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F83" t="str">
+      <c r="C90" t="str">
+        <v>6</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2025-09-01</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F90" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="G83" t="str">
-        <v>6</v>
-      </c>
-      <c r="H83" t="str">
-        <v>6</v>
-      </c>
-      <c r="I83" t="str">
-        <v/>
+      <c r="G90" t="str">
+        <v>6</v>
+      </c>
+      <c r="H90" t="str">
+        <v>6</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B91" t="str">
+        <v>30</v>
+      </c>
+      <c r="C91" t="str">
+        <v>6</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F91" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G91" t="str">
+        <v>6</v>
+      </c>
+      <c r="H91" t="str">
+        <v>6</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B92" t="str">
+        <v>30</v>
+      </c>
+      <c r="C92" t="str">
+        <v>6</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2025-09-03</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F92" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G92" t="str">
+        <v>6</v>
+      </c>
+      <c r="H92" t="str">
+        <v>6</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B93" t="str">
+        <v>30</v>
+      </c>
+      <c r="C93" t="str">
+        <v>6</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F93" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G93" t="str">
+        <v>6</v>
+      </c>
+      <c r="H93" t="str">
+        <v>6</v>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B94" t="str">
+        <v>30</v>
+      </c>
+      <c r="C94" t="str">
+        <v>6</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2025-09-05</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F94" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G94" t="str">
+        <v>6</v>
+      </c>
+      <c r="H94" t="str">
+        <v>6</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B95" t="str">
+        <v>30</v>
+      </c>
+      <c r="C95" t="str">
+        <v>6</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2025-09-02</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Dependant Leave</v>
+      </c>
+      <c r="F95" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G95" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="H95" t="str">
+        <v>0</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I95"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2854,13 +3201,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B2" t="str">
-        <v>58.6</v>
+        <v>57.33</v>
       </c>
       <c r="C2" t="str">
-        <v>58.6</v>
+        <v>57.33</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -2869,36 +3216,36 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>64.5</v>
       </c>
       <c r="G2" t="str">
-        <v>58.6</v>
+        <v>-7.17</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B3" t="str">
-        <v>75.1</v>
+        <v>74.57</v>
       </c>
       <c r="C3" t="str">
-        <v>75.1</v>
+        <v>80.57</v>
       </c>
       <c r="D3" t="str">
-        <v>2.67</v>
+        <v>4.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>65.25</v>
       </c>
       <c r="G3" t="str">
-        <v>75.1</v>
+        <v>15.32</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -2906,51 +3253,51 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B4" t="str">
-        <v>65.44</v>
+        <v>65.07</v>
       </c>
       <c r="C4" t="str">
-        <v>65.44</v>
+        <v>65.07</v>
       </c>
       <c r="D4" t="str">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>69.75</v>
       </c>
       <c r="G4" t="str">
-        <v>65.44</v>
+        <v>-4.68</v>
       </c>
       <c r="H4" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B5" t="str">
-        <v>60.77</v>
+        <v>70.5</v>
       </c>
       <c r="C5" t="str">
-        <v>60.77</v>
+        <v>70.5</v>
       </c>
       <c r="D5" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>66.58</v>
       </c>
       <c r="G5" t="str">
-        <v>60.77</v>
+        <v>3.92</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -2958,25 +3305,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>54.1</v>
+        <v>55.4</v>
       </c>
       <c r="C6" t="str">
-        <v>54.1</v>
+        <v>55.4</v>
       </c>
       <c r="D6" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="G6" t="str">
-        <v>54.1</v>
+        <v>3.9</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -2984,54 +3331,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="C7" t="str">
-        <v>42.67</v>
+        <v>30.17</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>42.75</v>
       </c>
       <c r="G7" t="str">
-        <v>42.67</v>
+        <v>-12.58</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="C8" t="str">
-        <v>40.33</v>
+        <v>32.83</v>
       </c>
       <c r="D8" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="E8" t="str">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G8" t="str">
-        <v>40.33</v>
+        <v>-7.17</v>
       </c>
       <c r="H8" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +3390,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3071,36 +3418,35 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B2" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C2" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F2" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="str">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Has appointment and is unable to work 
-Eilidh 22/08/2025</v>
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3115,10 +3461,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3126,33 +3472,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B4" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C4" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="G4" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3167,10 +3513,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3178,103 +3524,103 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="F6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="G6" t="str">
-        <v>3.2</v>
+        <v>6.67</v>
       </c>
       <c r="H6" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B8" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B9" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E9" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -3282,16 +3628,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B10" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E10" t="str">
         <v>3.2</v>
@@ -3303,82 +3649,83 @@
         <v>3.2</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B11" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C11" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D11" t="str">
-        <v>08:00-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E11" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F11" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="G11" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
+        <v>Created by new vacation process.</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B12" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C12" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D12" t="str">
-        <v>08:00-13:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E12" t="str">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="F12" t="str">
-        <v>5.33</v>
+        <v>2</v>
       </c>
       <c r="G12" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H12" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C13" t="str">
         <v>Available</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E13" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F13" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="G13" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -3386,25 +3733,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B14" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E14" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F14" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G14" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3412,51 +3759,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B15" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E15" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F15" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B16" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E16" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F16" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G16" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3464,25 +3811,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B17" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E17" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F17" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3490,10 +3837,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B18" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
@@ -3502,13 +3849,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E18" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="F18" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="G18" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3516,36 +3863,36 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B19" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C19" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D19" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E19" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F19" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="G19" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B20" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C20" t="str">
         <v>Available</v>
@@ -3554,13 +3901,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G20" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -3568,60 +3915,59 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B21" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E21" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F21" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G21" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H21" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B22" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C22" t="str">
-        <v>Other Unavailable</v>
+        <v>Holiday</v>
       </c>
       <c r="D22" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E22" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F22" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="G22" t="str">
         <v>0</v>
       </c>
-      <c r="H22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Family event
-Eilidh 01/09/2025</v>
+      <c r="H22" t="str">
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B23" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
@@ -3636,10 +3982,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -3647,25 +3993,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B24" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E24" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F24" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="G24" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -3673,51 +4019,51 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-06</v>
       </c>
       <c r="B25" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E25" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F25" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G25" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B26" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E26" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F26" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G26" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -3725,25 +4071,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B27" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E27" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F27" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G27" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -3751,130 +4097,129 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B28" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C28" t="str">
-        <v>Available</v>
+        <v>Holiday</v>
       </c>
       <c r="D28" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-17:00</v>
       </c>
       <c r="E28" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="F28" t="str">
-        <v>6</v>
+        <v>3.43</v>
       </c>
       <c r="G28" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>Created by new vacation process.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C29" t="str">
         <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E29" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G29" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="str">
         <v/>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
+    <row r="30">
       <c r="A30" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B30" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C30" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E30" t="str">
-        <v>6.67</v>
+        <v>5.33</v>
       </c>
       <c r="F30" t="str">
-        <v>6.67</v>
+        <v>5.33</v>
       </c>
       <c r="G30" t="str">
-        <v>0</v>
-      </c>
-      <c r="H30" t="str" xml:space="preserve">
-        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
-Eilidh 01/09/2025</v>
+        <v>5.33</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B31" t="str">
-        <v>Ferris, Marykate</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C31" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D31" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E31" t="str">
-        <v>6.67</v>
+        <v>2.67</v>
       </c>
       <c r="F31" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B32" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C32" t="str">
         <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E32" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F32" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G32" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -3882,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-07</v>
       </c>
       <c r="B33" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
@@ -3894,39 +4239,39 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E33" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F33" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="G33" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E34" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F34" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -3934,36 +4279,36 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B35" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E35" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="F35" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="G35" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B36" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
@@ -3972,39 +4317,39 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E36" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F36" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G36" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H36" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B37" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
       </c>
       <c r="D37" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E37" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F37" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G37" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -4012,51 +4357,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B38" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G38" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B39" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="F39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="G39" t="str">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4064,7 +4409,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4073,7 +4418,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4085,30 +4430,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B41" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-11:30</v>
       </c>
       <c r="E41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4116,10 +4461,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B42" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4142,103 +4487,103 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B43" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C43" t="str">
         <v>Available</v>
       </c>
       <c r="D43" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E43" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F43" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G43" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H43" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E44" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F44" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B45" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C45" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D45" t="str">
-        <v>16:45-21:30</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E45" t="str">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="F45" t="str">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="G45" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B46" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>08:00-15:00</v>
+        <v>09:15-16:15</v>
       </c>
       <c r="E46" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F46" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="G46" t="str">
-        <v>4</v>
+        <v>1.43</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4246,114 +4591,114 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B47" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C47" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D47" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E47" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F47" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G47" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H47" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B48" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E48" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F48" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="G48" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H48" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B49" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C49" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D49" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E49" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F49" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G49" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E50" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F50" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G50" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B51" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
@@ -4362,65 +4707,65 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G51" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H51" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-02</v>
       </c>
       <c r="B52" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C52" t="str">
-        <v>Available</v>
+        <v>Dependant Leave</v>
       </c>
       <c r="D52" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E52" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F52" t="str">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="G52" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B53" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E53" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F53" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G53" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4428,51 +4773,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B54" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E54" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F54" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G54" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B55" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E55" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="F55" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="G55" t="str">
-        <v>3.2</v>
+        <v>9</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4480,25 +4825,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B56" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E56" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F56" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G56" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -4506,25 +4851,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B57" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
       </c>
       <c r="D57" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E57" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="F57" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="G57" t="str">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4532,51 +4877,51 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B59" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E59" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F59" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -4584,16 +4929,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B60" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E60" t="str">
         <v>3.2</v>
@@ -4605,108 +4950,109 @@
         <v>3.2</v>
       </c>
       <c r="H60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B61" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C61" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D61" t="str">
-        <v>08:00-15:00</v>
+        <v>10:30-12:30</v>
       </c>
       <c r="E61" t="str">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="F61" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G61" t="str">
-        <v>4</v>
-      </c>
-      <c r="H61" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H61" t="str" xml:space="preserve">
+        <v xml:space="preserve">Wants this as a break. 
+Eilidh 29/05/2025</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B62" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C62" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D62" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-16:30</v>
       </c>
       <c r="E62" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F62" t="str">
-        <v>2.67</v>
+        <v>1.43</v>
       </c>
       <c r="G62" t="str">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="H62" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B63" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E63" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F63" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G63" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H63" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B64" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C64" t="str">
         <v>Available</v>
       </c>
       <c r="D64" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E64" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F64" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G64" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -4714,77 +5060,77 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B65" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E65" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F65" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G65" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H65" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B66" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
       </c>
       <c r="D66" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E66" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F66" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G66" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-03</v>
       </c>
       <c r="B67" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E67" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F67" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G67" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -4792,51 +5138,51 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B68" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
       </c>
       <c r="D68" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E68" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="F68" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="G68" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B69" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E69" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F69" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -4844,25 +5190,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B70" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E70" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F70" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G70" t="str">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -4870,77 +5216,77 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B71" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G71" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B72" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Gabillard (NL), Donna</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>09:15-15:00</v>
+        <v>09:15-14:45</v>
       </c>
       <c r="E72" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F72" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="H72" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B73" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E73" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F73" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G73" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -4948,25 +5294,25 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B74" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G74" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -4974,77 +5320,77 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>08:00-14:00</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="F75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B76" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Jack (NL), Sharon</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-10:15</v>
       </c>
       <c r="E76" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="F76" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="G76" t="str">
-        <v>2.67</v>
+        <v>3.43</v>
       </c>
       <c r="H76" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B77" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G77" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -5052,103 +5398,103 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B78" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-21:30</v>
       </c>
       <c r="E78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G78" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B79" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C79" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D79" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E79" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="F79" t="str">
-        <v>9</v>
+        <v>2.67</v>
       </c>
       <c r="G79" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>Brooke has a colonoscopy appointment - MT</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B80" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E80" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F80" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G80" t="str">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-01</v>
       </c>
       <c r="B81" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E81" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F81" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G81" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -5156,10 +5502,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B82" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C82" t="str">
         <v>Available</v>
@@ -5168,13 +5514,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E82" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F82" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G82" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -5182,33 +5528,345 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-04</v>
       </c>
       <c r="B83" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E83" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F83" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G83" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H83" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D84" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E84" t="str">
+        <v>9</v>
+      </c>
+      <c r="F84" t="str">
+        <v>9</v>
+      </c>
+      <c r="G84" t="str">
+        <v>9</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Ferris, Marykate</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D85" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E85" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F85" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G85" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D86" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G86" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Gabillard (NL), Donna</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D87" t="str">
+        <v>09:15-11:30</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="F87" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="G87" t="str">
+        <v>2.8</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D88" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E88" t="str">
+        <v>6</v>
+      </c>
+      <c r="F88" t="str">
+        <v>6</v>
+      </c>
+      <c r="G88" t="str">
+        <v>6</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D89" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G89" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Jack (NL), Sharon</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D90" t="str">
+        <v>09:15-16:15</v>
+      </c>
+      <c r="E90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="F90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="G90" t="str">
+        <v>3.43</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D91" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G91" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B92" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D92" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G92" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Nelson (NL), Anne</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D93" t="str">
+        <v>08:00-17:15</v>
+      </c>
+      <c r="E93" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="F93" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="G93" t="str">
+        <v>5.33</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B94" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D94" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F94" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2025-09-04</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D95" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E95" t="str">
+        <v>6</v>
+      </c>
+      <c r="F95" t="str">
+        <v>6</v>
+      </c>
+      <c r="G95" t="str">
+        <v>6</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,296 +434,297 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B2" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E2" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G2" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H2" t="str">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B3" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E3" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F3" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G3" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
-      <c r="I3" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="I3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B4" t="str">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="D4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E4" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F4" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G4" t="str">
-        <v>3.43</v>
+        <v>6.67</v>
       </c>
       <c r="H4" t="str">
         <v>0</v>
       </c>
-      <c r="I4" t="str">
-        <v>Created by new vacation process.</v>
+      <c r="I4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B5" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D5" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E5" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F5" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G5" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B6" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="D6" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E6" t="str">
-        <v>Holiday</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F6" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G6" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H6" t="str">
         <v>0</v>
       </c>
       <c r="I6" t="str">
-        <v>Created by new vacation process.</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B7" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E7" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F7" t="str">
-        <v>10:30-12:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G7" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B8" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C8" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E8" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F8" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G8" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v>0</v>
-      </c>
-      <c r="I8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
-      </c>
-    </row>
-    <row r="9" xml:space="preserve">
+        <v>3.2</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B9" t="str">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E9" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="F9" t="str">
-        <v>10:30-12:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G9" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="H9" t="str">
-        <v>0</v>
-      </c>
-      <c r="I9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>3.2</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B10" t="str">
         <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E10" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G10" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E11" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F11" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="12">
@@ -737,106 +738,106 @@
         <v>2.67</v>
       </c>
       <c r="D12" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E12" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="F12" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H12" t="str">
         <v>0</v>
       </c>
       <c r="I12" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B13" t="str">
         <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D13" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E13" t="str">
         <v>Available</v>
       </c>
       <c r="F13" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G13" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D14" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E14" t="str">
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H14" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D15" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E15" t="str">
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H15" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -844,28 +845,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D16" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E16" t="str">
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H16" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -873,45 +874,45 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B17" t="str">
         <v>16</v>
       </c>
       <c r="C17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H17" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="I17" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B18" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -920,27 +921,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I18" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B19" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C19" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -949,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B20" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C20" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -978,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H20" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="I20" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B21" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1007,242 +1008,242 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="H21" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B22" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C22" t="str">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
       </c>
       <c r="F22" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H22" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B23" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23" t="str">
-        <v>2.67</v>
+        <v>10</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G23" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H23" t="str">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B24" t="str">
         <v>20</v>
       </c>
       <c r="C24" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G24" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H24" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I24" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B25" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C25" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G25" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H25" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I25" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B26" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C26" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G26" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I26" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B27" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C27" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G27" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I27" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B28" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C28" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
       </c>
       <c r="F28" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G28" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I28" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B29" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C29" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G29" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="H29" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1250,28 +1251,28 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B30" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C30" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="D30" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E30" t="str">
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G30" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="H30" t="str">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1279,28 +1280,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B31" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D31" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E31" t="str">
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H31" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1308,28 +1309,28 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B32" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C32" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D32" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E32" t="str">
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G32" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H32" t="str">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1337,28 +1338,28 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B33" t="str">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D33" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E33" t="str">
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>09:15-10:15</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1366,74 +1367,74 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B34" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I34" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B35" t="str">
         <v>20</v>
       </c>
       <c r="C35" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G35" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="H35" t="str">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="I35" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B36" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C36" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
@@ -1442,10 +1443,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G36" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H36" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1453,16 +1454,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="B37" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C37" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
@@ -1471,10 +1472,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G37" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H37" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1482,16 +1483,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B38" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
@@ -1500,10 +1501,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H38" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1511,16 +1512,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B39" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C39" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
@@ -1529,10 +1530,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G39" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H39" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1540,28 +1541,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B40" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C40" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
       </c>
       <c r="F40" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H40" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1569,28 +1570,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B41" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C41" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
       </c>
       <c r="F41" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H41" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1598,28 +1599,28 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B42" t="str">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C42" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
       </c>
       <c r="F42" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H42" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1627,28 +1628,28 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B43" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
       </c>
       <c r="F43" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H43" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1656,16 +1657,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B44" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
@@ -1674,10 +1675,10 @@
         <v>08:00-15:15</v>
       </c>
       <c r="G44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1685,28 +1686,28 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B45" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
       </c>
       <c r="F45" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H45" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1714,28 +1715,28 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B46" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C46" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
       </c>
       <c r="F46" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G46" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H46" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1743,16 +1744,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B47" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C47" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1761,10 +1762,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G47" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H47" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1772,16 +1773,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B48" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C48" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1790,10 +1791,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G48" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="H48" t="str">
-        <v>6.67</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -1801,16 +1802,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B49" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C49" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
@@ -1819,10 +1820,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G49" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -1830,16 +1831,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B50" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C50" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1848,10 +1849,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G50" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -1859,16 +1860,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B51" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C51" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1877,10 +1878,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H51" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1888,16 +1889,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B52" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C52" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1906,10 +1907,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H52" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1917,16 +1918,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B53" t="str">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C53" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1935,10 +1936,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H53" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1946,28 +1947,28 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B54" t="str">
         <v>30</v>
       </c>
       <c r="C54" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
       </c>
       <c r="F54" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H54" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1975,16 +1976,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B55" t="str">
         <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1993,10 +1994,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H55" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2004,161 +2005,161 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B56" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C56" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D56" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E56" t="str">
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G56" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H56" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B57" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C57" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D57" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E57" t="str">
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G57" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H57" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B58" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D58" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E58" t="str">
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B59" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H59" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B60" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H60" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B61" t="str">
         <v>30</v>
       </c>
       <c r="C61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D61" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E61" t="str">
         <v>Available</v>
@@ -2167,10 +2168,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H61" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2178,7 +2179,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B62" t="str">
         <v>30</v>
@@ -2187,7 +2188,7 @@
         <v>6</v>
       </c>
       <c r="D62" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E62" t="str">
         <v>Available</v>
@@ -2207,7 +2208,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B63" t="str">
         <v>30</v>
@@ -2216,7 +2217,7 @@
         <v>6</v>
       </c>
       <c r="D63" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E63" t="str">
         <v>Available</v>
@@ -2236,7 +2237,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B64" t="str">
         <v>30</v>
@@ -2245,7 +2246,7 @@
         <v>6</v>
       </c>
       <c r="D64" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E64" t="str">
         <v>Available</v>
@@ -2265,7 +2266,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B65" t="str">
         <v>30</v>
@@ -2274,7 +2275,7 @@
         <v>6</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
@@ -2294,28 +2295,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B66" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="H66" t="str">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2323,65 +2324,65 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B67" t="str">
         <v>16</v>
       </c>
       <c r="C67" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G67" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H67" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="I67" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B68" t="str">
         <v>16</v>
       </c>
       <c r="C68" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G68" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H68" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="I68" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B69" t="str">
         <v>16</v>
@@ -2390,13 +2391,13 @@
         <v>3.2</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G69" t="str">
         <v>3.2</v>
@@ -2405,12 +2406,12 @@
         <v>3.2</v>
       </c>
       <c r="I69" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B70" t="str">
         <v>16</v>
@@ -2419,13 +2420,13 @@
         <v>3.2</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G70" t="str">
         <v>3.2</v>
@@ -2434,12 +2435,12 @@
         <v>3.2</v>
       </c>
       <c r="I70" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
@@ -2448,13 +2449,13 @@
         <v>3.2</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G71" t="str">
         <v>3.2</v>
@@ -2463,33 +2464,33 @@
         <v>3.2</v>
       </c>
       <c r="I71" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B72" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2497,28 +2498,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B73" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H73" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2526,28 +2527,28 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B74" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C74" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D74" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E74" t="str">
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G74" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H74" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2555,28 +2556,28 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B75" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D75" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E75" t="str">
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -2584,28 +2585,28 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B76" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D76" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E76" t="str">
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2613,28 +2614,28 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B77" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C77" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D77" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E77" t="str">
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G77" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2642,28 +2643,28 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B78" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C78" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="D78" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E78" t="str">
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G78" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="H78" t="str">
-        <v>5.33</v>
+        <v>4</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2671,28 +2672,28 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B79" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C79" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D79" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E79" t="str">
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>08:00-18:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G79" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H79" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2700,57 +2701,57 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B80" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C80" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D80" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E80" t="str">
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>09:15-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G80" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I80" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B81" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C81" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D81" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E81" t="str">
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G81" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H81" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2758,28 +2759,28 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B82" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C82" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D82" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E82" t="str">
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G82" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H82" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2787,384 +2788,36 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="B83" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C83" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D83" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E83" t="str">
         <v>Available</v>
       </c>
       <c r="F83" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G83" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H83" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I83" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="B84" t="str">
-        <v>16</v>
-      </c>
-      <c r="C84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D84" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F84" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="G84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H84" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B85" t="str">
-        <v>24</v>
-      </c>
-      <c r="C85" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D85" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F85" t="str">
-        <v>09:15-10:15</v>
-      </c>
-      <c r="G85" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H85" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B86" t="str">
-        <v>24</v>
-      </c>
-      <c r="C86" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D86" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F86" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G86" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H86" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B87" t="str">
-        <v>24</v>
-      </c>
-      <c r="C87" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D87" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F87" t="str">
-        <v>09:15-16:30</v>
-      </c>
-      <c r="G87" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="H87" t="str">
-        <v>1.43</v>
-      </c>
-      <c r="I87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B88" t="str">
-        <v>24</v>
-      </c>
-      <c r="C88" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D88" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F88" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="G88" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H88" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="I88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="B89" t="str">
-        <v>24</v>
-      </c>
-      <c r="C89" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="D89" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F89" t="str">
-        <v>09:15-17:00</v>
-      </c>
-      <c r="G89" t="str">
-        <v>0</v>
-      </c>
-      <c r="H89" t="str">
-        <v>0</v>
-      </c>
-      <c r="I89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B90" t="str">
-        <v>30</v>
-      </c>
-      <c r="C90" t="str">
-        <v>6</v>
-      </c>
-      <c r="D90" t="str">
-        <v>2025-09-01</v>
-      </c>
-      <c r="E90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F90" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G90" t="str">
-        <v>6</v>
-      </c>
-      <c r="H90" t="str">
-        <v>6</v>
-      </c>
-      <c r="I90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B91" t="str">
-        <v>30</v>
-      </c>
-      <c r="C91" t="str">
-        <v>6</v>
-      </c>
-      <c r="D91" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F91" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G91" t="str">
-        <v>6</v>
-      </c>
-      <c r="H91" t="str">
-        <v>6</v>
-      </c>
-      <c r="I91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B92" t="str">
-        <v>30</v>
-      </c>
-      <c r="C92" t="str">
-        <v>6</v>
-      </c>
-      <c r="D92" t="str">
-        <v>2025-09-03</v>
-      </c>
-      <c r="E92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F92" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G92" t="str">
-        <v>6</v>
-      </c>
-      <c r="H92" t="str">
-        <v>6</v>
-      </c>
-      <c r="I92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B93" t="str">
-        <v>30</v>
-      </c>
-      <c r="C93" t="str">
-        <v>6</v>
-      </c>
-      <c r="D93" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="E93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F93" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G93" t="str">
-        <v>6</v>
-      </c>
-      <c r="H93" t="str">
-        <v>6</v>
-      </c>
-      <c r="I93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B94" t="str">
-        <v>30</v>
-      </c>
-      <c r="C94" t="str">
-        <v>6</v>
-      </c>
-      <c r="D94" t="str">
-        <v>2025-09-05</v>
-      </c>
-      <c r="E94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F94" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G94" t="str">
-        <v>6</v>
-      </c>
-      <c r="H94" t="str">
-        <v>6</v>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="B95" t="str">
-        <v>30</v>
-      </c>
-      <c r="C95" t="str">
-        <v>6</v>
-      </c>
-      <c r="D95" t="str">
-        <v>2025-09-02</v>
-      </c>
-      <c r="E95" t="str">
-        <v>Dependant Leave</v>
-      </c>
-      <c r="F95" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="G95" t="str">
-        <v>5.75</v>
-      </c>
-      <c r="H95" t="str">
-        <v>0</v>
-      </c>
-      <c r="I95" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3201,13 +2854,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B2" t="str">
-        <v>57.33</v>
+        <v>58.6</v>
       </c>
       <c r="C2" t="str">
-        <v>57.33</v>
+        <v>58.6</v>
       </c>
       <c r="D2" t="str">
         <v>2.67</v>
@@ -3216,36 +2869,36 @@
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>64.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>-7.17</v>
+        <v>58.6</v>
       </c>
       <c r="H2" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B3" t="str">
-        <v>74.57</v>
+        <v>75.1</v>
       </c>
       <c r="C3" t="str">
-        <v>80.57</v>
+        <v>75.1</v>
       </c>
       <c r="D3" t="str">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>65.25</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>15.32</v>
+        <v>75.1</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -3253,51 +2906,51 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B4" t="str">
-        <v>65.07</v>
+        <v>65.44</v>
       </c>
       <c r="C4" t="str">
-        <v>65.07</v>
+        <v>65.44</v>
       </c>
       <c r="D4" t="str">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>69.75</v>
+        <v>0</v>
       </c>
       <c r="G4" t="str">
-        <v>-4.68</v>
+        <v>65.44</v>
       </c>
       <c r="H4" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B5" t="str">
-        <v>70.5</v>
+        <v>60.77</v>
       </c>
       <c r="C5" t="str">
-        <v>70.5</v>
+        <v>60.77</v>
       </c>
       <c r="D5" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>66.58</v>
+        <v>0</v>
       </c>
       <c r="G5" t="str">
-        <v>3.92</v>
+        <v>60.77</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -3305,25 +2958,25 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>55.4</v>
+        <v>54.1</v>
       </c>
       <c r="C6" t="str">
-        <v>55.4</v>
+        <v>54.1</v>
       </c>
       <c r="D6" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>51.5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="str">
-        <v>3.9</v>
+        <v>54.1</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -3331,54 +2984,54 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="C7" t="str">
-        <v>30.17</v>
+        <v>42.67</v>
       </c>
       <c r="D7" t="str">
         <v>0</v>
       </c>
       <c r="E7" t="str">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>42.75</v>
+        <v>0</v>
       </c>
       <c r="G7" t="str">
-        <v>-12.58</v>
+        <v>42.67</v>
       </c>
       <c r="H7" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="C8" t="str">
-        <v>32.83</v>
+        <v>40.33</v>
       </c>
       <c r="D8" t="str">
-        <v>2.67</v>
+        <v>6.67</v>
       </c>
       <c r="E8" t="str">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
-        <v>-7.17</v>
+        <v>40.33</v>
       </c>
       <c r="H8" t="str">
-        <v>Shortage</v>
+        <v>Sufficient</v>
       </c>
     </row>
   </sheetData>
@@ -3390,7 +3043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3418,35 +3071,36 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B2" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C2" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D2" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Has appointment and is unable to work 
+Eilidh 22/08/2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B3" t="str">
         <v>Asokhia (NL), Deborah</v>
@@ -3461,10 +3115,10 @@
         <v>4</v>
       </c>
       <c r="F3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
@@ -3472,33 +3126,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B4" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C4" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D4" t="str">
         <v>08:00-21:30</v>
       </c>
       <c r="E4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="F4" t="str">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="G4" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B5" t="str">
         <v>Fayaz GH, Shafiya</v>
@@ -3513,10 +3167,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -3524,103 +3178,103 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B6" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C6" t="str">
         <v>Available</v>
       </c>
       <c r="D6" t="str">
-        <v>08:00-21:30</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="str">
-        <v>6.67</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C7" t="str">
         <v>Available</v>
       </c>
       <c r="D7" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G7" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H7" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B8" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C8" t="str">
         <v>Available</v>
       </c>
       <c r="D8" t="str">
-        <v>09:15-10:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B9" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C9" t="str">
         <v>Available</v>
       </c>
       <c r="D9" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E9" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -3628,16 +3282,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B10" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C10" t="str">
         <v>Available</v>
       </c>
       <c r="D10" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E10" t="str">
         <v>3.2</v>
@@ -3649,83 +3303,82 @@
         <v>3.2</v>
       </c>
       <c r="H10" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B11" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C11" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D11" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E11" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F11" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="G11" t="str">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="str">
-        <v>Created by new vacation process.</v>
-      </c>
-    </row>
-    <row r="12" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B12" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C12" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D12" t="str">
-        <v>10:30-12:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="E12" t="str">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="F12" t="str">
-        <v>2</v>
+        <v>5.33</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
-      </c>
-      <c r="H12" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>5.33</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B13" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C13" t="str">
         <v>Available</v>
       </c>
       <c r="D13" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E13" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F13" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -3733,25 +3386,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-12</v>
       </c>
       <c r="B14" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C14" t="str">
         <v>Available</v>
       </c>
       <c r="D14" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E14" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="str">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -3759,51 +3412,51 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B15" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C15" t="str">
         <v>Available</v>
       </c>
       <c r="D15" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E15" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F15" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G15" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B16" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C16" t="str">
         <v>Available</v>
       </c>
       <c r="D16" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E16" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="str">
-        <v>5.33</v>
+        <v>7.5</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -3811,25 +3464,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2025-09-05</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B17" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C17" t="str">
         <v>Available</v>
       </c>
       <c r="D17" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E17" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F17" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G17" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -3837,10 +3490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B18" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C18" t="str">
         <v>Available</v>
@@ -3849,13 +3502,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E18" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="F18" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="G18" t="str">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -3863,36 +3516,36 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B19" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C19" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D19" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E19" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F19" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H19" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B20" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C20" t="str">
         <v>Available</v>
@@ -3901,13 +3554,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E20" t="str">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -3915,59 +3568,60 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B21" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C21" t="str">
         <v>Available</v>
       </c>
       <c r="D21" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E21" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F21" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B22" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C22" t="str">
-        <v>Holiday</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D22" t="str">
-        <v>09:15-17:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E22" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F22" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="G22" t="str">
         <v>0</v>
       </c>
-      <c r="H22" t="str">
-        <v>Created by new vacation process.</v>
+      <c r="H22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Family event
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B23" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
@@ -3982,10 +3636,10 @@
         <v>4</v>
       </c>
       <c r="F23" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -3993,25 +3647,25 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B24" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C24" t="str">
         <v>Available</v>
       </c>
       <c r="D24" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E24" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="F24" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -4019,51 +3673,51 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2025-09-06</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B25" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C25" t="str">
         <v>Available</v>
       </c>
       <c r="D25" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E25" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F25" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G25" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B26" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C26" t="str">
         <v>Available</v>
       </c>
       <c r="D26" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="E26" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="F26" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>5.33</v>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -4071,25 +3725,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B27" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C27" t="str">
         <v>Available</v>
       </c>
       <c r="D27" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E27" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="F27" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="G27" t="str">
-        <v>6</v>
+        <v>2.67</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -4097,129 +3751,130 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-11</v>
       </c>
       <c r="B28" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C28" t="str">
-        <v>Holiday</v>
+        <v>Available</v>
       </c>
       <c r="D28" t="str">
-        <v>09:15-17:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E28" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="F28" t="str">
-        <v>3.43</v>
+        <v>6</v>
       </c>
       <c r="G28" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H28" t="str">
-        <v>Created by new vacation process.</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B29" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C29" t="str">
         <v>Available</v>
       </c>
       <c r="D29" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E29" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F29" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="G29" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="str">
         <v/>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B30" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C30" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="D30" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E30" t="str">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="F30" t="str">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="G30" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H30" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
+Eilidh 01/09/2025</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B31" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C31" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D31" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E31" t="str">
-        <v>2.67</v>
+        <v>6.67</v>
       </c>
       <c r="F31" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="G31" t="str">
         <v>0</v>
       </c>
       <c r="H31" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B32" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C32" t="str">
         <v>Available</v>
       </c>
       <c r="D32" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E32" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H32" t="str">
         <v/>
@@ -4227,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2025-09-07</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B33" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C33" t="str">
         <v>Available</v>
@@ -4239,39 +3894,39 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E33" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F33" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G33" t="str">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="H33" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B34" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C34" t="str">
         <v>Available</v>
       </c>
       <c r="D34" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E34" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F34" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -4279,36 +3934,36 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B35" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="C35" t="str">
         <v>Available</v>
       </c>
       <c r="D35" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E35" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="F35" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="G35" t="str">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="H35" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-14</v>
       </c>
       <c r="B36" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C36" t="str">
         <v>Available</v>
@@ -4317,39 +3972,39 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E36" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F36" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="G36" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B37" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C37" t="str">
         <v>Available</v>
       </c>
       <c r="D37" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E37" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F37" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="G37" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -4357,51 +4012,51 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C38" t="str">
         <v>Available</v>
       </c>
       <c r="D38" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B39" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C39" t="str">
         <v>Available</v>
       </c>
       <c r="D39" t="str">
-        <v>08:00-15:00</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="F39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="G39" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -4409,7 +4064,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B40" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
@@ -4418,7 +4073,7 @@
         <v>Available</v>
       </c>
       <c r="D40" t="str">
-        <v>09:15-15:15</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="E40" t="str">
         <v>3.2</v>
@@ -4430,30 +4085,30 @@
         <v>3.2</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B41" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C41" t="str">
         <v>Available</v>
       </c>
       <c r="D41" t="str">
-        <v>09:15-11:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G41" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -4461,10 +4116,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B42" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C42" t="str">
         <v>Available</v>
@@ -4487,103 +4142,103 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B43" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C43" t="str">
         <v>Available</v>
       </c>
       <c r="D43" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F43" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G43" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B44" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C44" t="str">
         <v>Available</v>
       </c>
       <c r="D44" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E44" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F44" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G44" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H44" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B45" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C45" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D45" t="str">
-        <v>10:30-12:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E45" t="str">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="F45" t="str">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="G45" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H45" t="str">
-        <v>Sharon has advised she is unable to work between 10.30 and 12.30 on Tuesday's - MT</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B46" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C46" t="str">
         <v>Available</v>
       </c>
       <c r="D46" t="str">
-        <v>09:15-16:15</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E46" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F46" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="G46" t="str">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -4591,114 +4246,114 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B47" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C47" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D47" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E47" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F47" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G47" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B48" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C48" t="str">
         <v>Available</v>
       </c>
       <c r="D48" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E48" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="F48" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G48" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-08</v>
       </c>
       <c r="B49" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C49" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D49" t="str">
         <v>09:15-14:00</v>
       </c>
       <c r="E49" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F49" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="G49" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H49" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B50" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C50" t="str">
         <v>Available</v>
       </c>
       <c r="D50" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E50" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F50" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="G50" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H50" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B51" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C51" t="str">
         <v>Available</v>
@@ -4707,65 +4362,65 @@
         <v>09:15-14:00</v>
       </c>
       <c r="E51" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F51" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G51" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2025-09-02</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B52" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C52" t="str">
-        <v>Dependant Leave</v>
+        <v>Available</v>
       </c>
       <c r="D52" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E52" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F52" t="str">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="G52" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H52" t="str">
-        <v>Lori's little boy has an abscess and isn't able to go to school - MT</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B53" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="C53" t="str">
         <v>Available</v>
       </c>
       <c r="D53" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="E53" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F53" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G53" t="str">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -4773,51 +4428,51 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B54" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C54" t="str">
         <v>Available</v>
       </c>
       <c r="D54" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E54" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F54" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G54" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H54" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B55" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C55" t="str">
         <v>Available</v>
       </c>
       <c r="D55" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E55" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="F55" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="G55" t="str">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -4825,25 +4480,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B56" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C56" t="str">
         <v>Available</v>
       </c>
       <c r="D56" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -4851,25 +4506,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B57" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C57" t="str">
         <v>Available</v>
       </c>
       <c r="D57" t="str">
-        <v>09:15-14:45</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E57" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="F57" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G57" t="str">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -4877,51 +4532,51 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B58" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C58" t="str">
         <v>Available</v>
       </c>
       <c r="D58" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G58" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B59" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C59" t="str">
         <v>Available</v>
       </c>
       <c r="D59" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E59" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F59" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G59" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -4929,16 +4584,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C60" t="str">
         <v>Available</v>
       </c>
       <c r="D60" t="str">
-        <v>09:15-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E60" t="str">
         <v>3.2</v>
@@ -4950,109 +4605,108 @@
         <v>3.2</v>
       </c>
       <c r="H60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B61" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C61" t="str">
-        <v>Other Unavailable</v>
+        <v>Available</v>
       </c>
       <c r="D61" t="str">
-        <v>10:30-12:30</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="E61" t="str">
-        <v>3.43</v>
+        <v>4</v>
       </c>
       <c r="F61" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" t="str">
-        <v>0</v>
-      </c>
-      <c r="H61" t="str" xml:space="preserve">
-        <v xml:space="preserve">Wants this as a break. 
-Eilidh 29/05/2025</v>
+        <v>4</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B62" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C62" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="D62" t="str">
-        <v>09:15-16:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E62" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F62" t="str">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="G62" t="str">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B63" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C63" t="str">
         <v>Available</v>
       </c>
       <c r="D63" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E63" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F63" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="G63" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-09</v>
       </c>
       <c r="B64" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C64" t="str">
         <v>Available</v>
       </c>
       <c r="D64" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E64" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F64" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G64" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -5060,77 +4714,77 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B65" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="C65" t="str">
         <v>Available</v>
       </c>
       <c r="D65" t="str">
-        <v>16:45-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E65" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F65" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G65" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B66" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="C66" t="str">
         <v>Available</v>
       </c>
       <c r="D66" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E66" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="F66" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="G66" t="str">
-        <v>2.67</v>
+        <v>7.5</v>
       </c>
       <c r="H66" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2025-09-03</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B67" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C67" t="str">
         <v>Available</v>
       </c>
       <c r="D67" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E67" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F67" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G67" t="str">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -5138,51 +4792,51 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B68" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Ferris, Marykate</v>
       </c>
       <c r="C68" t="str">
         <v>Available</v>
       </c>
       <c r="D68" t="str">
-        <v>09:15-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E68" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="F68" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="G68" t="str">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="H68" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B69" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="C69" t="str">
         <v>Available</v>
       </c>
       <c r="D69" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="E69" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="F69" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G69" t="str">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -5190,25 +4844,25 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B70" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="C70" t="str">
         <v>Available</v>
       </c>
       <c r="D70" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E70" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F70" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G70" t="str">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -5216,77 +4870,77 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B71" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C71" t="str">
         <v>Available</v>
       </c>
       <c r="D71" t="str">
-        <v>10:30-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="F71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G71" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B72" t="str">
-        <v>Gabillard (NL), Donna</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="C72" t="str">
         <v>Available</v>
       </c>
       <c r="D72" t="str">
-        <v>09:15-14:45</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E72" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="F72" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G72" t="str">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B73" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="C73" t="str">
         <v>Available</v>
       </c>
       <c r="D73" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="E73" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F73" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G73" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -5294,25 +4948,25 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B74" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="C74" t="str">
         <v>Available</v>
       </c>
       <c r="D74" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="E74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="F74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="G74" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -5320,77 +4974,77 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B75" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="C75" t="str">
         <v>Available</v>
       </c>
       <c r="D75" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="E75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="F75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="G75" t="str">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B76" t="str">
-        <v>Jack (NL), Sharon</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C76" t="str">
         <v>Available</v>
       </c>
       <c r="D76" t="str">
-        <v>09:15-10:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="E76" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="F76" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="G76" t="str">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-10</v>
       </c>
       <c r="B77" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Wylie (NL), Lori</v>
       </c>
       <c r="C77" t="str">
         <v>Available</v>
       </c>
       <c r="D77" t="str">
-        <v>08:00-15:15</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="E77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -5398,103 +5052,103 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B78" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="C78" t="str">
         <v>Available</v>
       </c>
       <c r="D78" t="str">
-        <v>09:15-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="F78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="G78" t="str">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="H78" t="str">
-        <v>Cheryl has agreed to extend her availability via email 02/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B79" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="C79" t="str">
-        <v>Pre-Agreed Appointment</v>
+        <v>Available</v>
       </c>
       <c r="D79" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E79" t="str">
-        <v>2.67</v>
+        <v>9</v>
       </c>
       <c r="F79" t="str">
-        <v>2.67</v>
+        <v>9</v>
       </c>
       <c r="G79" t="str">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H79" t="str">
-        <v>Brooke has a colonoscopy appointment - MT</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B80" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="C80" t="str">
         <v>Available</v>
       </c>
       <c r="D80" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E80" t="str">
-        <v>2.67</v>
+        <v>6</v>
       </c>
       <c r="F80" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G80" t="str">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2025-09-01</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B81" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="C81" t="str">
         <v>Available</v>
       </c>
       <c r="D81" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E81" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -5502,10 +5156,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B82" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="C82" t="str">
         <v>Available</v>
@@ -5514,13 +5168,13 @@
         <v>08:00-21:30</v>
       </c>
       <c r="E82" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="F82" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="G82" t="str">
-        <v>7.5</v>
+        <v>2.67</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -5528,345 +5182,33 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2025-09-04</v>
+        <v>2025-09-13</v>
       </c>
       <c r="B83" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="C83" t="str">
         <v>Available</v>
       </c>
       <c r="D83" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="E83" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F83" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G83" t="str">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H83" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B84" t="str">
-        <v>Fayaz GH, Shafiya</v>
-      </c>
-      <c r="C84" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D84" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E84" t="str">
-        <v>9</v>
-      </c>
-      <c r="F84" t="str">
-        <v>9</v>
-      </c>
-      <c r="G84" t="str">
-        <v>9</v>
-      </c>
-      <c r="H84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B85" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D85" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E85" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="F85" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="G85" t="str">
-        <v>6.67</v>
-      </c>
-      <c r="H85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B86" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D86" t="str">
-        <v>09:15-15:15</v>
-      </c>
-      <c r="E86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G86" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B87" t="str">
-        <v>Gabillard (NL), Donna</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D87" t="str">
-        <v>09:15-11:30</v>
-      </c>
-      <c r="E87" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="F87" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="G87" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="H87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B88" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D88" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E88" t="str">
-        <v>6</v>
-      </c>
-      <c r="F88" t="str">
-        <v>6</v>
-      </c>
-      <c r="G88" t="str">
-        <v>6</v>
-      </c>
-      <c r="H88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B89" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D89" t="str">
-        <v>09:15-15:00</v>
-      </c>
-      <c r="E89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G89" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H89" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B90" t="str">
-        <v>Jack (NL), Sharon</v>
-      </c>
-      <c r="C90" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D90" t="str">
-        <v>09:15-16:15</v>
-      </c>
-      <c r="E90" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="F90" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="G90" t="str">
-        <v>3.43</v>
-      </c>
-      <c r="H90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B91" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
-      </c>
-      <c r="C91" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D91" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E91" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F91" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G91" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B92" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D92" t="str">
-        <v>16:45-21:30</v>
-      </c>
-      <c r="E92" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F92" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G92" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B93" t="str">
-        <v>Nelson (NL), Anne</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D93" t="str">
-        <v>08:00-17:15</v>
-      </c>
-      <c r="E93" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="F93" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="G93" t="str">
-        <v>5.33</v>
-      </c>
-      <c r="H93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B94" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D94" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E94" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="F94" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="G94" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>2025-09-04</v>
-      </c>
-      <c r="B95" t="str">
-        <v>Wylie (NL), Lori</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D95" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="E95" t="str">
-        <v>6</v>
-      </c>
-      <c r="F95" t="str">
-        <v>6</v>
-      </c>
-      <c r="G95" t="str">
-        <v>6</v>
-      </c>
-      <c r="H95" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H83"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/capacity_dashboard.xlsx
+++ b/capacity_dashboard.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,308 +434,308 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B2" t="str">
+        <v>16</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="F2" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H2" t="str">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B3" t="str">
+        <v>16</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="F3" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="B4" t="str">
+        <v>16</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="F4" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="H4" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
         <v>Asokhia (NL), Deborah</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B5" t="str">
         <v>20</v>
       </c>
-      <c r="C2" t="str">
-        <v>4</v>
-      </c>
-      <c r="D2" t="str">
+      <c r="C5" t="str">
+        <v>4</v>
+      </c>
+      <c r="D5" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E5" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F2" t="str">
+      <c r="F5" t="str">
         <v>08:00-15:00</v>
       </c>
-      <c r="G2" t="str">
-        <v>4</v>
-      </c>
-      <c r="H2" t="str">
-        <v>0</v>
-      </c>
-      <c r="I2" t="str" xml:space="preserve">
+      <c r="G5" t="str">
+        <v>4</v>
+      </c>
+      <c r="H5" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str" xml:space="preserve">
         <v xml:space="preserve">Has appointment and is unable to work 
 Eilidh 22/08/2025</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B6" t="str">
         <v>16</v>
       </c>
-      <c r="C3" t="str">
-        <v>4</v>
-      </c>
-      <c r="D3" t="str">
+      <c r="C6" t="str">
+        <v>4</v>
+      </c>
+      <c r="D6" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E6" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F6" t="str">
         <v>08:00-15:00</v>
       </c>
-      <c r="G3" t="str">
-        <v>4</v>
-      </c>
-      <c r="H3" t="str">
-        <v>0</v>
-      </c>
-      <c r="I3" t="str" xml:space="preserve">
+      <c r="G6" t="str">
+        <v>4</v>
+      </c>
+      <c r="H6" t="str">
+        <v>0</v>
+      </c>
+      <c r="I6" t="str" xml:space="preserve">
         <v xml:space="preserve">Family event
 Eilidh 01/09/2025</v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="B4" t="str">
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>Ferris (NL), Marykate</v>
+      </c>
+      <c r="B7" t="str">
         <v>20</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C7" t="str">
         <v>6.67</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D7" t="str">
         <v>2025-09-14</v>
       </c>
-      <c r="E4" t="str">
+      <c r="E7" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="F4" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="F7" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="G7" t="str">
         <v>6.67</v>
       </c>
-      <c r="H4" t="str">
-        <v>0</v>
-      </c>
-      <c r="I4" t="str" xml:space="preserve">
+      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str" xml:space="preserve">
         <v xml:space="preserve">Away for a family members birthday, tickets were already bought before checking
 Eilidh 01/09/2025</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="B5" t="str">
-        <v>16</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2025-09-08</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Pre-Agreed Appointment</v>
-      </c>
-      <c r="F5" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H5" t="str">
-        <v>0</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
-      </c>
-      <c r="B6" t="str">
-        <v>16</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2025-09-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Pre-Agreed Appointment</v>
-      </c>
-      <c r="F6" t="str">
-        <v>09:15-14:00</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2.67</v>
-      </c>
-      <c r="H6" t="str">
-        <v>0</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
-      </c>
-      <c r="B7" t="str">
-        <v>16</v>
-      </c>
-      <c r="C7" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2025-09-08</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Available</v>
-      </c>
-      <c r="F7" t="str">
-        <v>10:30-14:00</v>
-      </c>
-      <c r="G7" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H7" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Confirmed at induction with MT</v>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B8" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C8" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E8" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F8" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G8" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H8" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>Wayne called to advise that his car had broke down and that he would not be returning until his car situation was sorted. SM</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B9" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C9" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E9" t="str">
-        <v>Available</v>
+        <v>Other Unavailable</v>
       </c>
       <c r="F9" t="str">
-        <v>09:15-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G9" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H9" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>Wayne called to advise that his car had broke down and that he would not be returning until his car situation was sorted. SM</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B10" t="str">
         <v>16</v>
       </c>
       <c r="C10" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E10" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F10" t="str">
-        <v>09:15-15:15</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G10" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Forbes (NL) (GH), Amanda</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B11" t="str">
         <v>16</v>
       </c>
       <c r="C11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E11" t="str">
-        <v>Available</v>
+        <v>Pre-Agreed Appointment</v>
       </c>
       <c r="F11" t="str">
-        <v>10:30-14:00</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G11" t="str">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="str">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>Confirmed at induction with MT</v>
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B12" t="str">
         <v>16</v>
       </c>
       <c r="C12" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D12" t="str">
         <v>2025-09-08</v>
@@ -744,27 +744,27 @@
         <v>Available</v>
       </c>
       <c r="F12" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G12" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B13" t="str">
         <v>16</v>
       </c>
       <c r="C13" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D13" t="str">
         <v>2025-09-09</v>
@@ -773,27 +773,27 @@
         <v>Available</v>
       </c>
       <c r="F13" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="str">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B14" t="str">
         <v>16</v>
       </c>
       <c r="C14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="str">
         <v>2025-09-10</v>
@@ -802,27 +802,27 @@
         <v>Available</v>
       </c>
       <c r="F14" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="str">
-        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B15" t="str">
         <v>16</v>
       </c>
       <c r="C15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D15" t="str">
         <v>2025-09-11</v>
@@ -831,13 +831,13 @@
         <v>Available</v>
       </c>
       <c r="F15" t="str">
-        <v>09:15-14:00</v>
+        <v>09:15-15:15</v>
       </c>
       <c r="G15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -845,13 +845,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>O'Brien (NL) (GH), Brooke</v>
+        <v>Forbes (NL) (GH), Amanda</v>
       </c>
       <c r="B16" t="str">
         <v>16</v>
       </c>
       <c r="C16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="D16" t="str">
         <v>2025-09-12</v>
@@ -860,16 +860,16 @@
         <v>Available</v>
       </c>
       <c r="F16" t="str">
-        <v>09:15-14:00</v>
+        <v>10:30-14:00</v>
       </c>
       <c r="G16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="H16" t="str">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>Confirmed at induction with MT</v>
       </c>
     </row>
     <row r="17">
@@ -883,36 +883,36 @@
         <v>2.67</v>
       </c>
       <c r="D17" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E17" t="str">
         <v>Available</v>
       </c>
       <c r="F17" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G17" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="H17" t="str">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B18" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C18" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D18" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E18" t="str">
         <v>Available</v>
@@ -921,27 +921,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B19" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D19" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E19" t="str">
         <v>Available</v>
@@ -950,27 +950,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B20" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D20" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E20" t="str">
         <v>Available</v>
@@ -979,27 +979,27 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H20" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I20" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B21" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D21" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E21" t="str">
         <v>Available</v>
@@ -1008,201 +1008,201 @@
         <v>09:15-14:00</v>
       </c>
       <c r="G21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="H21" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="I21" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Asokhia (NL), Deborah</v>
+        <v>O'Brien (NL) (GH), Brooke</v>
       </c>
       <c r="B22" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="str">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="D22" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E22" t="str">
         <v>Available</v>
       </c>
       <c r="F22" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="H22" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="str">
-        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B23" t="str">
         <v>20</v>
       </c>
       <c r="C23" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D23" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E23" t="str">
         <v>Available</v>
       </c>
       <c r="F23" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G23" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H23" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I23" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Shawcross (NL), Emma</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B24" t="str">
         <v>20</v>
       </c>
       <c r="C24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D24" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E24" t="str">
         <v>Available</v>
       </c>
       <c r="F24" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H24" t="str">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I24" t="str">
-        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B25" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D25" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E25" t="str">
         <v>Available</v>
       </c>
       <c r="F25" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H25" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B26" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E26" t="str">
         <v>Available</v>
       </c>
       <c r="F26" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="H26" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Asokhia (NL), Deborah</v>
       </c>
       <c r="B27" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C27" t="str">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="D27" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E27" t="str">
         <v>Available</v>
       </c>
       <c r="F27" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-14:00</v>
       </c>
       <c r="G27" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="str">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Barton (NL) (GH), Kaitlyn</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B28" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C28" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D28" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E28" t="str">
         <v>Available</v>
@@ -1211,53 +1211,53 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G28" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H28" t="str">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Shawcross (NL), Emma</v>
       </c>
       <c r="B29" t="str">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C29" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E29" t="str">
         <v>Available</v>
       </c>
       <c r="F29" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G29" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H29" t="str">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Can only do Airdrie and Coatbridge clients on a Sunday - MT</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Duncan (NL), Madison</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B30" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C30" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="D30" t="str">
         <v>2025-09-09</v>
@@ -1266,13 +1266,13 @@
         <v>Available</v>
       </c>
       <c r="F30" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G30" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H30" t="str">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1280,13 +1280,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B31" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C31" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D31" t="str">
         <v>2025-09-10</v>
@@ -1295,13 +1295,13 @@
         <v>Available</v>
       </c>
       <c r="F31" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G31" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H31" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1309,13 +1309,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B32" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C32" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D32" t="str">
         <v>2025-09-11</v>
@@ -1324,13 +1324,13 @@
         <v>Available</v>
       </c>
       <c r="F32" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G32" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H32" t="str">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1338,13 +1338,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
       <c r="B33" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C33" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D33" t="str">
         <v>2025-09-12</v>
@@ -1353,13 +1353,13 @@
         <v>Available</v>
       </c>
       <c r="F33" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G33" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H33" t="str">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1367,28 +1367,28 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Mcewan (NL) (GH), Makala</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B34" t="str">
         <v>16</v>
       </c>
       <c r="C34" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D34" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E34" t="str">
         <v>Available</v>
       </c>
       <c r="F34" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G34" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H34" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1396,28 +1396,28 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Duncan (NL), Madison</v>
       </c>
       <c r="B35" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C35" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="D35" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E35" t="str">
         <v>Available</v>
       </c>
       <c r="F35" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G35" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="H35" t="str">
-        <v>6.67</v>
+        <v>8</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1425,28 +1425,28 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B36" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C36" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D36" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E36" t="str">
         <v>Available</v>
       </c>
       <c r="F36" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G36" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="H36" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1454,22 +1454,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ferris, Marykate</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B37" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C37" t="str">
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="D37" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E37" t="str">
         <v>Available</v>
       </c>
       <c r="F37" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G37" t="str">
         <v>0</v>
@@ -1483,28 +1483,28 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B38" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D38" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E38" t="str">
         <v>Available</v>
       </c>
       <c r="F38" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1512,28 +1512,28 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Mcewan (NL) (GH), Makala</v>
       </c>
       <c r="B39" t="str">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C39" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D39" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E39" t="str">
         <v>Available</v>
       </c>
       <c r="F39" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G39" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H39" t="str">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1541,28 +1541,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris (NL), Marykate</v>
       </c>
       <c r="B40" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C40" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D40" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E40" t="str">
         <v>Available</v>
       </c>
       <c r="F40" t="str">
-        <v>08:00-21:30</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G40" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="H40" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1570,16 +1570,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris (NL), Marykate</v>
       </c>
       <c r="B41" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C41" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D41" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E41" t="str">
         <v>Available</v>
@@ -1588,10 +1588,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G41" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="H41" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1599,16 +1599,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Fayaz GH, Shafiya</v>
+        <v>Ferris (NL), Marykate</v>
       </c>
       <c r="B42" t="str">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C42" t="str">
-        <v>9</v>
+        <v>6.67</v>
       </c>
       <c r="D42" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E42" t="str">
         <v>Available</v>
@@ -1617,10 +1617,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G42" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H42" t="str">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1628,16 +1628,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B43" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C43" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D43" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E43" t="str">
         <v>Available</v>
@@ -1646,10 +1646,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G43" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H43" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1657,28 +1657,28 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B44" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C44" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D44" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E44" t="str">
         <v>Available</v>
       </c>
       <c r="F44" t="str">
-        <v>08:00-15:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G44" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H44" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1686,16 +1686,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B45" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C45" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D45" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E45" t="str">
         <v>Available</v>
@@ -1704,10 +1704,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G45" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H45" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1715,16 +1715,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Lamont (NL) (GH), Sophie</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B46" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C46" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D46" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E46" t="str">
         <v>Available</v>
@@ -1733,10 +1733,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G46" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H46" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -1744,16 +1744,16 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Fayaz GH, Shafiya</v>
       </c>
       <c r="B47" t="str">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C47" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="D47" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E47" t="str">
         <v>Available</v>
@@ -1762,10 +1762,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G47" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="H47" t="str">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B48" t="str">
         <v>30</v>
@@ -1782,7 +1782,7 @@
         <v>7.5</v>
       </c>
       <c r="D48" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E48" t="str">
         <v>Available</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B49" t="str">
         <v>30</v>
@@ -1811,13 +1811,13 @@
         <v>7.5</v>
       </c>
       <c r="D49" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E49" t="str">
         <v>Available</v>
       </c>
       <c r="F49" t="str">
-        <v>08:00-21:30</v>
+        <v>08:00-15:15</v>
       </c>
       <c r="G49" t="str">
         <v>7.5</v>
@@ -1831,7 +1831,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Adeyanju (NL) (GH), Adedayo</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B50" t="str">
         <v>30</v>
@@ -1840,7 +1840,7 @@
         <v>7.5</v>
       </c>
       <c r="D50" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E50" t="str">
         <v>Available</v>
@@ -1860,16 +1860,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Lamont (NL) (GH), Sophie</v>
       </c>
       <c r="B51" t="str">
         <v>30</v>
       </c>
       <c r="C51" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D51" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E51" t="str">
         <v>Available</v>
@@ -1878,10 +1878,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G51" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H51" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -1889,16 +1889,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B52" t="str">
         <v>30</v>
       </c>
       <c r="C52" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D52" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E52" t="str">
         <v>Available</v>
@@ -1907,10 +1907,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G52" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H52" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -1918,16 +1918,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B53" t="str">
         <v>30</v>
       </c>
       <c r="C53" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D53" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E53" t="str">
         <v>Available</v>
@@ -1936,10 +1936,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G53" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H53" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -1947,16 +1947,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B54" t="str">
         <v>30</v>
       </c>
       <c r="C54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D54" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E54" t="str">
         <v>Available</v>
@@ -1965,10 +1965,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H54" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -1976,16 +1976,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Hussain (NL) (GH), Mustansar</v>
+        <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
       <c r="B55" t="str">
         <v>30</v>
       </c>
       <c r="C55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="D55" t="str">
-        <v>2025-09-13</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E55" t="str">
         <v>Available</v>
@@ -1994,10 +1994,10 @@
         <v>08:00-21:30</v>
       </c>
       <c r="G55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H55" t="str">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2005,13 +2005,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B56" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D56" t="str">
         <v>2025-09-08</v>
@@ -2020,27 +2020,27 @@
         <v>Available</v>
       </c>
       <c r="F56" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H56" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I56" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B57" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C57" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D57" t="str">
         <v>2025-09-09</v>
@@ -2049,27 +2049,27 @@
         <v>Available</v>
       </c>
       <c r="F57" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G57" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H57" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I57" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B58" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="str">
         <v>2025-09-10</v>
@@ -2078,85 +2078,85 @@
         <v>Available</v>
       </c>
       <c r="F58" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H58" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I58" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B59" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C59" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D59" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E59" t="str">
         <v>Available</v>
       </c>
       <c r="F59" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G59" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H59" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I59" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ibrahim (NL), Olusegun Isaac</v>
+        <v>Hussain (NL) (GH), Mustansar</v>
       </c>
       <c r="B60" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-13</v>
       </c>
       <c r="E60" t="str">
         <v>Available</v>
       </c>
       <c r="F60" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H60" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I60" t="str">
-        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B61" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C61" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D61" t="str">
         <v>2025-09-08</v>
@@ -2165,27 +2165,27 @@
         <v>Available</v>
       </c>
       <c r="F61" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G61" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H61" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B62" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C62" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D62" t="str">
         <v>2025-09-09</v>
@@ -2194,27 +2194,27 @@
         <v>Available</v>
       </c>
       <c r="F62" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G62" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H62" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B63" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C63" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D63" t="str">
         <v>2025-09-10</v>
@@ -2223,27 +2223,27 @@
         <v>Available</v>
       </c>
       <c r="F63" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G63" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H63" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B64" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D64" t="str">
         <v>2025-09-11</v>
@@ -2252,71 +2252,71 @@
         <v>Available</v>
       </c>
       <c r="F64" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H64" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Griffiths (NL), Wayne (GH)</v>
+        <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
       <c r="B65" t="str">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C65" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="D65" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E65" t="str">
         <v>Available</v>
       </c>
       <c r="F65" t="str">
-        <v>08:00-21:30</v>
+        <v>09:15-15:00</v>
       </c>
       <c r="G65" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="H65" t="str">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B66" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C66" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D66" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-08</v>
       </c>
       <c r="E66" t="str">
         <v>Available</v>
       </c>
       <c r="F66" t="str">
-        <v>08:00-17:15</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G66" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H66" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2324,28 +2324,28 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B67" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C67" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D67" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-09</v>
       </c>
       <c r="E67" t="str">
         <v>Available</v>
       </c>
       <c r="F67" t="str">
-        <v>08:00-13:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G67" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="H67" t="str">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2353,28 +2353,28 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nelson (NL), Anne</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B68" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="D68" t="str">
-        <v>2025-09-14</v>
+        <v>2025-09-10</v>
       </c>
       <c r="E68" t="str">
         <v>Available</v>
       </c>
       <c r="F68" t="str">
-        <v>08:00-18:00</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="H68" t="str">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2382,28 +2382,28 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B69" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D69" t="str">
-        <v>2025-09-08</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E69" t="str">
         <v>Available</v>
       </c>
       <c r="F69" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H69" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2411,28 +2411,28 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Griffiths (NL), Wayne (GH)</v>
       </c>
       <c r="B70" t="str">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D70" t="str">
-        <v>2025-09-09</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E70" t="str">
         <v>Available</v>
       </c>
       <c r="F70" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-21:30</v>
       </c>
       <c r="G70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="H70" t="str">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2440,28 +2440,28 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B71" t="str">
         <v>16</v>
       </c>
       <c r="C71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="D71" t="str">
-        <v>2025-09-10</v>
+        <v>2025-09-11</v>
       </c>
       <c r="E71" t="str">
         <v>Available</v>
       </c>
       <c r="F71" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-17:15</v>
       </c>
       <c r="G71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H71" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2469,28 +2469,28 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B72" t="str">
         <v>16</v>
       </c>
       <c r="C72" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="D72" t="str">
-        <v>2025-09-11</v>
+        <v>2025-09-12</v>
       </c>
       <c r="E72" t="str">
         <v>Available</v>
       </c>
       <c r="F72" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-13:00</v>
       </c>
       <c r="G72" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H72" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2498,28 +2498,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>McGhie (NL) (GH), Cheryl</v>
+        <v>Nelson (NL), Anne</v>
       </c>
       <c r="B73" t="str">
         <v>16</v>
       </c>
       <c r="C73" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="D73" t="str">
-        <v>2025-09-12</v>
+        <v>2025-09-14</v>
       </c>
       <c r="E73" t="str">
         <v>Available</v>
       </c>
       <c r="F73" t="str">
-        <v>16:45-21:30</v>
+        <v>08:00-18:00</v>
       </c>
       <c r="G73" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="H73" t="str">
-        <v>3.2</v>
+        <v>5.33</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2527,13 +2527,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B74" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D74" t="str">
         <v>2025-09-08</v>
@@ -2542,13 +2542,13 @@
         <v>Available</v>
       </c>
       <c r="F74" t="str">
-        <v>08:00-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -2556,13 +2556,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B75" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D75" t="str">
         <v>2025-09-09</v>
@@ -2571,13 +2571,13 @@
         <v>Available</v>
       </c>
       <c r="F75" t="str">
-        <v>08:00-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -2585,13 +2585,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B76" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C76" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D76" t="str">
         <v>2025-09-10</v>
@@ -2600,13 +2600,13 @@
         <v>Available</v>
       </c>
       <c r="F76" t="str">
-        <v>08:00-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G76" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H76" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -2614,13 +2614,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B77" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C77" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D77" t="str">
         <v>2025-09-11</v>
@@ -2629,13 +2629,13 @@
         <v>Available</v>
       </c>
       <c r="F77" t="str">
-        <v>08:00-15:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G77" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2643,13 +2643,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Mooney (NL), Lynsey (GH)</v>
+        <v>McGhie (NL) (GH), Cheryl</v>
       </c>
       <c r="B78" t="str">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D78" t="str">
         <v>2025-09-12</v>
@@ -2658,13 +2658,13 @@
         <v>Available</v>
       </c>
       <c r="F78" t="str">
-        <v>08:00-14:00</v>
+        <v>16:45-21:30</v>
       </c>
       <c r="G78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="H78" t="str">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -2672,13 +2672,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B79" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C79" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D79" t="str">
         <v>2025-09-08</v>
@@ -2687,13 +2687,13 @@
         <v>Available</v>
       </c>
       <c r="F79" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G79" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H79" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -2701,13 +2701,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B80" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D80" t="str">
         <v>2025-09-09</v>
@@ -2716,13 +2716,13 @@
         <v>Available</v>
       </c>
       <c r="F80" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H80" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -2730,13 +2730,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B81" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C81" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D81" t="str">
         <v>2025-09-10</v>
@@ -2745,13 +2745,13 @@
         <v>Available</v>
       </c>
       <c r="F81" t="str">
-        <v>09:15-15:00</v>
+        <v>08:00-14:00</v>
       </c>
       <c r="G81" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H81" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -2759,13 +2759,13 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B82" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C82" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D82" t="str">
         <v>2025-09-11</v>
@@ -2774,13 +2774,13 @@
         <v>Available</v>
       </c>
       <c r="F82" t="str">
-        <v>09:15-14:00</v>
+        <v>08:00-15:00</v>
       </c>
       <c r="G82" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H82" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -2788,13 +2788,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Wylie (NL), Lori</v>
+        <v>Mooney (NL), Lynsey (GH)</v>
       </c>
       <c r="B83" t="str">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C83" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D83" t="str">
         <v>2025-09-12</v>
@@ -2803,21 +2803,166 @@
         <v>Available</v>
       </c>
       <c r="F83" t="str">
+        <v>08:00-14:00</v>
+      </c>
+      <c r="G83" t="str">
+        <v>4</v>
+      </c>
+      <c r="H83" t="str">
+        <v>4</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B84" t="str">
+        <v>30</v>
+      </c>
+      <c r="C84" t="str">
+        <v>6</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F84" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="G83" t="str">
-        <v>6</v>
-      </c>
-      <c r="H83" t="str">
-        <v>6</v>
-      </c>
-      <c r="I83" t="str">
+      <c r="G84" t="str">
+        <v>6</v>
+      </c>
+      <c r="H84" t="str">
+        <v>6</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B85" t="str">
+        <v>30</v>
+      </c>
+      <c r="C85" t="str">
+        <v>6</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F85" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G85" t="str">
+        <v>6</v>
+      </c>
+      <c r="H85" t="str">
+        <v>6</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B86" t="str">
+        <v>30</v>
+      </c>
+      <c r="C86" t="str">
+        <v>6</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F86" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="G86" t="str">
+        <v>6</v>
+      </c>
+      <c r="H86" t="str">
+        <v>6</v>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B87" t="str">
+        <v>30</v>
+      </c>
+      <c r="C87" t="str">
+        <v>6</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2025-09-11</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F87" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G87" t="str">
+        <v>6</v>
+      </c>
+      <c r="H87" t="str">
+        <v>6</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="B88" t="str">
+        <v>30</v>
+      </c>
+      <c r="C88" t="str">
+        <v>6</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2025-09-12</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Available</v>
+      </c>
+      <c r="F88" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="G88" t="str">
+        <v>6</v>
+      </c>
+      <c r="H88" t="str">
+        <v>6</v>
+      </c>
+      <c r="I88" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I83"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I88"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2857,25 +3002,25 @@
         <v>2025-09-08</v>
       </c>
       <c r="B2" t="str">
-        <v>58.6</v>
+        <v>52.6</v>
       </c>
       <c r="C2" t="str">
-        <v>58.6</v>
+        <v>52.6</v>
       </c>
       <c r="D2" t="str">
-        <v>2.67</v>
+        <v>11.34</v>
       </c>
       <c r="E2" t="str">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>0</v>
+        <v>58.75</v>
       </c>
       <c r="G2" t="str">
-        <v>58.6</v>
+        <v>-6.15</v>
       </c>
       <c r="H2" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="3">
@@ -2883,22 +3028,22 @@
         <v>2025-09-09</v>
       </c>
       <c r="B3" t="str">
-        <v>75.1</v>
+        <v>69.1</v>
       </c>
       <c r="C3" t="str">
-        <v>75.1</v>
+        <v>69.1</v>
       </c>
       <c r="D3" t="str">
-        <v>2.67</v>
+        <v>11.34</v>
       </c>
       <c r="E3" t="str">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>59.75</v>
       </c>
       <c r="G3" t="str">
-        <v>75.1</v>
+        <v>9.35</v>
       </c>
       <c r="H3" t="str">
         <v>Sufficient</v>
@@ -2909,25 +3054,25 @@
         <v>2025-09-10</v>
       </c>
       <c r="B4" t="str">
-        <v>65.44</v>
+        <v>62.77</v>
       </c>
       <c r="C4" t="str">
-        <v>65.44</v>
+        <v>62.77</v>
       </c>
       <c r="D4" t="str">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="E4" t="str">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>0</v>
+        <v>69.75</v>
       </c>
       <c r="G4" t="str">
-        <v>65.44</v>
+        <v>-6.98</v>
       </c>
       <c r="H4" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="5">
@@ -2947,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>57.75</v>
       </c>
       <c r="G5" t="str">
-        <v>60.77</v>
+        <v>3.02</v>
       </c>
       <c r="H5" t="str">
         <v>Sufficient</v>
@@ -2973,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>0</v>
+        <v>53.75</v>
       </c>
       <c r="G6" t="str">
-        <v>54.1</v>
+        <v>0.35</v>
       </c>
       <c r="H6" t="str">
         <v>Sufficient</v>
@@ -2999,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>46.75</v>
       </c>
       <c r="G7" t="str">
-        <v>42.67</v>
+        <v>-4.08</v>
       </c>
       <c r="H7" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
     <row r="8">
@@ -3025,13 +3170,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G8" t="str">
-        <v>40.33</v>
+        <v>-2.67</v>
       </c>
       <c r="H8" t="str">
-        <v>Sufficient</v>
+        <v>Shortage</v>
       </c>
     </row>
   </sheetData>
@@ -3043,7 +3188,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3071,1980 +3216,1980 @@
         <v>Notes</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D2" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G2" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D3" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E3" t="str">
+        <v>4</v>
+      </c>
+      <c r="F3" t="str">
+        <v>4</v>
+      </c>
+      <c r="G3" t="str">
+        <v>4</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D4" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="E4" t="str">
+        <v>8</v>
+      </c>
+      <c r="F4" t="str">
+        <v>8</v>
+      </c>
+      <c r="G4" t="str">
+        <v>8</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D5" t="str">
+        <v>10:30-14:00</v>
+      </c>
+      <c r="E5" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Confirmed at induction with MT</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D6" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E6" t="str">
+        <v>6</v>
+      </c>
+      <c r="F6" t="str">
+        <v>6</v>
+      </c>
+      <c r="G6" t="str">
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Wayne called to advise that his car had broke down and that he would not be returning until his car situation was sorted. SM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D7" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E7" t="str">
+        <v>6</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D8" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E8" t="str">
+        <v>6</v>
+      </c>
+      <c r="F8" t="str">
+        <v>6</v>
+      </c>
+      <c r="G8" t="str">
+        <v>6</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D9" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E9" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G9" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D10" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G10" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B11" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D11" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E11" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F11" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G11" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D12" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="E12" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>4</v>
+      </c>
+      <c r="G12" t="str">
+        <v>4</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B13" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="D13" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B14" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Pre-Agreed Appointment</v>
+      </c>
+      <c r="D14" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G14" t="str">
+        <v>0</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B15" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D15" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2025-09-08</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D16" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E16" t="str">
+        <v>6</v>
+      </c>
+      <c r="F16" t="str">
+        <v>6</v>
+      </c>
+      <c r="G16" t="str">
+        <v>6</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Adeyanju (NL) (GH), Adedayo</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D17" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E17" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F17" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G17" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D18" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E18" t="str">
+        <v>4</v>
+      </c>
+      <c r="F18" t="str">
+        <v>4</v>
+      </c>
+      <c r="G18" t="str">
+        <v>4</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D19" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E19" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F19" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Duncan (NL), Madison</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D20" t="str">
+        <v>08:00-18:00</v>
+      </c>
+      <c r="E20" t="str">
+        <v>8</v>
+      </c>
+      <c r="F20" t="str">
+        <v>8</v>
+      </c>
+      <c r="G20" t="str">
+        <v>8</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D21" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E21" t="str">
+        <v>9</v>
+      </c>
+      <c r="F21" t="str">
+        <v>9</v>
+      </c>
+      <c r="G21" t="str">
+        <v>9</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D22" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Other Unavailable</v>
+      </c>
+      <c r="D23" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E23" t="str">
+        <v>6</v>
+      </c>
+      <c r="F23" t="str">
+        <v>6</v>
+      </c>
+      <c r="G23" t="str">
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Wayne called to advise that his car had broke down and that he would not be returning until his car situation was sorted. SM</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D24" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E24" t="str">
+        <v>6</v>
+      </c>
+      <c r="F24" t="str">
+        <v>0</v>
+      </c>
+      <c r="G24" t="str">
+        <v>0</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D25" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E25" t="str">
+        <v>6</v>
+      </c>
+      <c r="F25" t="str">
+        <v>6</v>
+      </c>
+      <c r="G25" t="str">
+        <v>6</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D26" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E26" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F26" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G26" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Lamont (NL) (GH), Sophie</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D27" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G27" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B28" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D28" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E28" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F28" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G28" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D29" t="str">
+        <v>08:00-15:00</v>
+      </c>
+      <c r="E29" t="str">
+        <v>4</v>
+      </c>
+      <c r="F29" t="str">
+        <v>4</v>
+      </c>
+      <c r="G29" t="str">
+        <v>4</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B30" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="D30" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F30" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G30" t="str">
+        <v>0</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B31" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Pre-Agreed Appointment</v>
+      </c>
+      <c r="D31" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G31" t="str">
+        <v>0</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Brooke advised that her previous appointment was cancelled and that it has been rescheduled. SM</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B32" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D32" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F32" t="str">
+        <v>0</v>
+      </c>
+      <c r="G32" t="str">
+        <v>0</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2025-09-09</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D33" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E33" t="str">
+        <v>6</v>
+      </c>
+      <c r="F33" t="str">
+        <v>6</v>
+      </c>
+      <c r="G33" t="str">
+        <v>6</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Asokhia (NL), Deborah</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D34" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E34" t="str">
+        <v>4</v>
+      </c>
+      <c r="F34" t="str">
+        <v>4</v>
+      </c>
+      <c r="G34" t="str">
+        <v>4</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Agreed at induction with MT and SM - 09/05/2025</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Barton (NL) (GH), Kaitlyn</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D35" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E35" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F35" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G35" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Fayaz GH, Shafiya</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D36" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E36" t="str">
+        <v>9</v>
+      </c>
+      <c r="F36" t="str">
+        <v>9</v>
+      </c>
+      <c r="G36" t="str">
+        <v>9</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Ferris (NL), Marykate</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D37" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E37" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="F37" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="G37" t="str">
+        <v>6.67</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Forbes (NL) (GH), Amanda</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D38" t="str">
+        <v>09:15-15:15</v>
+      </c>
+      <c r="E38" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F38" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G38" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Griffiths (NL), Wayne (GH)</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D39" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E39" t="str">
+        <v>6</v>
+      </c>
+      <c r="F39" t="str">
+        <v>6</v>
+      </c>
+      <c r="G39" t="str">
+        <v>6</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Hussain (NL) (GH), Mustansar</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D40" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E40" t="str">
+        <v>6</v>
+      </c>
+      <c r="F40" t="str">
+        <v>6</v>
+      </c>
+      <c r="G40" t="str">
+        <v>6</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Ibrahim (NL), Olusegun Isaac</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D41" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E41" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F41" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G41" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Agreed at induction with SM 25/04/2025 - MT</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Mcewan (NL) (GH), Makala</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D42" t="str">
+        <v>08:00-15:15</v>
+      </c>
+      <c r="E42" t="str">
+        <v>4</v>
+      </c>
+      <c r="F42" t="str">
+        <v>4</v>
+      </c>
+      <c r="G42" t="str">
+        <v>4</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B43" t="str">
+        <v>McGhie (NL) (GH), Cheryl</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D43" t="str">
+        <v>16:45-21:30</v>
+      </c>
+      <c r="E43" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F43" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G43" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Mooney (NL), Lynsey (GH)</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D44" t="str">
+        <v>08:00-14:00</v>
+      </c>
+      <c r="E44" t="str">
+        <v>4</v>
+      </c>
+      <c r="F44" t="str">
+        <v>4</v>
+      </c>
+      <c r="G44" t="str">
+        <v>4</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B45" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Sick</v>
+      </c>
+      <c r="D45" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F45" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="G45" t="str">
+        <v>0</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Brooke called to advise that she has been given a sick line due to multiple health problems at the moment. SM</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B46" t="str">
+        <v>O'Brien (NL) (GH), Brooke</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D46" t="str">
+        <v>09:15-14:00</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2.67</v>
+      </c>
+      <c r="F46" t="str">
+        <v>0</v>
+      </c>
+      <c r="G46" t="str">
+        <v>0</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Increased availability to 09.15am starts on Monday, Tuesday and Wednesday as of Monday 28/04 - MT</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Wylie (NL), Lori</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D47" t="str">
+        <v>09:15-15:00</v>
+      </c>
+      <c r="E47" t="str">
+        <v>6</v>
+      </c>
+      <c r="F47" t="str">
+        <v>6</v>
+      </c>
+      <c r="G47" t="str">
+        <v>6</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B48" t="str">
         <v>Asokhia (NL), Deborah</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C48" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D48" t="str">
         <v>08:00-15:00</v>
       </c>
-      <c r="E2" t="str">
-        <v>4</v>
-      </c>
-      <c r="F2" t="str">
-        <v>4</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str" xml:space="preserve">
+      <c r="E48" t="str">
+        <v>4</v>
+      </c>
+      <c r="F48" t="str">
+        <v>4</v>
+      </c>
+      <c r="G48" t="str">
+        <v>0</v>
+      </c>
+      <c r="H48" t="str" xml:space="preserve">
         <v xml:space="preserve">Has appointment and is unable to work 
 Eilidh 22/08/2025</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
+    <row r="49">
+      <c r="A49" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B49" t="str">
         <v>Asokhia (NL), Deborah</v>
       </c>
-      <c r="C3" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D3" t="str">
+      <c r="C49" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D49" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E3" t="str">
-        <v>4</v>
-      </c>
-      <c r="F3" t="str">
-        <v>0</v>
-      </c>
-      <c r="G3" t="str">
-        <v>0</v>
-      </c>
-      <c r="H3" t="str">
+      <c r="E49" t="str">
+        <v>4</v>
+      </c>
+      <c r="F49" t="str">
+        <v>0</v>
+      </c>
+      <c r="G49" t="str">
+        <v>0</v>
+      </c>
+      <c r="H49" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
+    <row r="50">
+      <c r="A50" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B50" t="str">
         <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
-      <c r="C4" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D4" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E4" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F4" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G4" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="C50" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D50" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E50" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F50" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G50" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B51" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
-      <c r="C5" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D5" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="C51" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D51" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E51" t="str">
         <v>9</v>
       </c>
-      <c r="F5" t="str">
+      <c r="F51" t="str">
         <v>9</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G51" t="str">
         <v>9</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B52" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
       </c>
-      <c r="C6" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D6" t="str">
+      <c r="C52" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D52" t="str">
         <v>10:30-14:00</v>
       </c>
-      <c r="E6" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F6" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G6" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="E52" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F52" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G52" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H52" t="str">
         <v>Confirmed at induction with MT</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
+    <row r="53">
+      <c r="A53" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B53" t="str">
         <v>Hussain (NL) (GH), Mustansar</v>
       </c>
-      <c r="C7" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D7" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E7" t="str">
-        <v>6</v>
-      </c>
-      <c r="F7" t="str">
-        <v>6</v>
-      </c>
-      <c r="G7" t="str">
-        <v>6</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
+      <c r="C53" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D53" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E53" t="str">
+        <v>6</v>
+      </c>
+      <c r="F53" t="str">
+        <v>6</v>
+      </c>
+      <c r="G53" t="str">
+        <v>6</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B54" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
-      <c r="C8" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D8" t="str">
+      <c r="C54" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D54" t="str">
         <v>09:15-15:00</v>
       </c>
-      <c r="E8" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F8" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G8" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H8" t="str">
+      <c r="E54" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F54" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G54" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H54" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
+    <row r="55">
+      <c r="A55" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B55" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
       </c>
-      <c r="C9" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D9" t="str">
+      <c r="C55" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D55" t="str">
         <v>08:00-15:15</v>
       </c>
-      <c r="E9" t="str">
-        <v>4</v>
-      </c>
-      <c r="F9" t="str">
-        <v>4</v>
-      </c>
-      <c r="G9" t="str">
-        <v>4</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
+      <c r="E55" t="str">
+        <v>4</v>
+      </c>
+      <c r="F55" t="str">
+        <v>4</v>
+      </c>
+      <c r="G55" t="str">
+        <v>4</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B56" t="str">
         <v>McGhie (NL) (GH), Cheryl</v>
       </c>
-      <c r="C10" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D10" t="str">
+      <c r="C56" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D56" t="str">
         <v>16:45-21:30</v>
       </c>
-      <c r="E10" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F10" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G10" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
+      <c r="E56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G56" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B57" t="str">
         <v>Mooney (NL), Lynsey (GH)</v>
       </c>
-      <c r="C11" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D11" t="str">
+      <c r="C57" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D57" t="str">
         <v>08:00-14:00</v>
       </c>
-      <c r="E11" t="str">
-        <v>4</v>
-      </c>
-      <c r="F11" t="str">
-        <v>4</v>
-      </c>
-      <c r="G11" t="str">
-        <v>4</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
+      <c r="E57" t="str">
+        <v>4</v>
+      </c>
+      <c r="F57" t="str">
+        <v>4</v>
+      </c>
+      <c r="G57" t="str">
+        <v>4</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B12" t="str">
+      <c r="B58" t="str">
         <v>Nelson (NL), Anne</v>
       </c>
-      <c r="C12" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D12" t="str">
+      <c r="C58" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D58" t="str">
         <v>08:00-13:00</v>
       </c>
-      <c r="E12" t="str">
+      <c r="E58" t="str">
         <v>5.33</v>
       </c>
-      <c r="F12" t="str">
+      <c r="F58" t="str">
         <v>5.33</v>
       </c>
-      <c r="G12" t="str">
+      <c r="G58" t="str">
         <v>5.33</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
+      <c r="H58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B59" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
-      <c r="C13" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D13" t="str">
+      <c r="C59" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D59" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E13" t="str">
+      <c r="E59" t="str">
         <v>2.67</v>
       </c>
-      <c r="F13" t="str">
+      <c r="F59" t="str">
         <v>2.67</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G59" t="str">
         <v>2.67</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
+      <c r="H59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
         <v>2025-09-12</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B60" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="C14" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D14" t="str">
+      <c r="C60" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D60" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E14" t="str">
-        <v>6</v>
-      </c>
-      <c r="F14" t="str">
-        <v>6</v>
-      </c>
-      <c r="G14" t="str">
-        <v>6</v>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
+      <c r="E60" t="str">
+        <v>6</v>
+      </c>
+      <c r="F60" t="str">
+        <v>6</v>
+      </c>
+      <c r="G60" t="str">
+        <v>6</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B61" t="str">
         <v>Asokhia (NL), Deborah</v>
       </c>
-      <c r="C15" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D15" t="str">
+      <c r="C61" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D61" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E15" t="str">
-        <v>4</v>
-      </c>
-      <c r="F15" t="str">
-        <v>4</v>
-      </c>
-      <c r="G15" t="str">
-        <v>4</v>
-      </c>
-      <c r="H15" t="str">
+      <c r="E61" t="str">
+        <v>4</v>
+      </c>
+      <c r="F61" t="str">
+        <v>4</v>
+      </c>
+      <c r="G61" t="str">
+        <v>4</v>
+      </c>
+      <c r="H61" t="str">
         <v>Agreed at induction with MT and SM - 09/05/2025</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
+    <row r="62">
+      <c r="A62" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B62" t="str">
         <v>Barton (NL) (GH), Kaitlyn</v>
       </c>
-      <c r="C16" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D16" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E16" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F16" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G16" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
+      <c r="C62" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D62" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G62" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B63" t="str">
         <v>Fayaz GH, Shafiya</v>
       </c>
-      <c r="C17" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D17" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E17" t="str">
+      <c r="C63" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D63" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E63" t="str">
         <v>9</v>
       </c>
-      <c r="F17" t="str">
+      <c r="F63" t="str">
         <v>9</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G63" t="str">
         <v>9</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
+      <c r="H63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B18" t="str">
-        <v>Ferris, Marykate</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D18" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E18" t="str">
+      <c r="B64" t="str">
+        <v>Ferris (NL), Marykate</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D64" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E64" t="str">
         <v>6.67</v>
       </c>
-      <c r="F18" t="str">
+      <c r="F64" t="str">
         <v>6.67</v>
       </c>
-      <c r="G18" t="str">
+      <c r="G64" t="str">
         <v>6.67</v>
       </c>
-      <c r="H18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
+      <c r="H64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B65" t="str">
         <v>Forbes (NL) (GH), Amanda</v>
       </c>
-      <c r="C19" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D19" t="str">
+      <c r="C65" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D65" t="str">
         <v>09:15-15:15</v>
       </c>
-      <c r="E19" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F19" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G19" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
+      <c r="E65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G65" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B66" t="str">
         <v>Griffiths (NL), Wayne (GH)</v>
       </c>
-      <c r="C20" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D20" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E20" t="str">
-        <v>6</v>
-      </c>
-      <c r="F20" t="str">
-        <v>6</v>
-      </c>
-      <c r="G20" t="str">
-        <v>6</v>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
+      <c r="C66" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D66" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E66" t="str">
+        <v>6</v>
+      </c>
+      <c r="F66" t="str">
+        <v>6</v>
+      </c>
+      <c r="G66" t="str">
+        <v>6</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B67" t="str">
         <v>Ibrahim (NL), Olusegun Isaac</v>
       </c>
-      <c r="C21" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D21" t="str">
+      <c r="C67" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D67" t="str">
         <v>09:15-15:00</v>
       </c>
-      <c r="E21" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F21" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G21" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H21" t="str">
+      <c r="E67" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F67" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G67" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H67" t="str">
         <v>Agreed at induction with SM 25/04/2025 - MT</v>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B68" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C68" t="str">
         <v>Other Unavailable</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D68" t="str">
         <v>08:00-15:00</v>
       </c>
-      <c r="E22" t="str">
-        <v>4</v>
-      </c>
-      <c r="F22" t="str">
-        <v>4</v>
-      </c>
-      <c r="G22" t="str">
-        <v>0</v>
-      </c>
-      <c r="H22" t="str" xml:space="preserve">
+      <c r="E68" t="str">
+        <v>4</v>
+      </c>
+      <c r="F68" t="str">
+        <v>4</v>
+      </c>
+      <c r="G68" t="str">
+        <v>0</v>
+      </c>
+      <c r="H68" t="str" xml:space="preserve">
         <v xml:space="preserve">Family event
 Eilidh 01/09/2025</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
+    <row r="69">
+      <c r="A69" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B69" t="str">
         <v>Mcewan (NL) (GH), Makala</v>
       </c>
-      <c r="C23" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D23" t="str">
+      <c r="C69" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D69" t="str">
         <v>08:00-15:15</v>
       </c>
-      <c r="E23" t="str">
-        <v>4</v>
-      </c>
-      <c r="F23" t="str">
-        <v>0</v>
-      </c>
-      <c r="G23" t="str">
-        <v>0</v>
-      </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
+      <c r="E69" t="str">
+        <v>4</v>
+      </c>
+      <c r="F69" t="str">
+        <v>0</v>
+      </c>
+      <c r="G69" t="str">
+        <v>0</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B70" t="str">
         <v>McGhie (NL) (GH), Cheryl</v>
       </c>
-      <c r="C24" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D24" t="str">
+      <c r="C70" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D70" t="str">
         <v>16:45-21:30</v>
       </c>
-      <c r="E24" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="F24" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="G24" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
+      <c r="E70" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="F70" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="G70" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B71" t="str">
         <v>Mooney (NL), Lynsey (GH)</v>
       </c>
-      <c r="C25" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D25" t="str">
+      <c r="C71" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D71" t="str">
         <v>08:00-15:00</v>
       </c>
-      <c r="E25" t="str">
-        <v>4</v>
-      </c>
-      <c r="F25" t="str">
-        <v>4</v>
-      </c>
-      <c r="G25" t="str">
-        <v>4</v>
-      </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
+      <c r="E71" t="str">
+        <v>4</v>
+      </c>
+      <c r="F71" t="str">
+        <v>4</v>
+      </c>
+      <c r="G71" t="str">
+        <v>4</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B72" t="str">
         <v>Nelson (NL), Anne</v>
       </c>
-      <c r="C26" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D26" t="str">
+      <c r="C72" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D72" t="str">
         <v>08:00-17:15</v>
       </c>
-      <c r="E26" t="str">
+      <c r="E72" t="str">
         <v>5.33</v>
       </c>
-      <c r="F26" t="str">
+      <c r="F72" t="str">
         <v>5.33</v>
       </c>
-      <c r="G26" t="str">
+      <c r="G72" t="str">
         <v>5.33</v>
       </c>
-      <c r="H26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B73" t="str">
         <v>O'Brien (NL) (GH), Brooke</v>
       </c>
-      <c r="C27" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D27" t="str">
+      <c r="C73" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D73" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E73" t="str">
         <v>2.67</v>
       </c>
-      <c r="F27" t="str">
+      <c r="F73" t="str">
         <v>2.67</v>
       </c>
-      <c r="G27" t="str">
+      <c r="G73" t="str">
         <v>2.67</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
         <v>2025-09-11</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B74" t="str">
         <v>Wylie (NL), Lori</v>
       </c>
-      <c r="C28" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D28" t="str">
+      <c r="C74" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D74" t="str">
         <v>09:15-14:00</v>
       </c>
-      <c r="E28" t="str">
-        <v>6</v>
-      </c>
-      <c r="F28" t="str">
-        <v>6</v>
-      </c>
-      <c r="G28" t="str">
-        <v>6</v>
-      </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
+      <c r="E74" t="str">
+        <v>6</v>
+      </c>
+      <c r="F74" t="str">
+        <v>6</v>
+      </c>
+      <c r="G74" t="str">
+        <v>6</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>2025-09-14</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B75" t="str">
         <v>Adeyanju (NL) (GH), Adedayo</v>
       </c>
-      <c r="C29" t="str">
-        <v>Available</v>
-      </c>
-      <c r="D29" t="str">
-        <v>08:00-21:30</v>
-      </c>
-      <c r="E29" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="F29" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="G29" t="str">
-        <v>7.5</v>
-      </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
+      <c r="C75" t="str">
+        <v>Available</v>
+      </c>
+      <c r="D75" t="str">
+        <v>08:00-21:30</v>
+      </c>
+      <c r="E75" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="F75" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="G75" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="st